--- a/finance/_refresh_rakta.xlsx
+++ b/finance/_refresh_rakta.xlsx
@@ -45,8 +45,8 @@
     <definedName name="load_sel">'Assumptions'!$B$36</definedName>
     <definedName name="revleg_sel">'Assumptions'!$B$37</definedName>
     <definedName name="country_opex">'Country opex'!$A$4:$G$4</definedName>
-    <definedName name="som_floor_fleet">'Corridor economics'!$D$62</definedName>
-    <definedName name="som_floor_rev">'Corridor economics'!$E$62</definedName>
+    <definedName name="som_floor_fleet">'Corridor economics'!$D$51</definedName>
+    <definedName name="som_floor_rev">'Corridor economics'!$E$51</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -1814,7 +1814,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX66"/>
+  <dimension ref="A1:AX56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -2274,7 +2274,7 @@
         <v/>
       </c>
       <c r="AG4" s="31" t="n">
-        <v>4285</v>
+        <v>5217</v>
       </c>
       <c r="AH4" s="32" t="inlineStr">
         <is>
@@ -2341,11 +2341,11 @@
       </c>
       <c r="C5" s="30" t="inlineStr">
         <is>
-          <t>Dubai Islands Marina → Dubai island Marina Slipway</t>
+          <t>Ras Al Khaimah Harbour → RAK Corniche public pier</t>
         </is>
       </c>
       <c r="D5" s="31" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="E5" s="26" t="n">
         <v>35</v>
@@ -2460,7 +2460,7 @@
         <v/>
       </c>
       <c r="AG5" s="31" t="n">
-        <v>4285</v>
+        <v>5217</v>
       </c>
       <c r="AH5" s="32" t="inlineStr">
         <is>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C6" s="30" t="inlineStr">
         <is>
-          <t>Ras Al Khaimah Harbour → RAK Corniche public pier</t>
+          <t>Marjan Island Resort &amp; Spa beach jetty → Hampton by Hilton Marjan Island beach landing</t>
         </is>
       </c>
       <c r="D6" s="31" t="n">
@@ -2646,7 +2646,7 @@
         <v/>
       </c>
       <c r="AG6" s="31" t="n">
-        <v>4285</v>
+        <v>5217</v>
       </c>
       <c r="AH6" s="32" t="inlineStr">
         <is>
@@ -2713,11 +2713,11 @@
       </c>
       <c r="C7" s="30" t="inlineStr">
         <is>
-          <t>Marjan Island Resort &amp; Spa beach jetty → Hampton by Hilton Marjan Island beach landing</t>
+          <t>Wynn Al Marjan Island arrival lagoon → Marjan Island Resort &amp; Spa beach jetty</t>
         </is>
       </c>
       <c r="D7" s="31" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="E7" s="26" t="n">
         <v>35</v>
@@ -2832,7 +2832,7 @@
         <v/>
       </c>
       <c r="AG7" s="31" t="n">
-        <v>4285</v>
+        <v>5217</v>
       </c>
       <c r="AH7" s="32" t="inlineStr">
         <is>
@@ -2899,11 +2899,11 @@
       </c>
       <c r="C8" s="30" t="inlineStr">
         <is>
-          <t>Deira Old Souq Marine Transport Station → Al Ghubaiba Marine Transport Station 1</t>
+          <t>Anantara Mina Al Arab Ras Al Khaimah Resort jetty → InterContinental Ras Al Khaimah Mina Al Arab Resort &amp; Spa jetty</t>
         </is>
       </c>
       <c r="D8" s="31" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="E8" s="26" t="n">
         <v>35</v>
@@ -3018,7 +3018,7 @@
         <v/>
       </c>
       <c r="AG8" s="31" t="n">
-        <v>4285</v>
+        <v>5217</v>
       </c>
       <c r="AH8" s="32" t="inlineStr">
         <is>
@@ -3085,11 +3085,11 @@
       </c>
       <c r="C9" s="30" t="inlineStr">
         <is>
-          <t>Cruise Terminal 3 - Port Rashid → Cruise Terminal 2</t>
+          <t>Al Hamra Marina &amp; Royal Yacht Club RAK → Waldorf Astoria Ras Al Khaimah jetty</t>
         </is>
       </c>
       <c r="D9" s="31" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="E9" s="26" t="n">
         <v>35</v>
@@ -3204,7 +3204,7 @@
         <v/>
       </c>
       <c r="AG9" s="31" t="n">
-        <v>4285</v>
+        <v>5217</v>
       </c>
       <c r="AH9" s="32" t="inlineStr">
         <is>
@@ -3271,11 +3271,11 @@
       </c>
       <c r="C10" s="30" t="inlineStr">
         <is>
-          <t>Wynn Al Marjan Island arrival lagoon → Marjan Island Resort &amp; Spa beach jetty</t>
+          <t>Al Marjan Island public arrival marina → Hampton by Hilton Marjan Island beach landing</t>
         </is>
       </c>
       <c r="D10" s="31" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="E10" s="26" t="n">
         <v>35</v>
@@ -3390,7 +3390,7 @@
         <v/>
       </c>
       <c r="AG10" s="31" t="n">
-        <v>4285</v>
+        <v>5217</v>
       </c>
       <c r="AH10" s="32" t="inlineStr">
         <is>
@@ -3457,11 +3457,11 @@
       </c>
       <c r="C11" s="30" t="inlineStr">
         <is>
-          <t>Anantara Mina Al Arab Ras Al Khaimah Resort jetty → InterContinental Ras Al Khaimah Mina Al Arab Resort &amp; Spa jetty</t>
+          <t>Mina Al Arab marina / lagoon basin → InterContinental Ras Al Khaimah Mina Al Arab Resort &amp; Spa jetty</t>
         </is>
       </c>
       <c r="D11" s="31" t="n">
-        <v>0.6</v>
+        <v>0.9</v>
       </c>
       <c r="E11" s="26" t="n">
         <v>35</v>
@@ -3576,7 +3576,7 @@
         <v/>
       </c>
       <c r="AG11" s="31" t="n">
-        <v>4285</v>
+        <v>5217</v>
       </c>
       <c r="AH11" s="32" t="inlineStr">
         <is>
@@ -3643,11 +3643,11 @@
       </c>
       <c r="C12" s="30" t="inlineStr">
         <is>
-          <t>Al Sabkha Marine Transport Station → Deira Old Souq Marine Transport Station</t>
+          <t>Anantara Mina Al Arab Ras Al Khaimah Resort jetty → Mina Al Arab marina / lagoon basin</t>
         </is>
       </c>
       <c r="D12" s="31" t="n">
-        <v>0.6</v>
+        <v>0.9</v>
       </c>
       <c r="E12" s="26" t="n">
         <v>35</v>
@@ -3762,7 +3762,7 @@
         <v/>
       </c>
       <c r="AG12" s="31" t="n">
-        <v>4285</v>
+        <v>5217</v>
       </c>
       <c r="AH12" s="32" t="inlineStr">
         <is>
@@ -3829,11 +3829,11 @@
       </c>
       <c r="C13" s="30" t="inlineStr">
         <is>
-          <t>Cruise Terminal 3 - Port Rashid → Dubai island Marina Slipway</t>
+          <t>Rixos Bab Al Bahr beach jetty → Hampton by Hilton Marjan Island beach landing</t>
         </is>
       </c>
       <c r="D13" s="31" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="E13" s="26" t="n">
         <v>35</v>
@@ -3948,7 +3948,7 @@
         <v/>
       </c>
       <c r="AG13" s="31" t="n">
-        <v>4285</v>
+        <v>5217</v>
       </c>
       <c r="AH13" s="32" t="inlineStr">
         <is>
@@ -4015,11 +4015,11 @@
       </c>
       <c r="C14" s="30" t="inlineStr">
         <is>
-          <t>Khasab → Khasab Cruise Terminal</t>
+          <t>Wynn Al Marjan Island arrival lagoon → Hampton by Hilton Marjan Island beach landing</t>
         </is>
       </c>
       <c r="D14" s="31" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="E14" s="26" t="n">
         <v>35</v>
@@ -4134,7 +4134,7 @@
         <v/>
       </c>
       <c r="AG14" s="31" t="n">
-        <v>4285</v>
+        <v>5217</v>
       </c>
       <c r="AH14" s="32" t="inlineStr">
         <is>
@@ -4201,11 +4201,11 @@
       </c>
       <c r="C15" s="30" t="inlineStr">
         <is>
-          <t>Al Hamra Marina &amp; Royal Yacht Club RAK → Waldorf Astoria Ras Al Khaimah jetty</t>
+          <t>Ras Al Khaimah Harbour → Hilton Garden Inn Ras Al Khaimah (Corniche) jetty</t>
         </is>
       </c>
       <c r="D15" s="31" t="n">
-        <v>0.7</v>
+        <v>1.1</v>
       </c>
       <c r="E15" s="26" t="n">
         <v>35</v>
@@ -4320,7 +4320,7 @@
         <v/>
       </c>
       <c r="AG15" s="31" t="n">
-        <v>4285</v>
+        <v>5217</v>
       </c>
       <c r="AH15" s="32" t="inlineStr">
         <is>
@@ -4387,11 +4387,11 @@
       </c>
       <c r="C16" s="30" t="inlineStr">
         <is>
-          <t>Al Ghubaiba Marine Transport Station 1 → Al Sabkha Marine Transport Station</t>
+          <t>Hilton Garden Inn Ras Al Khaimah (Corniche) jetty → RAK Corniche public pier</t>
         </is>
       </c>
       <c r="D16" s="31" t="n">
-        <v>0.7</v>
+        <v>1.2</v>
       </c>
       <c r="E16" s="26" t="n">
         <v>35</v>
@@ -4506,7 +4506,7 @@
         <v/>
       </c>
       <c r="AG16" s="31" t="n">
-        <v>4285</v>
+        <v>5217</v>
       </c>
       <c r="AH16" s="32" t="inlineStr">
         <is>
@@ -4573,11 +4573,11 @@
       </c>
       <c r="C17" s="30" t="inlineStr">
         <is>
-          <t>Al Marjan Island public arrival marina → Hampton by Hilton Marjan Island beach landing</t>
+          <t>Bin Majid Beach Resort jetty → Acacia by Bin Majid jetty</t>
         </is>
       </c>
       <c r="D17" s="31" t="n">
-        <v>0.8</v>
+        <v>1.2</v>
       </c>
       <c r="E17" s="26" t="n">
         <v>35</v>
@@ -4692,7 +4692,7 @@
         <v/>
       </c>
       <c r="AG17" s="31" t="n">
-        <v>4285</v>
+        <v>5217</v>
       </c>
       <c r="AH17" s="32" t="inlineStr">
         <is>
@@ -4759,11 +4759,11 @@
       </c>
       <c r="C18" s="30" t="inlineStr">
         <is>
-          <t>Dubai Islands Marina → Cruise Terminal 3 - Port Rashid</t>
+          <t>Al Zorah Marina 1 → Ajman Marina</t>
         </is>
       </c>
       <c r="D18" s="31" t="n">
-        <v>0.8</v>
+        <v>1.6</v>
       </c>
       <c r="E18" s="26" t="n">
         <v>35</v>
@@ -4878,7 +4878,7 @@
         <v/>
       </c>
       <c r="AG18" s="31" t="n">
-        <v>4285</v>
+        <v>5217</v>
       </c>
       <c r="AH18" s="32" t="inlineStr">
         <is>
@@ -4945,11 +4945,11 @@
       </c>
       <c r="C19" s="30" t="inlineStr">
         <is>
-          <t>Mina Al Arab marina / lagoon basin → InterContinental Ras Al Khaimah Mina Al Arab Resort &amp; Spa jetty</t>
+          <t>Raksa → Ras Al Khaimah Harbour</t>
         </is>
       </c>
       <c r="D19" s="31" t="n">
-        <v>0.9</v>
+        <v>1.9</v>
       </c>
       <c r="E19" s="26" t="n">
         <v>35</v>
@@ -5064,7 +5064,7 @@
         <v/>
       </c>
       <c r="AG19" s="31" t="n">
-        <v>4285</v>
+        <v>5217</v>
       </c>
       <c r="AH19" s="32" t="inlineStr">
         <is>
@@ -5131,11 +5131,11 @@
       </c>
       <c r="C20" s="30" t="inlineStr">
         <is>
-          <t>Anantara Mina Al Arab Ras Al Khaimah Resort jetty → Mina Al Arab marina / lagoon basin</t>
+          <t>Sha'am Fishing Boat Harbour → Sha'am coastal staging point</t>
         </is>
       </c>
       <c r="D20" s="31" t="n">
-        <v>0.9</v>
+        <v>2.1</v>
       </c>
       <c r="E20" s="26" t="n">
         <v>35</v>
@@ -5250,7 +5250,7 @@
         <v/>
       </c>
       <c r="AG20" s="31" t="n">
-        <v>4285</v>
+        <v>5217</v>
       </c>
       <c r="AH20" s="32" t="inlineStr">
         <is>
@@ -5317,11 +5317,11 @@
       </c>
       <c r="C21" s="30" t="inlineStr">
         <is>
-          <t>Rixos Bab Al Bahr beach jetty → Hampton by Hilton Marjan Island beach landing</t>
+          <t>The Cove Rotana Resort jetty → Anantara Mina Al Arab Ras Al Khaimah Resort jetty</t>
         </is>
       </c>
       <c r="D21" s="31" t="n">
-        <v>1</v>
+        <v>2.2</v>
       </c>
       <c r="E21" s="26" t="n">
         <v>35</v>
@@ -5436,7 +5436,7 @@
         <v/>
       </c>
       <c r="AG21" s="31" t="n">
-        <v>4285</v>
+        <v>5217</v>
       </c>
       <c r="AH21" s="32" t="inlineStr">
         <is>
@@ -5503,11 +5503,11 @@
       </c>
       <c r="C22" s="30" t="inlineStr">
         <is>
-          <t>Wynn Al Marjan Island arrival lagoon → Hampton by Hilton Marjan Island beach landing</t>
+          <t>ميناء صيادين غليلة → Sha'am Fishing Boat Harbour</t>
         </is>
       </c>
       <c r="D22" s="31" t="n">
-        <v>1</v>
+        <v>2.5</v>
       </c>
       <c r="E22" s="26" t="n">
         <v>35</v>
@@ -5622,7 +5622,7 @@
         <v/>
       </c>
       <c r="AG22" s="31" t="n">
-        <v>4285</v>
+        <v>5217</v>
       </c>
       <c r="AH22" s="32" t="inlineStr">
         <is>
@@ -5689,11 +5689,11 @@
       </c>
       <c r="C23" s="30" t="inlineStr">
         <is>
-          <t>Cruise Terminal 2 → Al Ghubaiba Marine Transport Station 1</t>
+          <t>Daba Port → Dibba Al-Hisn Marina - Sharjah</t>
         </is>
       </c>
       <c r="D23" s="31" t="n">
-        <v>1</v>
+        <v>2.7</v>
       </c>
       <c r="E23" s="26" t="n">
         <v>35</v>
@@ -5808,7 +5808,7 @@
         <v/>
       </c>
       <c r="AG23" s="31" t="n">
-        <v>4285</v>
+        <v>5217</v>
       </c>
       <c r="AH23" s="32" t="inlineStr">
         <is>
@@ -5875,11 +5875,11 @@
       </c>
       <c r="C24" s="30" t="inlineStr">
         <is>
-          <t>Ras Al Khaimah Harbour → Hilton Garden Inn Ras Al Khaimah (Corniche) jetty</t>
+          <t>ميناء صيادين غليلة → ميناء صيادين خورخوير</t>
         </is>
       </c>
       <c r="D24" s="31" t="n">
-        <v>1.1</v>
+        <v>2.8</v>
       </c>
       <c r="E24" s="26" t="n">
         <v>35</v>
@@ -5994,7 +5994,7 @@
         <v/>
       </c>
       <c r="AG24" s="31" t="n">
-        <v>4285</v>
+        <v>5217</v>
       </c>
       <c r="AH24" s="32" t="inlineStr">
         <is>
@@ -6061,11 +6061,11 @@
       </c>
       <c r="C25" s="30" t="inlineStr">
         <is>
-          <t>Hilton Garden Inn Ras Al Khaimah (Corniche) jetty → RAK Corniche public pier</t>
+          <t>Acacia by Bin Majid jetty → The Cove Rotana Resort jetty</t>
         </is>
       </c>
       <c r="D25" s="31" t="n">
-        <v>1.2</v>
+        <v>2.9</v>
       </c>
       <c r="E25" s="26" t="n">
         <v>35</v>
@@ -6180,7 +6180,7 @@
         <v/>
       </c>
       <c r="AG25" s="31" t="n">
-        <v>4285</v>
+        <v>5217</v>
       </c>
       <c r="AH25" s="32" t="inlineStr">
         <is>
@@ -6247,11 +6247,11 @@
       </c>
       <c r="C26" s="30" t="inlineStr">
         <is>
-          <t>Bin Majid Beach Resort jetty → Acacia by Bin Majid jetty</t>
+          <t>Raksa → Hilton Garden Inn Ras Al Khaimah (Corniche) jetty</t>
         </is>
       </c>
       <c r="D26" s="31" t="n">
-        <v>1.2</v>
+        <v>3</v>
       </c>
       <c r="E26" s="26" t="n">
         <v>35</v>
@@ -6366,7 +6366,7 @@
         <v/>
       </c>
       <c r="AG26" s="31" t="n">
-        <v>4285</v>
+        <v>5217</v>
       </c>
       <c r="AH26" s="32" t="inlineStr">
         <is>
@@ -6433,11 +6433,11 @@
       </c>
       <c r="C27" s="30" t="inlineStr">
         <is>
-          <t>Al Zorah Marina 1 → Ajman Marina</t>
+          <t>Bin Majid Beach Resort jetty → The Cove Rotana Resort jetty</t>
         </is>
       </c>
       <c r="D27" s="31" t="n">
-        <v>1.6</v>
+        <v>3</v>
       </c>
       <c r="E27" s="26" t="n">
         <v>35</v>
@@ -6552,7 +6552,7 @@
         <v/>
       </c>
       <c r="AG27" s="31" t="n">
-        <v>4285</v>
+        <v>5217</v>
       </c>
       <c r="AH27" s="32" t="inlineStr">
         <is>
@@ -6619,11 +6619,11 @@
       </c>
       <c r="C28" s="30" t="inlineStr">
         <is>
-          <t>Raksa → Ras Al Khaimah Harbour</t>
+          <t>Al Zorah Marina 1 → Hamriyah Port Main Harbour</t>
         </is>
       </c>
       <c r="D28" s="31" t="n">
-        <v>1.9</v>
+        <v>3.2</v>
       </c>
       <c r="E28" s="26" t="n">
         <v>35</v>
@@ -6738,7 +6738,7 @@
         <v/>
       </c>
       <c r="AG28" s="31" t="n">
-        <v>4285</v>
+        <v>5217</v>
       </c>
       <c r="AH28" s="32" t="inlineStr">
         <is>
@@ -6805,11 +6805,11 @@
       </c>
       <c r="C29" s="30" t="inlineStr">
         <is>
-          <t>Dubai Offshore Sailing Club → Dubai Canal Marine Transport Station 1</t>
+          <t>Sha'am coastal staging point → ميناء صيادين غليلة</t>
         </is>
       </c>
       <c r="D29" s="31" t="n">
-        <v>2</v>
+        <v>3.9</v>
       </c>
       <c r="E29" s="26" t="n">
         <v>35</v>
@@ -6924,7 +6924,7 @@
         <v/>
       </c>
       <c r="AG29" s="31" t="n">
-        <v>4285</v>
+        <v>5217</v>
       </c>
       <c r="AH29" s="32" t="inlineStr">
         <is>
@@ -6991,11 +6991,11 @@
       </c>
       <c r="C30" s="30" t="inlineStr">
         <is>
-          <t>Sha'am Fishing Boat Harbour → Sha'am coastal staging point</t>
+          <t>Ajman Marina → Hamriyah Port Main Harbour</t>
         </is>
       </c>
       <c r="D30" s="31" t="n">
-        <v>2.1</v>
+        <v>3.9</v>
       </c>
       <c r="E30" s="26" t="n">
         <v>35</v>
@@ -7110,7 +7110,7 @@
         <v/>
       </c>
       <c r="AG30" s="31" t="n">
-        <v>4285</v>
+        <v>5217</v>
       </c>
       <c r="AH30" s="32" t="inlineStr">
         <is>
@@ -7177,11 +7177,11 @@
       </c>
       <c r="C31" s="30" t="inlineStr">
         <is>
-          <t>The Cove Rotana Resort jetty → Anantara Mina Al Arab Ras Al Khaimah Resort jetty</t>
+          <t>ميناء صيادين خورخوير → Sha'am Fishing Boat Harbour</t>
         </is>
       </c>
       <c r="D31" s="31" t="n">
-        <v>2.2</v>
+        <v>4.3</v>
       </c>
       <c r="E31" s="26" t="n">
         <v>35</v>
@@ -7296,7 +7296,7 @@
         <v/>
       </c>
       <c r="AG31" s="31" t="n">
-        <v>4285</v>
+        <v>5217</v>
       </c>
       <c r="AH31" s="32" t="inlineStr">
         <is>
@@ -7363,11 +7363,11 @@
       </c>
       <c r="C32" s="30" t="inlineStr">
         <is>
-          <t>ميناء صيادين غليلة → Sha'am Fishing Boat Harbour</t>
+          <t>Zighy Marina → Dibba Al-Hisn Marina - Sharjah</t>
         </is>
       </c>
       <c r="D32" s="31" t="n">
-        <v>2.5</v>
+        <v>5.3</v>
       </c>
       <c r="E32" s="26" t="n">
         <v>35</v>
@@ -7482,7 +7482,7 @@
         <v/>
       </c>
       <c r="AG32" s="31" t="n">
-        <v>4285</v>
+        <v>5217</v>
       </c>
       <c r="AH32" s="32" t="inlineStr">
         <is>
@@ -7549,11 +7549,11 @@
       </c>
       <c r="C33" s="30" t="inlineStr">
         <is>
-          <t>Daba Port → Dibba Al-Hisn Marina - Sharjah</t>
+          <t>Gumda Fishing Harbour → Sha'am coastal staging point</t>
         </is>
       </c>
       <c r="D33" s="31" t="n">
-        <v>2.7</v>
+        <v>5.3</v>
       </c>
       <c r="E33" s="26" t="n">
         <v>35</v>
@@ -7668,7 +7668,7 @@
         <v/>
       </c>
       <c r="AG33" s="31" t="n">
-        <v>4285</v>
+        <v>5217</v>
       </c>
       <c r="AH33" s="32" t="inlineStr">
         <is>
@@ -7735,11 +7735,11 @@
       </c>
       <c r="C34" s="30" t="inlineStr">
         <is>
-          <t>ميناء صيادين غليلة → ميناء صيادين خورخوير</t>
+          <t>Gumda Fishing Harbour → Sha'am Fishing Boat Harbour</t>
         </is>
       </c>
       <c r="D34" s="31" t="n">
-        <v>2.8</v>
+        <v>7.2</v>
       </c>
       <c r="E34" s="26" t="n">
         <v>35</v>
@@ -7854,7 +7854,7 @@
         <v/>
       </c>
       <c r="AG34" s="31" t="n">
-        <v>4285</v>
+        <v>5217</v>
       </c>
       <c r="AH34" s="32" t="inlineStr">
         <is>
@@ -7921,11 +7921,11 @@
       </c>
       <c r="C35" s="30" t="inlineStr">
         <is>
-          <t>Acacia by Bin Majid jetty → The Cove Rotana Resort jetty</t>
+          <t>UAQ Marine Club → Hamriyah Port Main Harbour</t>
         </is>
       </c>
       <c r="D35" s="31" t="n">
-        <v>2.9</v>
+        <v>10.5</v>
       </c>
       <c r="E35" s="26" t="n">
         <v>35</v>
@@ -8040,7 +8040,7 @@
         <v/>
       </c>
       <c r="AG35" s="31" t="n">
-        <v>4285</v>
+        <v>5217</v>
       </c>
       <c r="AH35" s="32" t="inlineStr">
         <is>
@@ -8107,11 +8107,11 @@
       </c>
       <c r="C36" s="30" t="inlineStr">
         <is>
-          <t>Raksa → Hilton Garden Inn Ras Al Khaimah (Corniche) jetty</t>
+          <t>UAQ Marine Club → Rixos Bab Al Bahr beach jetty</t>
         </is>
       </c>
       <c r="D36" s="31" t="n">
-        <v>3</v>
+        <v>11.8</v>
       </c>
       <c r="E36" s="26" t="n">
         <v>35</v>
@@ -8226,7 +8226,7 @@
         <v/>
       </c>
       <c r="AG36" s="31" t="n">
-        <v>4285</v>
+        <v>5217</v>
       </c>
       <c r="AH36" s="32" t="inlineStr">
         <is>
@@ -8293,11 +8293,11 @@
       </c>
       <c r="C37" s="30" t="inlineStr">
         <is>
-          <t>Bin Majid Beach Resort jetty → The Cove Rotana Resort jetty</t>
+          <t>Ras Al Khaimah → ميناء صيادين غليلة</t>
         </is>
       </c>
       <c r="D37" s="31" t="n">
-        <v>3</v>
+        <v>11.9</v>
       </c>
       <c r="E37" s="26" t="n">
         <v>35</v>
@@ -8412,7 +8412,7 @@
         <v/>
       </c>
       <c r="AG37" s="31" t="n">
-        <v>4285</v>
+        <v>5217</v>
       </c>
       <c r="AH37" s="32" t="inlineStr">
         <is>
@@ -8479,11 +8479,11 @@
       </c>
       <c r="C38" s="30" t="inlineStr">
         <is>
-          <t>Al Zorah Marina 1 → Hamriyah Port Main Harbour</t>
+          <t>Ras Al Khaimah → Al Hamra Marina &amp; Royal Yacht Club RAK</t>
         </is>
       </c>
       <c r="D38" s="31" t="n">
-        <v>3.2</v>
+        <v>13.6</v>
       </c>
       <c r="E38" s="26" t="n">
         <v>35</v>
@@ -8598,7 +8598,7 @@
         <v/>
       </c>
       <c r="AG38" s="31" t="n">
-        <v>4285</v>
+        <v>5217</v>
       </c>
       <c r="AH38" s="32" t="inlineStr">
         <is>
@@ -8665,11 +8665,11 @@
       </c>
       <c r="C39" s="30" t="inlineStr">
         <is>
-          <t>Sha'am coastal staging point → ميناء صيادين غليلة</t>
+          <t>Ras Al Khaimah → Al Marjan Island public arrival marina</t>
         </is>
       </c>
       <c r="D39" s="31" t="n">
-        <v>3.9</v>
+        <v>16</v>
       </c>
       <c r="E39" s="26" t="n">
         <v>35</v>
@@ -8784,7 +8784,7 @@
         <v/>
       </c>
       <c r="AG39" s="31" t="n">
-        <v>4285</v>
+        <v>5217</v>
       </c>
       <c r="AH39" s="32" t="inlineStr">
         <is>
@@ -8851,11 +8851,11 @@
       </c>
       <c r="C40" s="30" t="inlineStr">
         <is>
-          <t>Ajman Marina → Hamriyah Port Main Harbour</t>
+          <t>Ras Al Khaimah → UAQ Marine Club</t>
         </is>
       </c>
       <c r="D40" s="31" t="n">
-        <v>3.9</v>
+        <v>26.6</v>
       </c>
       <c r="E40" s="26" t="n">
         <v>35</v>
@@ -8970,7 +8970,7 @@
         <v/>
       </c>
       <c r="AG40" s="31" t="n">
-        <v>4285</v>
+        <v>5217</v>
       </c>
       <c r="AH40" s="32" t="inlineStr">
         <is>
@@ -9037,11 +9037,11 @@
       </c>
       <c r="C41" s="30" t="inlineStr">
         <is>
-          <t>ميناء صيادين خورخوير → Sha'am Fishing Boat Harbour</t>
+          <t>Ras Al Khaimah → Ajman Marina</t>
         </is>
       </c>
       <c r="D41" s="31" t="n">
-        <v>4.3</v>
+        <v>39</v>
       </c>
       <c r="E41" s="26" t="n">
         <v>35</v>
@@ -9156,7 +9156,7 @@
         <v/>
       </c>
       <c r="AG41" s="31" t="n">
-        <v>4285</v>
+        <v>5217</v>
       </c>
       <c r="AH41" s="32" t="inlineStr">
         <is>
@@ -9223,11 +9223,11 @@
       </c>
       <c r="C42" s="30" t="inlineStr">
         <is>
-          <t>Gumda Fishing Harbour → Sha'am coastal staging point</t>
+          <t>Ras Al Khaimah → Sharjah</t>
         </is>
       </c>
       <c r="D42" s="31" t="n">
-        <v>5.3</v>
+        <v>42</v>
       </c>
       <c r="E42" s="26" t="n">
         <v>35</v>
@@ -9342,7 +9342,7 @@
         <v/>
       </c>
       <c r="AG42" s="31" t="n">
-        <v>4285</v>
+        <v>5217</v>
       </c>
       <c r="AH42" s="32" t="inlineStr">
         <is>
@@ -9409,11 +9409,11 @@
       </c>
       <c r="C43" s="30" t="inlineStr">
         <is>
-          <t>Zighy Marina → Dibba Al-Hisn Marina - Sharjah</t>
+          <t>Dubai Harbour Marina → Wynn Al Marjan Island arrival lagoon</t>
         </is>
       </c>
       <c r="D43" s="31" t="n">
-        <v>5.3</v>
+        <v>49.8</v>
       </c>
       <c r="E43" s="26" t="n">
         <v>35</v>
@@ -9528,7 +9528,7 @@
         <v/>
       </c>
       <c r="AG43" s="31" t="n">
-        <v>4285</v>
+        <v>5217</v>
       </c>
       <c r="AH43" s="32" t="inlineStr">
         <is>
@@ -9595,11 +9595,11 @@
       </c>
       <c r="C44" s="30" t="inlineStr">
         <is>
-          <t>Gumda Fishing Harbour → Sha'am Fishing Boat Harbour</t>
+          <t>Ras Al Khaimah → Dubai Islands Marina</t>
         </is>
       </c>
       <c r="D44" s="31" t="n">
-        <v>7.2</v>
+        <v>50</v>
       </c>
       <c r="E44" s="26" t="n">
         <v>35</v>
@@ -9714,7 +9714,7 @@
         <v/>
       </c>
       <c r="AG44" s="31" t="n">
-        <v>4285</v>
+        <v>5217</v>
       </c>
       <c r="AH44" s="32" t="inlineStr">
         <is>
@@ -9781,11 +9781,11 @@
       </c>
       <c r="C45" s="30" t="inlineStr">
         <is>
-          <t>UAQ Marine Club → Hamriyah Port Main Harbour</t>
+          <t>Ras Al Khaimah → Fujairah</t>
         </is>
       </c>
       <c r="D45" s="31" t="n">
-        <v>10.5</v>
+        <v>54.7</v>
       </c>
       <c r="E45" s="26" t="n">
         <v>35</v>
@@ -9900,7 +9900,7 @@
         <v/>
       </c>
       <c r="AG45" s="31" t="n">
-        <v>4285</v>
+        <v>5217</v>
       </c>
       <c r="AH45" s="32" t="inlineStr">
         <is>
@@ -9955,2172 +9955,133 @@
       <c r="AX45" s="44" t="n"/>
     </row>
     <row r="46">
-      <c r="A46" s="29" t="inlineStr">
+      <c r="A46" s="45" t="inlineStr">
+        <is>
+          <t>TOTAL / median</t>
+        </is>
+      </c>
+      <c r="T46" s="46">
+        <f>SUM(T4:T45)</f>
+        <v/>
+      </c>
+      <c r="AC46" s="46">
+        <f>SUM(AC4:AC45)</f>
+        <v/>
+      </c>
+      <c r="AD46" s="47">
+        <f>IF(T46=0,"",AC46/T46)</f>
+        <v/>
+      </c>
+      <c r="AL46" s="48">
+        <f>SUM(AL4:AL45)</f>
+        <v/>
+      </c>
+      <c r="AM46" s="46">
+        <f>SUM(AM4:AM45)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="8" t="inlineStr">
+        <is>
+          <t>Market fleet build-up — grounded floor (network-sum of raw vessel fractions per market, rounded once; subset slices excluded; legacy per-corridor-floor totals above kept for reference)</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="24" t="inlineStr">
+        <is>
+          <t>Market</t>
+        </is>
+      </c>
+      <c r="B49" s="24" t="inlineStr">
+        <is>
+          <t>Fleet basis</t>
+        </is>
+      </c>
+      <c r="C49" s="24" t="inlineStr">
+        <is>
+          <t>Raw vessels (sum)</t>
+        </is>
+      </c>
+      <c r="D49" s="24" t="inlineStr">
+        <is>
+          <t>Fleet (rounded once)</t>
+        </is>
+      </c>
+      <c r="E49" s="24" t="inlineStr">
+        <is>
+          <t>Market rev/yr (raw sum)</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="25" t="inlineStr">
         <is>
           <t>Gulf Authority Rakta</t>
         </is>
       </c>
-      <c r="B46" s="29" t="inlineStr">
-        <is>
-          <t>United Arab Emirates</t>
-        </is>
-      </c>
-      <c r="C46" s="30" t="inlineStr">
-        <is>
-          <t>UAQ Marine Club → Rixos Bab Al Bahr beach jetty</t>
-        </is>
-      </c>
-      <c r="D46" s="31" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="E46" s="26" t="n">
-        <v>35</v>
-      </c>
-      <c r="F46" s="32" t="inlineStr">
-        <is>
-          <t>T3</t>
-        </is>
-      </c>
-      <c r="G46" s="32" t="inlineStr">
-        <is>
-          <t>med-low</t>
-        </is>
-      </c>
-      <c r="H46" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="I46" s="33">
-        <f>60*D46/cruise_kt</f>
-        <v/>
-      </c>
-      <c r="J46" s="33">
-        <f>I46+turn_min+dwell_min</f>
-        <v/>
-      </c>
-      <c r="K46" s="34">
-        <f>MIN(10,FLOOR(60*service_hr/J46,1))</f>
-        <v/>
-      </c>
-      <c r="L46" s="34">
-        <f>ROUND(365*mech_uptime*H46,0)</f>
-        <v/>
-      </c>
-      <c r="M46" s="35">
-        <f>mech_uptime</f>
-        <v/>
-      </c>
-      <c r="N46" s="35">
-        <f>revleg_sel</f>
-        <v/>
-      </c>
-      <c r="O46" s="34">
-        <f>ROUND(K46*L46*revleg_sel,0)</f>
-        <v/>
-      </c>
-      <c r="P46" s="36">
-        <f>load_sel</f>
-        <v/>
-      </c>
-      <c r="Q46" s="36">
-        <f>pax_cap*P46</f>
-        <v/>
-      </c>
-      <c r="R46" s="34">
-        <f>Q46*O46</f>
-        <v/>
-      </c>
-      <c r="S46" s="37">
-        <f>E46*discount</f>
-        <v/>
-      </c>
-      <c r="T46" s="38">
-        <f>S46*R46</f>
-        <v/>
-      </c>
-      <c r="U46" s="38">
-        <f>(battery/range_nm)*D46*O46*VLOOKUP(B46,country_opex,3,FALSE)</f>
-        <v/>
-      </c>
-      <c r="V46" s="38">
-        <f>VLOOKUP(B46,country_opex,2,FALSE)*crew_factor</f>
-        <v/>
-      </c>
-      <c r="W46" s="38">
-        <f>VLOOKUP(B46,country_opex,5,FALSE)</f>
-        <v/>
-      </c>
-      <c r="X46" s="38">
-        <f>maint</f>
-        <v/>
-      </c>
-      <c r="Y46" s="38">
-        <f>VLOOKUP(B46,country_opex,7,FALSE)*ins_pct</f>
-        <v/>
-      </c>
-      <c r="Z46" s="38">
-        <f>charge_berth</f>
-        <v/>
-      </c>
-      <c r="AA46" s="38">
-        <f>U46+V46+W46+X46+Y46+Z46</f>
-        <v/>
-      </c>
-      <c r="AB46" s="38">
-        <f>VLOOKUP(B46,country_opex,7,FALSE)/dep_years</f>
-        <v/>
-      </c>
-      <c r="AC46" s="38">
-        <f>T46-AA46</f>
-        <v/>
-      </c>
-      <c r="AD46" s="35">
-        <f>IF(T46=0,"",AC46/T46)</f>
-        <v/>
-      </c>
-      <c r="AE46" s="36">
-        <f>IF(AC46&lt;=0,"",VLOOKUP(B46,country_opex,7,FALSE)/AC46)</f>
-        <v/>
-      </c>
-      <c r="AF46" s="33">
-        <f>((D46*O46/diesel_nmpg)*diesel_co2pg-(battery/range_nm)*D46*O46*VLOOKUP(B46,country_opex,4,FALSE))/1000</f>
-        <v/>
-      </c>
-      <c r="AG46" s="31" t="n">
-        <v>4285</v>
-      </c>
-      <c r="AH46" s="32" t="inlineStr">
-        <is>
-          <t>T3</t>
-        </is>
-      </c>
-      <c r="AI46" s="32" t="inlineStr">
-        <is>
-          <t>med-low</t>
-        </is>
-      </c>
-      <c r="AJ46" s="39" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="AK46" s="34">
-        <f>IF(AG46="","",AG46*AJ46)</f>
-        <v/>
-      </c>
-      <c r="AL46" s="34">
-        <f>IF(OR(AG46="",R46=0),"",MIN(IF(AS46="",9.9E+99,AS46),FLOOR(AK46/R46,1)))</f>
-        <v/>
-      </c>
-      <c r="AM46" s="38">
-        <f>IF(AL46="","",AL46*T46)</f>
-        <v/>
-      </c>
-      <c r="AN46" s="36">
-        <f>IF(OR(AG46="",R46=0),"",MIN(IF(AS46="",9.9E+99,AS46),AK46/R46))</f>
-        <v/>
-      </c>
-      <c r="AO46" s="38">
-        <f>IF(AN46="","",AN46*T46)</f>
-        <v/>
-      </c>
-      <c r="AP46" s="40" t="n"/>
-      <c r="AQ46" s="41" t="n"/>
-      <c r="AR46" s="41" t="n"/>
-      <c r="AS46" s="42" t="n"/>
-      <c r="AT46" s="43">
-        <f>IF(((S46*pax_cap*load_thin*ROUND(K46*L46*revleg_thin,0))-(((battery/range_nm)*D46*ROUND(K46*L46*revleg_thin,0)*VLOOKUP(B46,country_opex,3,FALSE))+V46+W46+X46+Y46+Z46))&lt;=0,"",VLOOKUP(B46,country_opex,7,FALSE)/((S46*pax_cap*load_thin*ROUND(K46*L46*revleg_thin,0))-(((battery/range_nm)*D46*ROUND(K46*L46*revleg_thin,0)*VLOOKUP(B46,country_opex,3,FALSE))+V46+W46+X46+Y46+Z46)))</f>
-        <v/>
-      </c>
-      <c r="AU46" s="43">
-        <f>IF(((S46*pax_cap*load_mid*ROUND(K46*L46*revleg_mid,0))-(((battery/range_nm)*D46*ROUND(K46*L46*revleg_mid,0)*VLOOKUP(B46,country_opex,3,FALSE))+V46+W46+X46+Y46+Z46))&lt;=0,"",VLOOKUP(B46,country_opex,7,FALSE)/((S46*pax_cap*load_mid*ROUND(K46*L46*revleg_mid,0))-(((battery/range_nm)*D46*ROUND(K46*L46*revleg_mid,0)*VLOOKUP(B46,country_opex,3,FALSE))+V46+W46+X46+Y46+Z46)))</f>
-        <v/>
-      </c>
-      <c r="AV46" s="43">
-        <f>IF(((S46*pax_cap*load_full*ROUND(K46*L46*revleg_full,0))-(((battery/range_nm)*D46*ROUND(K46*L46*revleg_full,0)*VLOOKUP(B46,country_opex,3,FALSE))+V46+W46+X46+Y46+Z46))&lt;=0,"",VLOOKUP(B46,country_opex,7,FALSE)/((S46*pax_cap*load_full*ROUND(K46*L46*revleg_full,0))-(((battery/range_nm)*D46*ROUND(K46*L46*revleg_full,0)*VLOOKUP(B46,country_opex,3,FALSE))+V46+W46+X46+Y46+Z46)))</f>
-        <v/>
-      </c>
-      <c r="AW46" s="44" t="n"/>
-      <c r="AX46" s="44" t="n"/>
-    </row>
-    <row r="47">
-      <c r="A47" s="29" t="inlineStr">
-        <is>
-          <t>Gulf Authority Rakta</t>
-        </is>
-      </c>
-      <c r="B47" s="29" t="inlineStr">
-        <is>
-          <t>United Arab Emirates</t>
-        </is>
-      </c>
-      <c r="C47" s="30" t="inlineStr">
-        <is>
-          <t>Ras Al Khaimah → ميناء صيادين غليلة</t>
-        </is>
-      </c>
-      <c r="D47" s="31" t="n">
-        <v>11.9</v>
-      </c>
-      <c r="E47" s="26" t="n">
-        <v>35</v>
-      </c>
-      <c r="F47" s="32" t="inlineStr">
-        <is>
-          <t>T3</t>
-        </is>
-      </c>
-      <c r="G47" s="32" t="inlineStr">
-        <is>
-          <t>med-low</t>
-        </is>
-      </c>
-      <c r="H47" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="I47" s="33">
-        <f>60*D47/cruise_kt</f>
-        <v/>
-      </c>
-      <c r="J47" s="33">
-        <f>I47+turn_min+dwell_min</f>
-        <v/>
-      </c>
-      <c r="K47" s="34">
-        <f>MIN(10,FLOOR(60*service_hr/J47,1))</f>
-        <v/>
-      </c>
-      <c r="L47" s="34">
-        <f>ROUND(365*mech_uptime*H47,0)</f>
-        <v/>
-      </c>
-      <c r="M47" s="35">
-        <f>mech_uptime</f>
-        <v/>
-      </c>
-      <c r="N47" s="35">
-        <f>revleg_sel</f>
-        <v/>
-      </c>
-      <c r="O47" s="34">
-        <f>ROUND(K47*L47*revleg_sel,0)</f>
-        <v/>
-      </c>
-      <c r="P47" s="36">
-        <f>load_sel</f>
-        <v/>
-      </c>
-      <c r="Q47" s="36">
-        <f>pax_cap*P47</f>
-        <v/>
-      </c>
-      <c r="R47" s="34">
-        <f>Q47*O47</f>
-        <v/>
-      </c>
-      <c r="S47" s="37">
-        <f>E47*discount</f>
-        <v/>
-      </c>
-      <c r="T47" s="38">
-        <f>S47*R47</f>
-        <v/>
-      </c>
-      <c r="U47" s="38">
-        <f>(battery/range_nm)*D47*O47*VLOOKUP(B47,country_opex,3,FALSE)</f>
-        <v/>
-      </c>
-      <c r="V47" s="38">
-        <f>VLOOKUP(B47,country_opex,2,FALSE)*crew_factor</f>
-        <v/>
-      </c>
-      <c r="W47" s="38">
-        <f>VLOOKUP(B47,country_opex,5,FALSE)</f>
-        <v/>
-      </c>
-      <c r="X47" s="38">
-        <f>maint</f>
-        <v/>
-      </c>
-      <c r="Y47" s="38">
-        <f>VLOOKUP(B47,country_opex,7,FALSE)*ins_pct</f>
-        <v/>
-      </c>
-      <c r="Z47" s="38">
-        <f>charge_berth</f>
-        <v/>
-      </c>
-      <c r="AA47" s="38">
-        <f>U47+V47+W47+X47+Y47+Z47</f>
-        <v/>
-      </c>
-      <c r="AB47" s="38">
-        <f>VLOOKUP(B47,country_opex,7,FALSE)/dep_years</f>
-        <v/>
-      </c>
-      <c r="AC47" s="38">
-        <f>T47-AA47</f>
-        <v/>
-      </c>
-      <c r="AD47" s="35">
-        <f>IF(T47=0,"",AC47/T47)</f>
-        <v/>
-      </c>
-      <c r="AE47" s="36">
-        <f>IF(AC47&lt;=0,"",VLOOKUP(B47,country_opex,7,FALSE)/AC47)</f>
-        <v/>
-      </c>
-      <c r="AF47" s="33">
-        <f>((D47*O47/diesel_nmpg)*diesel_co2pg-(battery/range_nm)*D47*O47*VLOOKUP(B47,country_opex,4,FALSE))/1000</f>
-        <v/>
-      </c>
-      <c r="AG47" s="31" t="n">
-        <v>4285</v>
-      </c>
-      <c r="AH47" s="32" t="inlineStr">
-        <is>
-          <t>T3</t>
-        </is>
-      </c>
-      <c r="AI47" s="32" t="inlineStr">
-        <is>
-          <t>med-low</t>
-        </is>
-      </c>
-      <c r="AJ47" s="39" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="AK47" s="34">
-        <f>IF(AG47="","",AG47*AJ47)</f>
-        <v/>
-      </c>
-      <c r="AL47" s="34">
-        <f>IF(OR(AG47="",R47=0),"",MIN(IF(AS47="",9.9E+99,AS47),FLOOR(AK47/R47,1)))</f>
-        <v/>
-      </c>
-      <c r="AM47" s="38">
-        <f>IF(AL47="","",AL47*T47)</f>
-        <v/>
-      </c>
-      <c r="AN47" s="36">
-        <f>IF(OR(AG47="",R47=0),"",MIN(IF(AS47="",9.9E+99,AS47),AK47/R47))</f>
-        <v/>
-      </c>
-      <c r="AO47" s="38">
-        <f>IF(AN47="","",AN47*T47)</f>
-        <v/>
-      </c>
-      <c r="AP47" s="40" t="n"/>
-      <c r="AQ47" s="41" t="n"/>
-      <c r="AR47" s="41" t="n"/>
-      <c r="AS47" s="42" t="n"/>
-      <c r="AT47" s="43">
-        <f>IF(((S47*pax_cap*load_thin*ROUND(K47*L47*revleg_thin,0))-(((battery/range_nm)*D47*ROUND(K47*L47*revleg_thin,0)*VLOOKUP(B47,country_opex,3,FALSE))+V47+W47+X47+Y47+Z47))&lt;=0,"",VLOOKUP(B47,country_opex,7,FALSE)/((S47*pax_cap*load_thin*ROUND(K47*L47*revleg_thin,0))-(((battery/range_nm)*D47*ROUND(K47*L47*revleg_thin,0)*VLOOKUP(B47,country_opex,3,FALSE))+V47+W47+X47+Y47+Z47)))</f>
-        <v/>
-      </c>
-      <c r="AU47" s="43">
-        <f>IF(((S47*pax_cap*load_mid*ROUND(K47*L47*revleg_mid,0))-(((battery/range_nm)*D47*ROUND(K47*L47*revleg_mid,0)*VLOOKUP(B47,country_opex,3,FALSE))+V47+W47+X47+Y47+Z47))&lt;=0,"",VLOOKUP(B47,country_opex,7,FALSE)/((S47*pax_cap*load_mid*ROUND(K47*L47*revleg_mid,0))-(((battery/range_nm)*D47*ROUND(K47*L47*revleg_mid,0)*VLOOKUP(B47,country_opex,3,FALSE))+V47+W47+X47+Y47+Z47)))</f>
-        <v/>
-      </c>
-      <c r="AV47" s="43">
-        <f>IF(((S47*pax_cap*load_full*ROUND(K47*L47*revleg_full,0))-(((battery/range_nm)*D47*ROUND(K47*L47*revleg_full,0)*VLOOKUP(B47,country_opex,3,FALSE))+V47+W47+X47+Y47+Z47))&lt;=0,"",VLOOKUP(B47,country_opex,7,FALSE)/((S47*pax_cap*load_full*ROUND(K47*L47*revleg_full,0))-(((battery/range_nm)*D47*ROUND(K47*L47*revleg_full,0)*VLOOKUP(B47,country_opex,3,FALSE))+V47+W47+X47+Y47+Z47)))</f>
-        <v/>
-      </c>
-      <c r="AW47" s="44" t="n"/>
-      <c r="AX47" s="44" t="n"/>
-    </row>
-    <row r="48">
-      <c r="A48" s="29" t="inlineStr">
-        <is>
-          <t>Gulf Authority Rakta</t>
-        </is>
-      </c>
-      <c r="B48" s="29" t="inlineStr">
-        <is>
-          <t>United Arab Emirates</t>
-        </is>
-      </c>
-      <c r="C48" s="30" t="inlineStr">
-        <is>
-          <t>Ras Al Khaimah → Al Hamra Marina &amp; Royal Yacht Club RAK</t>
-        </is>
-      </c>
-      <c r="D48" s="31" t="n">
-        <v>13.6</v>
-      </c>
-      <c r="E48" s="26" t="n">
-        <v>35</v>
-      </c>
-      <c r="F48" s="32" t="inlineStr">
-        <is>
-          <t>T3</t>
-        </is>
-      </c>
-      <c r="G48" s="32" t="inlineStr">
-        <is>
-          <t>med-low</t>
-        </is>
-      </c>
-      <c r="H48" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="I48" s="33">
-        <f>60*D48/cruise_kt</f>
-        <v/>
-      </c>
-      <c r="J48" s="33">
-        <f>I48+turn_min+dwell_min</f>
-        <v/>
-      </c>
-      <c r="K48" s="34">
-        <f>MIN(10,FLOOR(60*service_hr/J48,1))</f>
-        <v/>
-      </c>
-      <c r="L48" s="34">
-        <f>ROUND(365*mech_uptime*H48,0)</f>
-        <v/>
-      </c>
-      <c r="M48" s="35">
-        <f>mech_uptime</f>
-        <v/>
-      </c>
-      <c r="N48" s="35">
-        <f>revleg_sel</f>
-        <v/>
-      </c>
-      <c r="O48" s="34">
-        <f>ROUND(K48*L48*revleg_sel,0)</f>
-        <v/>
-      </c>
-      <c r="P48" s="36">
-        <f>load_sel</f>
-        <v/>
-      </c>
-      <c r="Q48" s="36">
-        <f>pax_cap*P48</f>
-        <v/>
-      </c>
-      <c r="R48" s="34">
-        <f>Q48*O48</f>
-        <v/>
-      </c>
-      <c r="S48" s="37">
-        <f>E48*discount</f>
-        <v/>
-      </c>
-      <c r="T48" s="38">
-        <f>S48*R48</f>
-        <v/>
-      </c>
-      <c r="U48" s="38">
-        <f>(battery/range_nm)*D48*O48*VLOOKUP(B48,country_opex,3,FALSE)</f>
-        <v/>
-      </c>
-      <c r="V48" s="38">
-        <f>VLOOKUP(B48,country_opex,2,FALSE)*crew_factor</f>
-        <v/>
-      </c>
-      <c r="W48" s="38">
-        <f>VLOOKUP(B48,country_opex,5,FALSE)</f>
-        <v/>
-      </c>
-      <c r="X48" s="38">
-        <f>maint</f>
-        <v/>
-      </c>
-      <c r="Y48" s="38">
-        <f>VLOOKUP(B48,country_opex,7,FALSE)*ins_pct</f>
-        <v/>
-      </c>
-      <c r="Z48" s="38">
-        <f>charge_berth</f>
-        <v/>
-      </c>
-      <c r="AA48" s="38">
-        <f>U48+V48+W48+X48+Y48+Z48</f>
-        <v/>
-      </c>
-      <c r="AB48" s="38">
-        <f>VLOOKUP(B48,country_opex,7,FALSE)/dep_years</f>
-        <v/>
-      </c>
-      <c r="AC48" s="38">
-        <f>T48-AA48</f>
-        <v/>
-      </c>
-      <c r="AD48" s="35">
-        <f>IF(T48=0,"",AC48/T48)</f>
-        <v/>
-      </c>
-      <c r="AE48" s="36">
-        <f>IF(AC48&lt;=0,"",VLOOKUP(B48,country_opex,7,FALSE)/AC48)</f>
-        <v/>
-      </c>
-      <c r="AF48" s="33">
-        <f>((D48*O48/diesel_nmpg)*diesel_co2pg-(battery/range_nm)*D48*O48*VLOOKUP(B48,country_opex,4,FALSE))/1000</f>
-        <v/>
-      </c>
-      <c r="AG48" s="31" t="n">
-        <v>4285</v>
-      </c>
-      <c r="AH48" s="32" t="inlineStr">
-        <is>
-          <t>T3</t>
-        </is>
-      </c>
-      <c r="AI48" s="32" t="inlineStr">
-        <is>
-          <t>med-low</t>
-        </is>
-      </c>
-      <c r="AJ48" s="39" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="AK48" s="34">
-        <f>IF(AG48="","",AG48*AJ48)</f>
-        <v/>
-      </c>
-      <c r="AL48" s="34">
-        <f>IF(OR(AG48="",R48=0),"",MIN(IF(AS48="",9.9E+99,AS48),FLOOR(AK48/R48,1)))</f>
-        <v/>
-      </c>
-      <c r="AM48" s="38">
-        <f>IF(AL48="","",AL48*T48)</f>
-        <v/>
-      </c>
-      <c r="AN48" s="36">
-        <f>IF(OR(AG48="",R48=0),"",MIN(IF(AS48="",9.9E+99,AS48),AK48/R48))</f>
-        <v/>
-      </c>
-      <c r="AO48" s="38">
-        <f>IF(AN48="","",AN48*T48)</f>
-        <v/>
-      </c>
-      <c r="AP48" s="40" t="n"/>
-      <c r="AQ48" s="41" t="n"/>
-      <c r="AR48" s="41" t="n"/>
-      <c r="AS48" s="42" t="n"/>
-      <c r="AT48" s="43">
-        <f>IF(((S48*pax_cap*load_thin*ROUND(K48*L48*revleg_thin,0))-(((battery/range_nm)*D48*ROUND(K48*L48*revleg_thin,0)*VLOOKUP(B48,country_opex,3,FALSE))+V48+W48+X48+Y48+Z48))&lt;=0,"",VLOOKUP(B48,country_opex,7,FALSE)/((S48*pax_cap*load_thin*ROUND(K48*L48*revleg_thin,0))-(((battery/range_nm)*D48*ROUND(K48*L48*revleg_thin,0)*VLOOKUP(B48,country_opex,3,FALSE))+V48+W48+X48+Y48+Z48)))</f>
-        <v/>
-      </c>
-      <c r="AU48" s="43">
-        <f>IF(((S48*pax_cap*load_mid*ROUND(K48*L48*revleg_mid,0))-(((battery/range_nm)*D48*ROUND(K48*L48*revleg_mid,0)*VLOOKUP(B48,country_opex,3,FALSE))+V48+W48+X48+Y48+Z48))&lt;=0,"",VLOOKUP(B48,country_opex,7,FALSE)/((S48*pax_cap*load_mid*ROUND(K48*L48*revleg_mid,0))-(((battery/range_nm)*D48*ROUND(K48*L48*revleg_mid,0)*VLOOKUP(B48,country_opex,3,FALSE))+V48+W48+X48+Y48+Z48)))</f>
-        <v/>
-      </c>
-      <c r="AV48" s="43">
-        <f>IF(((S48*pax_cap*load_full*ROUND(K48*L48*revleg_full,0))-(((battery/range_nm)*D48*ROUND(K48*L48*revleg_full,0)*VLOOKUP(B48,country_opex,3,FALSE))+V48+W48+X48+Y48+Z48))&lt;=0,"",VLOOKUP(B48,country_opex,7,FALSE)/((S48*pax_cap*load_full*ROUND(K48*L48*revleg_full,0))-(((battery/range_nm)*D48*ROUND(K48*L48*revleg_full,0)*VLOOKUP(B48,country_opex,3,FALSE))+V48+W48+X48+Y48+Z48)))</f>
-        <v/>
-      </c>
-      <c r="AW48" s="44" t="n"/>
-      <c r="AX48" s="44" t="n"/>
-    </row>
-    <row r="49">
-      <c r="A49" s="29" t="inlineStr">
-        <is>
-          <t>Gulf Authority Rakta</t>
-        </is>
-      </c>
-      <c r="B49" s="29" t="inlineStr">
-        <is>
-          <t>United Arab Emirates</t>
-        </is>
-      </c>
-      <c r="C49" s="30" t="inlineStr">
-        <is>
-          <t>Ras Al Khaimah → Al Marjan Island public arrival marina</t>
-        </is>
-      </c>
-      <c r="D49" s="31" t="n">
-        <v>16</v>
-      </c>
-      <c r="E49" s="26" t="n">
-        <v>35</v>
-      </c>
-      <c r="F49" s="32" t="inlineStr">
-        <is>
-          <t>T3</t>
-        </is>
-      </c>
-      <c r="G49" s="32" t="inlineStr">
-        <is>
-          <t>med-low</t>
-        </is>
-      </c>
-      <c r="H49" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="I49" s="33">
-        <f>60*D49/cruise_kt</f>
-        <v/>
-      </c>
-      <c r="J49" s="33">
-        <f>I49+turn_min+dwell_min</f>
-        <v/>
-      </c>
-      <c r="K49" s="34">
-        <f>MIN(10,FLOOR(60*service_hr/J49,1))</f>
-        <v/>
-      </c>
-      <c r="L49" s="34">
-        <f>ROUND(365*mech_uptime*H49,0)</f>
-        <v/>
-      </c>
-      <c r="M49" s="35">
-        <f>mech_uptime</f>
-        <v/>
-      </c>
-      <c r="N49" s="35">
-        <f>revleg_sel</f>
-        <v/>
-      </c>
-      <c r="O49" s="34">
-        <f>ROUND(K49*L49*revleg_sel,0)</f>
-        <v/>
-      </c>
-      <c r="P49" s="36">
-        <f>load_sel</f>
-        <v/>
-      </c>
-      <c r="Q49" s="36">
-        <f>pax_cap*P49</f>
-        <v/>
-      </c>
-      <c r="R49" s="34">
-        <f>Q49*O49</f>
-        <v/>
-      </c>
-      <c r="S49" s="37">
-        <f>E49*discount</f>
-        <v/>
-      </c>
-      <c r="T49" s="38">
-        <f>S49*R49</f>
-        <v/>
-      </c>
-      <c r="U49" s="38">
-        <f>(battery/range_nm)*D49*O49*VLOOKUP(B49,country_opex,3,FALSE)</f>
-        <v/>
-      </c>
-      <c r="V49" s="38">
-        <f>VLOOKUP(B49,country_opex,2,FALSE)*crew_factor</f>
-        <v/>
-      </c>
-      <c r="W49" s="38">
-        <f>VLOOKUP(B49,country_opex,5,FALSE)</f>
-        <v/>
-      </c>
-      <c r="X49" s="38">
-        <f>maint</f>
-        <v/>
-      </c>
-      <c r="Y49" s="38">
-        <f>VLOOKUP(B49,country_opex,7,FALSE)*ins_pct</f>
-        <v/>
-      </c>
-      <c r="Z49" s="38">
-        <f>charge_berth</f>
-        <v/>
-      </c>
-      <c r="AA49" s="38">
-        <f>U49+V49+W49+X49+Y49+Z49</f>
-        <v/>
-      </c>
-      <c r="AB49" s="38">
-        <f>VLOOKUP(B49,country_opex,7,FALSE)/dep_years</f>
-        <v/>
-      </c>
-      <c r="AC49" s="38">
-        <f>T49-AA49</f>
-        <v/>
-      </c>
-      <c r="AD49" s="35">
-        <f>IF(T49=0,"",AC49/T49)</f>
-        <v/>
-      </c>
-      <c r="AE49" s="36">
-        <f>IF(AC49&lt;=0,"",VLOOKUP(B49,country_opex,7,FALSE)/AC49)</f>
-        <v/>
-      </c>
-      <c r="AF49" s="33">
-        <f>((D49*O49/diesel_nmpg)*diesel_co2pg-(battery/range_nm)*D49*O49*VLOOKUP(B49,country_opex,4,FALSE))/1000</f>
-        <v/>
-      </c>
-      <c r="AG49" s="31" t="n">
-        <v>4285</v>
-      </c>
-      <c r="AH49" s="32" t="inlineStr">
-        <is>
-          <t>T3</t>
-        </is>
-      </c>
-      <c r="AI49" s="32" t="inlineStr">
-        <is>
-          <t>med-low</t>
-        </is>
-      </c>
-      <c r="AJ49" s="39" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="AK49" s="34">
-        <f>IF(AG49="","",AG49*AJ49)</f>
-        <v/>
-      </c>
-      <c r="AL49" s="34">
-        <f>IF(OR(AG49="",R49=0),"",MIN(IF(AS49="",9.9E+99,AS49),FLOOR(AK49/R49,1)))</f>
-        <v/>
-      </c>
-      <c r="AM49" s="38">
-        <f>IF(AL49="","",AL49*T49)</f>
-        <v/>
-      </c>
-      <c r="AN49" s="36">
-        <f>IF(OR(AG49="",R49=0),"",MIN(IF(AS49="",9.9E+99,AS49),AK49/R49))</f>
-        <v/>
-      </c>
-      <c r="AO49" s="38">
-        <f>IF(AN49="","",AN49*T49)</f>
-        <v/>
-      </c>
-      <c r="AP49" s="40" t="n"/>
-      <c r="AQ49" s="41" t="n"/>
-      <c r="AR49" s="41" t="n"/>
-      <c r="AS49" s="42" t="n"/>
-      <c r="AT49" s="43">
-        <f>IF(((S49*pax_cap*load_thin*ROUND(K49*L49*revleg_thin,0))-(((battery/range_nm)*D49*ROUND(K49*L49*revleg_thin,0)*VLOOKUP(B49,country_opex,3,FALSE))+V49+W49+X49+Y49+Z49))&lt;=0,"",VLOOKUP(B49,country_opex,7,FALSE)/((S49*pax_cap*load_thin*ROUND(K49*L49*revleg_thin,0))-(((battery/range_nm)*D49*ROUND(K49*L49*revleg_thin,0)*VLOOKUP(B49,country_opex,3,FALSE))+V49+W49+X49+Y49+Z49)))</f>
-        <v/>
-      </c>
-      <c r="AU49" s="43">
-        <f>IF(((S49*pax_cap*load_mid*ROUND(K49*L49*revleg_mid,0))-(((battery/range_nm)*D49*ROUND(K49*L49*revleg_mid,0)*VLOOKUP(B49,country_opex,3,FALSE))+V49+W49+X49+Y49+Z49))&lt;=0,"",VLOOKUP(B49,country_opex,7,FALSE)/((S49*pax_cap*load_mid*ROUND(K49*L49*revleg_mid,0))-(((battery/range_nm)*D49*ROUND(K49*L49*revleg_mid,0)*VLOOKUP(B49,country_opex,3,FALSE))+V49+W49+X49+Y49+Z49)))</f>
-        <v/>
-      </c>
-      <c r="AV49" s="43">
-        <f>IF(((S49*pax_cap*load_full*ROUND(K49*L49*revleg_full,0))-(((battery/range_nm)*D49*ROUND(K49*L49*revleg_full,0)*VLOOKUP(B49,country_opex,3,FALSE))+V49+W49+X49+Y49+Z49))&lt;=0,"",VLOOKUP(B49,country_opex,7,FALSE)/((S49*pax_cap*load_full*ROUND(K49*L49*revleg_full,0))-(((battery/range_nm)*D49*ROUND(K49*L49*revleg_full,0)*VLOOKUP(B49,country_opex,3,FALSE))+V49+W49+X49+Y49+Z49)))</f>
-        <v/>
-      </c>
-      <c r="AW49" s="44" t="n"/>
-      <c r="AX49" s="44" t="n"/>
-    </row>
-    <row r="50">
-      <c r="A50" s="29" t="inlineStr">
-        <is>
-          <t>Gulf Authority Rakta</t>
-        </is>
-      </c>
-      <c r="B50" s="29" t="inlineStr">
-        <is>
-          <t>United Arab Emirates</t>
-        </is>
-      </c>
-      <c r="C50" s="30" t="inlineStr">
-        <is>
-          <t>Ras Al Khaimah → UAQ Marine Club</t>
-        </is>
-      </c>
-      <c r="D50" s="31" t="n">
-        <v>26.6</v>
-      </c>
-      <c r="E50" s="26" t="n">
-        <v>35</v>
-      </c>
-      <c r="F50" s="32" t="inlineStr">
-        <is>
-          <t>T3</t>
-        </is>
-      </c>
-      <c r="G50" s="32" t="inlineStr">
-        <is>
-          <t>med-low</t>
-        </is>
-      </c>
-      <c r="H50" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="I50" s="33">
-        <f>60*D50/cruise_kt</f>
-        <v/>
-      </c>
-      <c r="J50" s="33">
-        <f>I50+turn_min+dwell_min</f>
-        <v/>
-      </c>
-      <c r="K50" s="34">
-        <f>MIN(10,FLOOR(60*service_hr/J50,1))</f>
-        <v/>
-      </c>
-      <c r="L50" s="34">
-        <f>ROUND(365*mech_uptime*H50,0)</f>
-        <v/>
-      </c>
-      <c r="M50" s="35">
-        <f>mech_uptime</f>
-        <v/>
-      </c>
-      <c r="N50" s="35">
-        <f>revleg_sel</f>
-        <v/>
-      </c>
-      <c r="O50" s="34">
-        <f>ROUND(K50*L50*revleg_sel,0)</f>
-        <v/>
-      </c>
-      <c r="P50" s="36">
-        <f>load_sel</f>
-        <v/>
-      </c>
-      <c r="Q50" s="36">
-        <f>pax_cap*P50</f>
-        <v/>
-      </c>
-      <c r="R50" s="34">
-        <f>Q50*O50</f>
-        <v/>
-      </c>
-      <c r="S50" s="37">
-        <f>E50*discount</f>
-        <v/>
-      </c>
-      <c r="T50" s="38">
-        <f>S50*R50</f>
-        <v/>
-      </c>
-      <c r="U50" s="38">
-        <f>(battery/range_nm)*D50*O50*VLOOKUP(B50,country_opex,3,FALSE)</f>
-        <v/>
-      </c>
-      <c r="V50" s="38">
-        <f>VLOOKUP(B50,country_opex,2,FALSE)*crew_factor</f>
-        <v/>
-      </c>
-      <c r="W50" s="38">
-        <f>VLOOKUP(B50,country_opex,5,FALSE)</f>
-        <v/>
-      </c>
-      <c r="X50" s="38">
-        <f>maint</f>
-        <v/>
-      </c>
-      <c r="Y50" s="38">
-        <f>VLOOKUP(B50,country_opex,7,FALSE)*ins_pct</f>
-        <v/>
-      </c>
-      <c r="Z50" s="38">
-        <f>charge_berth</f>
-        <v/>
-      </c>
-      <c r="AA50" s="38">
-        <f>U50+V50+W50+X50+Y50+Z50</f>
-        <v/>
-      </c>
-      <c r="AB50" s="38">
-        <f>VLOOKUP(B50,country_opex,7,FALSE)/dep_years</f>
-        <v/>
-      </c>
-      <c r="AC50" s="38">
-        <f>T50-AA50</f>
-        <v/>
-      </c>
-      <c r="AD50" s="35">
-        <f>IF(T50=0,"",AC50/T50)</f>
-        <v/>
-      </c>
-      <c r="AE50" s="36">
-        <f>IF(AC50&lt;=0,"",VLOOKUP(B50,country_opex,7,FALSE)/AC50)</f>
-        <v/>
-      </c>
-      <c r="AF50" s="33">
-        <f>((D50*O50/diesel_nmpg)*diesel_co2pg-(battery/range_nm)*D50*O50*VLOOKUP(B50,country_opex,4,FALSE))/1000</f>
-        <v/>
-      </c>
-      <c r="AG50" s="31" t="n">
-        <v>4285</v>
-      </c>
-      <c r="AH50" s="32" t="inlineStr">
-        <is>
-          <t>T3</t>
-        </is>
-      </c>
-      <c r="AI50" s="32" t="inlineStr">
-        <is>
-          <t>med-low</t>
-        </is>
-      </c>
-      <c r="AJ50" s="39" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="AK50" s="34">
-        <f>IF(AG50="","",AG50*AJ50)</f>
-        <v/>
-      </c>
-      <c r="AL50" s="34">
-        <f>IF(OR(AG50="",R50=0),"",MIN(IF(AS50="",9.9E+99,AS50),FLOOR(AK50/R50,1)))</f>
-        <v/>
-      </c>
-      <c r="AM50" s="38">
-        <f>IF(AL50="","",AL50*T50)</f>
-        <v/>
-      </c>
-      <c r="AN50" s="36">
-        <f>IF(OR(AG50="",R50=0),"",MIN(IF(AS50="",9.9E+99,AS50),AK50/R50))</f>
-        <v/>
-      </c>
-      <c r="AO50" s="38">
-        <f>IF(AN50="","",AN50*T50)</f>
-        <v/>
-      </c>
-      <c r="AP50" s="40" t="n"/>
-      <c r="AQ50" s="41" t="n"/>
-      <c r="AR50" s="41" t="n"/>
-      <c r="AS50" s="42" t="n"/>
-      <c r="AT50" s="43">
-        <f>IF(((S50*pax_cap*load_thin*ROUND(K50*L50*revleg_thin,0))-(((battery/range_nm)*D50*ROUND(K50*L50*revleg_thin,0)*VLOOKUP(B50,country_opex,3,FALSE))+V50+W50+X50+Y50+Z50))&lt;=0,"",VLOOKUP(B50,country_opex,7,FALSE)/((S50*pax_cap*load_thin*ROUND(K50*L50*revleg_thin,0))-(((battery/range_nm)*D50*ROUND(K50*L50*revleg_thin,0)*VLOOKUP(B50,country_opex,3,FALSE))+V50+W50+X50+Y50+Z50)))</f>
-        <v/>
-      </c>
-      <c r="AU50" s="43">
-        <f>IF(((S50*pax_cap*load_mid*ROUND(K50*L50*revleg_mid,0))-(((battery/range_nm)*D50*ROUND(K50*L50*revleg_mid,0)*VLOOKUP(B50,country_opex,3,FALSE))+V50+W50+X50+Y50+Z50))&lt;=0,"",VLOOKUP(B50,country_opex,7,FALSE)/((S50*pax_cap*load_mid*ROUND(K50*L50*revleg_mid,0))-(((battery/range_nm)*D50*ROUND(K50*L50*revleg_mid,0)*VLOOKUP(B50,country_opex,3,FALSE))+V50+W50+X50+Y50+Z50)))</f>
-        <v/>
-      </c>
-      <c r="AV50" s="43">
-        <f>IF(((S50*pax_cap*load_full*ROUND(K50*L50*revleg_full,0))-(((battery/range_nm)*D50*ROUND(K50*L50*revleg_full,0)*VLOOKUP(B50,country_opex,3,FALSE))+V50+W50+X50+Y50+Z50))&lt;=0,"",VLOOKUP(B50,country_opex,7,FALSE)/((S50*pax_cap*load_full*ROUND(K50*L50*revleg_full,0))-(((battery/range_nm)*D50*ROUND(K50*L50*revleg_full,0)*VLOOKUP(B50,country_opex,3,FALSE))+V50+W50+X50+Y50+Z50)))</f>
-        <v/>
-      </c>
-      <c r="AW50" s="44" t="n"/>
-      <c r="AX50" s="44" t="n"/>
+      <c r="B50" s="13" t="inlineStr">
+        <is>
+          <t>network_sum / ceil</t>
+        </is>
+      </c>
+      <c r="C50" s="23">
+        <f>SUMIFS(AN4:AN45,A4:A45,"Gulf Authority Rakta",AP4:AP45,"=",AQ4:AQ45,"=",AR4:AR45,"=")</f>
+        <v/>
+      </c>
+      <c r="D50" s="49">
+        <f>IF(C50=0,0,CEILING(C50,1))</f>
+        <v/>
+      </c>
+      <c r="E50" s="50">
+        <f>SUMIFS(AO4:AO45,A4:A45,"Gulf Authority Rakta",AP4:AP45,"=",AQ4:AQ45,"=",AR4:AR45,"=")</f>
+        <v/>
+      </c>
     </row>
     <row r="51">
-      <c r="A51" s="29" t="inlineStr">
-        <is>
-          <t>Gulf Authority Rakta</t>
-        </is>
-      </c>
-      <c r="B51" s="29" t="inlineStr">
-        <is>
-          <t>United Arab Emirates</t>
-        </is>
-      </c>
-      <c r="C51" s="30" t="inlineStr">
-        <is>
-          <t>Ras Al Khaimah → Ajman Marina</t>
-        </is>
-      </c>
-      <c r="D51" s="31" t="n">
-        <v>39</v>
-      </c>
-      <c r="E51" s="26" t="n">
-        <v>35</v>
-      </c>
-      <c r="F51" s="32" t="inlineStr">
-        <is>
-          <t>T3</t>
-        </is>
-      </c>
-      <c r="G51" s="32" t="inlineStr">
-        <is>
-          <t>med-low</t>
-        </is>
-      </c>
-      <c r="H51" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="I51" s="33">
-        <f>60*D51/cruise_kt</f>
-        <v/>
-      </c>
-      <c r="J51" s="33">
-        <f>I51+turn_min+dwell_min</f>
-        <v/>
-      </c>
-      <c r="K51" s="34">
-        <f>MIN(10,FLOOR(60*service_hr/J51,1))</f>
-        <v/>
-      </c>
-      <c r="L51" s="34">
-        <f>ROUND(365*mech_uptime*H51,0)</f>
-        <v/>
-      </c>
-      <c r="M51" s="35">
-        <f>mech_uptime</f>
-        <v/>
-      </c>
-      <c r="N51" s="35">
-        <f>revleg_sel</f>
-        <v/>
-      </c>
-      <c r="O51" s="34">
-        <f>ROUND(K51*L51*revleg_sel,0)</f>
-        <v/>
-      </c>
-      <c r="P51" s="36">
-        <f>load_sel</f>
-        <v/>
-      </c>
-      <c r="Q51" s="36">
-        <f>pax_cap*P51</f>
-        <v/>
-      </c>
-      <c r="R51" s="34">
-        <f>Q51*O51</f>
-        <v/>
-      </c>
-      <c r="S51" s="37">
-        <f>E51*discount</f>
-        <v/>
-      </c>
-      <c r="T51" s="38">
-        <f>S51*R51</f>
-        <v/>
-      </c>
-      <c r="U51" s="38">
-        <f>(battery/range_nm)*D51*O51*VLOOKUP(B51,country_opex,3,FALSE)</f>
-        <v/>
-      </c>
-      <c r="V51" s="38">
-        <f>VLOOKUP(B51,country_opex,2,FALSE)*crew_factor</f>
-        <v/>
-      </c>
-      <c r="W51" s="38">
-        <f>VLOOKUP(B51,country_opex,5,FALSE)</f>
-        <v/>
-      </c>
-      <c r="X51" s="38">
-        <f>maint</f>
-        <v/>
-      </c>
-      <c r="Y51" s="38">
-        <f>VLOOKUP(B51,country_opex,7,FALSE)*ins_pct</f>
-        <v/>
-      </c>
-      <c r="Z51" s="38">
-        <f>charge_berth</f>
-        <v/>
-      </c>
-      <c r="AA51" s="38">
-        <f>U51+V51+W51+X51+Y51+Z51</f>
-        <v/>
-      </c>
-      <c r="AB51" s="38">
-        <f>VLOOKUP(B51,country_opex,7,FALSE)/dep_years</f>
-        <v/>
-      </c>
-      <c r="AC51" s="38">
-        <f>T51-AA51</f>
-        <v/>
-      </c>
-      <c r="AD51" s="35">
-        <f>IF(T51=0,"",AC51/T51)</f>
-        <v/>
-      </c>
-      <c r="AE51" s="36">
-        <f>IF(AC51&lt;=0,"",VLOOKUP(B51,country_opex,7,FALSE)/AC51)</f>
-        <v/>
-      </c>
-      <c r="AF51" s="33">
-        <f>((D51*O51/diesel_nmpg)*diesel_co2pg-(battery/range_nm)*D51*O51*VLOOKUP(B51,country_opex,4,FALSE))/1000</f>
-        <v/>
-      </c>
-      <c r="AG51" s="31" t="n">
-        <v>4285</v>
-      </c>
-      <c r="AH51" s="32" t="inlineStr">
-        <is>
-          <t>T3</t>
-        </is>
-      </c>
-      <c r="AI51" s="32" t="inlineStr">
-        <is>
-          <t>med-low</t>
-        </is>
-      </c>
-      <c r="AJ51" s="39" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="AK51" s="34">
-        <f>IF(AG51="","",AG51*AJ51)</f>
-        <v/>
-      </c>
-      <c r="AL51" s="34">
-        <f>IF(OR(AG51="",R51=0),"",MIN(IF(AS51="",9.9E+99,AS51),FLOOR(AK51/R51,1)))</f>
-        <v/>
-      </c>
-      <c r="AM51" s="38">
-        <f>IF(AL51="","",AL51*T51)</f>
-        <v/>
-      </c>
-      <c r="AN51" s="36">
-        <f>IF(OR(AG51="",R51=0),"",MIN(IF(AS51="",9.9E+99,AS51),AK51/R51))</f>
-        <v/>
-      </c>
-      <c r="AO51" s="38">
-        <f>IF(AN51="","",AN51*T51)</f>
-        <v/>
-      </c>
-      <c r="AP51" s="40" t="n"/>
-      <c r="AQ51" s="41" t="n"/>
-      <c r="AR51" s="41" t="n"/>
-      <c r="AS51" s="42" t="n"/>
-      <c r="AT51" s="43">
-        <f>IF(((S51*pax_cap*load_thin*ROUND(K51*L51*revleg_thin,0))-(((battery/range_nm)*D51*ROUND(K51*L51*revleg_thin,0)*VLOOKUP(B51,country_opex,3,FALSE))+V51+W51+X51+Y51+Z51))&lt;=0,"",VLOOKUP(B51,country_opex,7,FALSE)/((S51*pax_cap*load_thin*ROUND(K51*L51*revleg_thin,0))-(((battery/range_nm)*D51*ROUND(K51*L51*revleg_thin,0)*VLOOKUP(B51,country_opex,3,FALSE))+V51+W51+X51+Y51+Z51)))</f>
-        <v/>
-      </c>
-      <c r="AU51" s="43">
-        <f>IF(((S51*pax_cap*load_mid*ROUND(K51*L51*revleg_mid,0))-(((battery/range_nm)*D51*ROUND(K51*L51*revleg_mid,0)*VLOOKUP(B51,country_opex,3,FALSE))+V51+W51+X51+Y51+Z51))&lt;=0,"",VLOOKUP(B51,country_opex,7,FALSE)/((S51*pax_cap*load_mid*ROUND(K51*L51*revleg_mid,0))-(((battery/range_nm)*D51*ROUND(K51*L51*revleg_mid,0)*VLOOKUP(B51,country_opex,3,FALSE))+V51+W51+X51+Y51+Z51)))</f>
-        <v/>
-      </c>
-      <c r="AV51" s="43">
-        <f>IF(((S51*pax_cap*load_full*ROUND(K51*L51*revleg_full,0))-(((battery/range_nm)*D51*ROUND(K51*L51*revleg_full,0)*VLOOKUP(B51,country_opex,3,FALSE))+V51+W51+X51+Y51+Z51))&lt;=0,"",VLOOKUP(B51,country_opex,7,FALSE)/((S51*pax_cap*load_full*ROUND(K51*L51*revleg_full,0))-(((battery/range_nm)*D51*ROUND(K51*L51*revleg_full,0)*VLOOKUP(B51,country_opex,3,FALSE))+V51+W51+X51+Y51+Z51)))</f>
-        <v/>
-      </c>
-      <c r="AW51" s="44" t="n"/>
-      <c r="AX51" s="44" t="n"/>
-    </row>
-    <row r="52">
-      <c r="A52" s="29" t="inlineStr">
-        <is>
-          <t>Gulf Authority Rakta</t>
-        </is>
-      </c>
-      <c r="B52" s="29" t="inlineStr">
-        <is>
-          <t>United Arab Emirates</t>
-        </is>
-      </c>
-      <c r="C52" s="30" t="inlineStr">
-        <is>
-          <t>Dubai Harbour Marina → Wynn Al Marjan Island arrival lagoon</t>
-        </is>
-      </c>
-      <c r="D52" s="31" t="n">
-        <v>49.8</v>
-      </c>
-      <c r="E52" s="26" t="n">
-        <v>35</v>
-      </c>
-      <c r="F52" s="32" t="inlineStr">
-        <is>
-          <t>T3</t>
-        </is>
-      </c>
-      <c r="G52" s="32" t="inlineStr">
-        <is>
-          <t>med-low</t>
-        </is>
-      </c>
-      <c r="H52" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="I52" s="33">
-        <f>60*D52/cruise_kt</f>
-        <v/>
-      </c>
-      <c r="J52" s="33">
-        <f>I52+turn_min+dwell_min</f>
-        <v/>
-      </c>
-      <c r="K52" s="34">
-        <f>MIN(10,FLOOR(60*service_hr/J52,1))</f>
-        <v/>
-      </c>
-      <c r="L52" s="34">
-        <f>ROUND(365*mech_uptime*H52,0)</f>
-        <v/>
-      </c>
-      <c r="M52" s="35">
-        <f>mech_uptime</f>
-        <v/>
-      </c>
-      <c r="N52" s="35">
-        <f>revleg_sel</f>
-        <v/>
-      </c>
-      <c r="O52" s="34">
-        <f>ROUND(K52*L52*revleg_sel,0)</f>
-        <v/>
-      </c>
-      <c r="P52" s="36">
-        <f>load_sel</f>
-        <v/>
-      </c>
-      <c r="Q52" s="36">
-        <f>pax_cap*P52</f>
-        <v/>
-      </c>
-      <c r="R52" s="34">
-        <f>Q52*O52</f>
-        <v/>
-      </c>
-      <c r="S52" s="37">
-        <f>E52*discount</f>
-        <v/>
-      </c>
-      <c r="T52" s="38">
-        <f>S52*R52</f>
-        <v/>
-      </c>
-      <c r="U52" s="38">
-        <f>(battery/range_nm)*D52*O52*VLOOKUP(B52,country_opex,3,FALSE)</f>
-        <v/>
-      </c>
-      <c r="V52" s="38">
-        <f>VLOOKUP(B52,country_opex,2,FALSE)*crew_factor</f>
-        <v/>
-      </c>
-      <c r="W52" s="38">
-        <f>VLOOKUP(B52,country_opex,5,FALSE)</f>
-        <v/>
-      </c>
-      <c r="X52" s="38">
-        <f>maint</f>
-        <v/>
-      </c>
-      <c r="Y52" s="38">
-        <f>VLOOKUP(B52,country_opex,7,FALSE)*ins_pct</f>
-        <v/>
-      </c>
-      <c r="Z52" s="38">
-        <f>charge_berth</f>
-        <v/>
-      </c>
-      <c r="AA52" s="38">
-        <f>U52+V52+W52+X52+Y52+Z52</f>
-        <v/>
-      </c>
-      <c r="AB52" s="38">
-        <f>VLOOKUP(B52,country_opex,7,FALSE)/dep_years</f>
-        <v/>
-      </c>
-      <c r="AC52" s="38">
-        <f>T52-AA52</f>
-        <v/>
-      </c>
-      <c r="AD52" s="35">
-        <f>IF(T52=0,"",AC52/T52)</f>
-        <v/>
-      </c>
-      <c r="AE52" s="36">
-        <f>IF(AC52&lt;=0,"",VLOOKUP(B52,country_opex,7,FALSE)/AC52)</f>
-        <v/>
-      </c>
-      <c r="AF52" s="33">
-        <f>((D52*O52/diesel_nmpg)*diesel_co2pg-(battery/range_nm)*D52*O52*VLOOKUP(B52,country_opex,4,FALSE))/1000</f>
-        <v/>
-      </c>
-      <c r="AG52" s="31" t="n">
-        <v>4285</v>
-      </c>
-      <c r="AH52" s="32" t="inlineStr">
-        <is>
-          <t>T3</t>
-        </is>
-      </c>
-      <c r="AI52" s="32" t="inlineStr">
-        <is>
-          <t>med-low</t>
-        </is>
-      </c>
-      <c r="AJ52" s="39" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="AK52" s="34">
-        <f>IF(AG52="","",AG52*AJ52)</f>
-        <v/>
-      </c>
-      <c r="AL52" s="34">
-        <f>IF(OR(AG52="",R52=0),"",MIN(IF(AS52="",9.9E+99,AS52),FLOOR(AK52/R52,1)))</f>
-        <v/>
-      </c>
-      <c r="AM52" s="38">
-        <f>IF(AL52="","",AL52*T52)</f>
-        <v/>
-      </c>
-      <c r="AN52" s="36">
-        <f>IF(OR(AG52="",R52=0),"",MIN(IF(AS52="",9.9E+99,AS52),AK52/R52))</f>
-        <v/>
-      </c>
-      <c r="AO52" s="38">
-        <f>IF(AN52="","",AN52*T52)</f>
-        <v/>
-      </c>
-      <c r="AP52" s="40" t="n"/>
-      <c r="AQ52" s="41" t="n"/>
-      <c r="AR52" s="41" t="n"/>
-      <c r="AS52" s="42" t="n"/>
-      <c r="AT52" s="43">
-        <f>IF(((S52*pax_cap*load_thin*ROUND(K52*L52*revleg_thin,0))-(((battery/range_nm)*D52*ROUND(K52*L52*revleg_thin,0)*VLOOKUP(B52,country_opex,3,FALSE))+V52+W52+X52+Y52+Z52))&lt;=0,"",VLOOKUP(B52,country_opex,7,FALSE)/((S52*pax_cap*load_thin*ROUND(K52*L52*revleg_thin,0))-(((battery/range_nm)*D52*ROUND(K52*L52*revleg_thin,0)*VLOOKUP(B52,country_opex,3,FALSE))+V52+W52+X52+Y52+Z52)))</f>
-        <v/>
-      </c>
-      <c r="AU52" s="43">
-        <f>IF(((S52*pax_cap*load_mid*ROUND(K52*L52*revleg_mid,0))-(((battery/range_nm)*D52*ROUND(K52*L52*revleg_mid,0)*VLOOKUP(B52,country_opex,3,FALSE))+V52+W52+X52+Y52+Z52))&lt;=0,"",VLOOKUP(B52,country_opex,7,FALSE)/((S52*pax_cap*load_mid*ROUND(K52*L52*revleg_mid,0))-(((battery/range_nm)*D52*ROUND(K52*L52*revleg_mid,0)*VLOOKUP(B52,country_opex,3,FALSE))+V52+W52+X52+Y52+Z52)))</f>
-        <v/>
-      </c>
-      <c r="AV52" s="43">
-        <f>IF(((S52*pax_cap*load_full*ROUND(K52*L52*revleg_full,0))-(((battery/range_nm)*D52*ROUND(K52*L52*revleg_full,0)*VLOOKUP(B52,country_opex,3,FALSE))+V52+W52+X52+Y52+Z52))&lt;=0,"",VLOOKUP(B52,country_opex,7,FALSE)/((S52*pax_cap*load_full*ROUND(K52*L52*revleg_full,0))-(((battery/range_nm)*D52*ROUND(K52*L52*revleg_full,0)*VLOOKUP(B52,country_opex,3,FALSE))+V52+W52+X52+Y52+Z52)))</f>
-        <v/>
-      </c>
-      <c r="AW52" s="44" t="n"/>
-      <c r="AX52" s="44" t="n"/>
+      <c r="A51" s="45" t="inlineStr">
+        <is>
+          <t>GROUNDED FLOOR (PUBLISHED)</t>
+        </is>
+      </c>
+      <c r="D51" s="48">
+        <f>SUM(D50:D50)</f>
+        <v/>
+      </c>
+      <c r="E51" s="46">
+        <f>SUM(E50:E50)</f>
+        <v/>
+      </c>
     </row>
     <row r="53">
-      <c r="A53" s="29" t="inlineStr">
-        <is>
-          <t>Gulf Authority Rakta</t>
-        </is>
-      </c>
-      <c r="B53" s="29" t="inlineStr">
-        <is>
-          <t>United Arab Emirates</t>
-        </is>
-      </c>
-      <c r="C53" s="30" t="inlineStr">
-        <is>
-          <t>Dubai Harbour Marina → Wynn Al Marjan Island arrival lagoon</t>
-        </is>
-      </c>
-      <c r="D53" s="31" t="n">
-        <v>49.8</v>
-      </c>
-      <c r="E53" s="26" t="n">
-        <v>35</v>
-      </c>
-      <c r="F53" s="32" t="inlineStr">
-        <is>
-          <t>T3</t>
-        </is>
-      </c>
-      <c r="G53" s="32" t="inlineStr">
-        <is>
-          <t>med-low</t>
-        </is>
-      </c>
-      <c r="H53" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="I53" s="33">
-        <f>60*D53/cruise_kt</f>
-        <v/>
-      </c>
-      <c r="J53" s="33">
-        <f>I53+turn_min+dwell_min</f>
-        <v/>
-      </c>
-      <c r="K53" s="34">
-        <f>MIN(10,FLOOR(60*service_hr/J53,1))</f>
-        <v/>
-      </c>
-      <c r="L53" s="34">
-        <f>ROUND(365*mech_uptime*H53,0)</f>
-        <v/>
-      </c>
-      <c r="M53" s="35">
-        <f>mech_uptime</f>
-        <v/>
-      </c>
-      <c r="N53" s="35">
-        <f>revleg_sel</f>
-        <v/>
-      </c>
-      <c r="O53" s="34">
-        <f>ROUND(K53*L53*revleg_sel,0)</f>
-        <v/>
-      </c>
-      <c r="P53" s="36">
-        <f>load_sel</f>
-        <v/>
-      </c>
-      <c r="Q53" s="36">
-        <f>pax_cap*P53</f>
-        <v/>
-      </c>
-      <c r="R53" s="34">
-        <f>Q53*O53</f>
-        <v/>
-      </c>
-      <c r="S53" s="37">
-        <f>E53*discount</f>
-        <v/>
-      </c>
-      <c r="T53" s="38">
-        <f>S53*R53</f>
-        <v/>
-      </c>
-      <c r="U53" s="38">
-        <f>(battery/range_nm)*D53*O53*VLOOKUP(B53,country_opex,3,FALSE)</f>
-        <v/>
-      </c>
-      <c r="V53" s="38">
-        <f>VLOOKUP(B53,country_opex,2,FALSE)*crew_factor</f>
-        <v/>
-      </c>
-      <c r="W53" s="38">
-        <f>VLOOKUP(B53,country_opex,5,FALSE)</f>
-        <v/>
-      </c>
-      <c r="X53" s="38">
-        <f>maint</f>
-        <v/>
-      </c>
-      <c r="Y53" s="38">
-        <f>VLOOKUP(B53,country_opex,7,FALSE)*ins_pct</f>
-        <v/>
-      </c>
-      <c r="Z53" s="38">
-        <f>charge_berth</f>
-        <v/>
-      </c>
-      <c r="AA53" s="38">
-        <f>U53+V53+W53+X53+Y53+Z53</f>
-        <v/>
-      </c>
-      <c r="AB53" s="38">
-        <f>VLOOKUP(B53,country_opex,7,FALSE)/dep_years</f>
-        <v/>
-      </c>
-      <c r="AC53" s="38">
-        <f>T53-AA53</f>
-        <v/>
-      </c>
-      <c r="AD53" s="35">
-        <f>IF(T53=0,"",AC53/T53)</f>
-        <v/>
-      </c>
-      <c r="AE53" s="36">
-        <f>IF(AC53&lt;=0,"",VLOOKUP(B53,country_opex,7,FALSE)/AC53)</f>
-        <v/>
-      </c>
-      <c r="AF53" s="33">
-        <f>((D53*O53/diesel_nmpg)*diesel_co2pg-(battery/range_nm)*D53*O53*VLOOKUP(B53,country_opex,4,FALSE))/1000</f>
-        <v/>
-      </c>
-      <c r="AG53" s="31" t="n">
-        <v>4285</v>
-      </c>
-      <c r="AH53" s="32" t="inlineStr">
-        <is>
-          <t>T3</t>
-        </is>
-      </c>
-      <c r="AI53" s="32" t="inlineStr">
-        <is>
-          <t>med-low</t>
-        </is>
-      </c>
-      <c r="AJ53" s="39" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="AK53" s="34">
-        <f>IF(AG53="","",AG53*AJ53)</f>
-        <v/>
-      </c>
-      <c r="AL53" s="34">
-        <f>IF(OR(AG53="",R53=0),"",MIN(IF(AS53="",9.9E+99,AS53),FLOOR(AK53/R53,1)))</f>
-        <v/>
-      </c>
-      <c r="AM53" s="38">
-        <f>IF(AL53="","",AL53*T53)</f>
-        <v/>
-      </c>
-      <c r="AN53" s="36">
-        <f>IF(OR(AG53="",R53=0),"",MIN(IF(AS53="",9.9E+99,AS53),AK53/R53))</f>
-        <v/>
-      </c>
-      <c r="AO53" s="38">
-        <f>IF(AN53="","",AN53*T53)</f>
-        <v/>
-      </c>
-      <c r="AP53" s="40" t="n"/>
-      <c r="AQ53" s="41" t="n"/>
-      <c r="AR53" s="41" t="n"/>
-      <c r="AS53" s="42" t="n"/>
-      <c r="AT53" s="43">
-        <f>IF(((S53*pax_cap*load_thin*ROUND(K53*L53*revleg_thin,0))-(((battery/range_nm)*D53*ROUND(K53*L53*revleg_thin,0)*VLOOKUP(B53,country_opex,3,FALSE))+V53+W53+X53+Y53+Z53))&lt;=0,"",VLOOKUP(B53,country_opex,7,FALSE)/((S53*pax_cap*load_thin*ROUND(K53*L53*revleg_thin,0))-(((battery/range_nm)*D53*ROUND(K53*L53*revleg_thin,0)*VLOOKUP(B53,country_opex,3,FALSE))+V53+W53+X53+Y53+Z53)))</f>
-        <v/>
-      </c>
-      <c r="AU53" s="43">
-        <f>IF(((S53*pax_cap*load_mid*ROUND(K53*L53*revleg_mid,0))-(((battery/range_nm)*D53*ROUND(K53*L53*revleg_mid,0)*VLOOKUP(B53,country_opex,3,FALSE))+V53+W53+X53+Y53+Z53))&lt;=0,"",VLOOKUP(B53,country_opex,7,FALSE)/((S53*pax_cap*load_mid*ROUND(K53*L53*revleg_mid,0))-(((battery/range_nm)*D53*ROUND(K53*L53*revleg_mid,0)*VLOOKUP(B53,country_opex,3,FALSE))+V53+W53+X53+Y53+Z53)))</f>
-        <v/>
-      </c>
-      <c r="AV53" s="43">
-        <f>IF(((S53*pax_cap*load_full*ROUND(K53*L53*revleg_full,0))-(((battery/range_nm)*D53*ROUND(K53*L53*revleg_full,0)*VLOOKUP(B53,country_opex,3,FALSE))+V53+W53+X53+Y53+Z53))&lt;=0,"",VLOOKUP(B53,country_opex,7,FALSE)/((S53*pax_cap*load_full*ROUND(K53*L53*revleg_full,0))-(((battery/range_nm)*D53*ROUND(K53*L53*revleg_full,0)*VLOOKUP(B53,country_opex,3,FALSE))+V53+W53+X53+Y53+Z53)))</f>
-        <v/>
-      </c>
-      <c r="AW53" s="44" t="n"/>
-      <c r="AX53" s="44" t="n"/>
+      <c r="A53" s="51" t="inlineStr">
+        <is>
+          <t>Held for Quanta-LR (&gt;70nm, roadmap H2 2026+):</t>
+        </is>
+      </c>
+      <c r="C53" s="52" t="inlineStr">
+        <is>
+          <t>Ras Al Khaimah → Abu Dhabi (112.0nm)</t>
+        </is>
+      </c>
     </row>
     <row r="54">
-      <c r="A54" s="29" t="inlineStr">
-        <is>
-          <t>Gulf Authority Rakta</t>
-        </is>
-      </c>
-      <c r="B54" s="29" t="inlineStr">
-        <is>
-          <t>United Arab Emirates</t>
-        </is>
-      </c>
-      <c r="C54" s="30" t="inlineStr">
-        <is>
-          <t>Dubai Harbour Marina → Wynn Al Marjan Island arrival lagoon</t>
-        </is>
-      </c>
-      <c r="D54" s="31" t="n">
-        <v>49.8</v>
-      </c>
-      <c r="E54" s="26" t="n">
-        <v>35</v>
-      </c>
-      <c r="F54" s="32" t="inlineStr">
-        <is>
-          <t>T3</t>
-        </is>
-      </c>
-      <c r="G54" s="32" t="inlineStr">
-        <is>
-          <t>med-low</t>
-        </is>
-      </c>
-      <c r="H54" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="I54" s="33">
-        <f>60*D54/cruise_kt</f>
-        <v/>
-      </c>
-      <c r="J54" s="33">
-        <f>I54+turn_min+dwell_min</f>
-        <v/>
-      </c>
-      <c r="K54" s="34">
-        <f>MIN(10,FLOOR(60*service_hr/J54,1))</f>
-        <v/>
-      </c>
-      <c r="L54" s="34">
-        <f>ROUND(365*mech_uptime*H54,0)</f>
-        <v/>
-      </c>
-      <c r="M54" s="35">
-        <f>mech_uptime</f>
-        <v/>
-      </c>
-      <c r="N54" s="35">
-        <f>revleg_sel</f>
-        <v/>
-      </c>
-      <c r="O54" s="34">
-        <f>ROUND(K54*L54*revleg_sel,0)</f>
-        <v/>
-      </c>
-      <c r="P54" s="36">
-        <f>load_sel</f>
-        <v/>
-      </c>
-      <c r="Q54" s="36">
-        <f>pax_cap*P54</f>
-        <v/>
-      </c>
-      <c r="R54" s="34">
-        <f>Q54*O54</f>
-        <v/>
-      </c>
-      <c r="S54" s="37">
-        <f>E54*discount</f>
-        <v/>
-      </c>
-      <c r="T54" s="38">
-        <f>S54*R54</f>
-        <v/>
-      </c>
-      <c r="U54" s="38">
-        <f>(battery/range_nm)*D54*O54*VLOOKUP(B54,country_opex,3,FALSE)</f>
-        <v/>
-      </c>
-      <c r="V54" s="38">
-        <f>VLOOKUP(B54,country_opex,2,FALSE)*crew_factor</f>
-        <v/>
-      </c>
-      <c r="W54" s="38">
-        <f>VLOOKUP(B54,country_opex,5,FALSE)</f>
-        <v/>
-      </c>
-      <c r="X54" s="38">
-        <f>maint</f>
-        <v/>
-      </c>
-      <c r="Y54" s="38">
-        <f>VLOOKUP(B54,country_opex,7,FALSE)*ins_pct</f>
-        <v/>
-      </c>
-      <c r="Z54" s="38">
-        <f>charge_berth</f>
-        <v/>
-      </c>
-      <c r="AA54" s="38">
-        <f>U54+V54+W54+X54+Y54+Z54</f>
-        <v/>
-      </c>
-      <c r="AB54" s="38">
-        <f>VLOOKUP(B54,country_opex,7,FALSE)/dep_years</f>
-        <v/>
-      </c>
-      <c r="AC54" s="38">
-        <f>T54-AA54</f>
-        <v/>
-      </c>
-      <c r="AD54" s="35">
-        <f>IF(T54=0,"",AC54/T54)</f>
-        <v/>
-      </c>
-      <c r="AE54" s="36">
-        <f>IF(AC54&lt;=0,"",VLOOKUP(B54,country_opex,7,FALSE)/AC54)</f>
-        <v/>
-      </c>
-      <c r="AF54" s="33">
-        <f>((D54*O54/diesel_nmpg)*diesel_co2pg-(battery/range_nm)*D54*O54*VLOOKUP(B54,country_opex,4,FALSE))/1000</f>
-        <v/>
-      </c>
-      <c r="AG54" s="31" t="n">
-        <v>4285</v>
-      </c>
-      <c r="AH54" s="32" t="inlineStr">
-        <is>
-          <t>T3</t>
-        </is>
-      </c>
-      <c r="AI54" s="32" t="inlineStr">
-        <is>
-          <t>med-low</t>
-        </is>
-      </c>
-      <c r="AJ54" s="39" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="AK54" s="34">
-        <f>IF(AG54="","",AG54*AJ54)</f>
-        <v/>
-      </c>
-      <c r="AL54" s="34">
-        <f>IF(OR(AG54="",R54=0),"",MIN(IF(AS54="",9.9E+99,AS54),FLOOR(AK54/R54,1)))</f>
-        <v/>
-      </c>
-      <c r="AM54" s="38">
-        <f>IF(AL54="","",AL54*T54)</f>
-        <v/>
-      </c>
-      <c r="AN54" s="36">
-        <f>IF(OR(AG54="",R54=0),"",MIN(IF(AS54="",9.9E+99,AS54),AK54/R54))</f>
-        <v/>
-      </c>
-      <c r="AO54" s="38">
-        <f>IF(AN54="","",AN54*T54)</f>
-        <v/>
-      </c>
-      <c r="AP54" s="40" t="n"/>
-      <c r="AQ54" s="41" t="n"/>
-      <c r="AR54" s="41" t="n"/>
-      <c r="AS54" s="42" t="n"/>
-      <c r="AT54" s="43">
-        <f>IF(((S54*pax_cap*load_thin*ROUND(K54*L54*revleg_thin,0))-(((battery/range_nm)*D54*ROUND(K54*L54*revleg_thin,0)*VLOOKUP(B54,country_opex,3,FALSE))+V54+W54+X54+Y54+Z54))&lt;=0,"",VLOOKUP(B54,country_opex,7,FALSE)/((S54*pax_cap*load_thin*ROUND(K54*L54*revleg_thin,0))-(((battery/range_nm)*D54*ROUND(K54*L54*revleg_thin,0)*VLOOKUP(B54,country_opex,3,FALSE))+V54+W54+X54+Y54+Z54)))</f>
-        <v/>
-      </c>
-      <c r="AU54" s="43">
-        <f>IF(((S54*pax_cap*load_mid*ROUND(K54*L54*revleg_mid,0))-(((battery/range_nm)*D54*ROUND(K54*L54*revleg_mid,0)*VLOOKUP(B54,country_opex,3,FALSE))+V54+W54+X54+Y54+Z54))&lt;=0,"",VLOOKUP(B54,country_opex,7,FALSE)/((S54*pax_cap*load_mid*ROUND(K54*L54*revleg_mid,0))-(((battery/range_nm)*D54*ROUND(K54*L54*revleg_mid,0)*VLOOKUP(B54,country_opex,3,FALSE))+V54+W54+X54+Y54+Z54)))</f>
-        <v/>
-      </c>
-      <c r="AV54" s="43">
-        <f>IF(((S54*pax_cap*load_full*ROUND(K54*L54*revleg_full,0))-(((battery/range_nm)*D54*ROUND(K54*L54*revleg_full,0)*VLOOKUP(B54,country_opex,3,FALSE))+V54+W54+X54+Y54+Z54))&lt;=0,"",VLOOKUP(B54,country_opex,7,FALSE)/((S54*pax_cap*load_full*ROUND(K54*L54*revleg_full,0))-(((battery/range_nm)*D54*ROUND(K54*L54*revleg_full,0)*VLOOKUP(B54,country_opex,3,FALSE))+V54+W54+X54+Y54+Z54)))</f>
-        <v/>
-      </c>
-      <c r="AW54" s="44" t="n"/>
-      <c r="AX54" s="44" t="n"/>
+      <c r="C54" s="52" t="inlineStr">
+        <is>
+          <t>Ras Al Khaimah → Muscat (263.5nm)</t>
+        </is>
+      </c>
     </row>
     <row r="55">
-      <c r="A55" s="29" t="inlineStr">
-        <is>
-          <t>Gulf Authority Rakta</t>
-        </is>
-      </c>
-      <c r="B55" s="29" t="inlineStr">
-        <is>
-          <t>United Arab Emirates</t>
-        </is>
-      </c>
-      <c r="C55" s="30" t="inlineStr">
-        <is>
-          <t>Dubai Harbour Marina → Wynn Al Marjan Island arrival lagoon</t>
-        </is>
-      </c>
-      <c r="D55" s="31" t="n">
-        <v>49.8</v>
-      </c>
-      <c r="E55" s="26" t="n">
-        <v>35</v>
-      </c>
-      <c r="F55" s="32" t="inlineStr">
-        <is>
-          <t>T3</t>
-        </is>
-      </c>
-      <c r="G55" s="32" t="inlineStr">
-        <is>
-          <t>med-low</t>
-        </is>
-      </c>
-      <c r="H55" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="I55" s="33">
-        <f>60*D55/cruise_kt</f>
-        <v/>
-      </c>
-      <c r="J55" s="33">
-        <f>I55+turn_min+dwell_min</f>
-        <v/>
-      </c>
-      <c r="K55" s="34">
-        <f>MIN(10,FLOOR(60*service_hr/J55,1))</f>
-        <v/>
-      </c>
-      <c r="L55" s="34">
-        <f>ROUND(365*mech_uptime*H55,0)</f>
-        <v/>
-      </c>
-      <c r="M55" s="35">
-        <f>mech_uptime</f>
-        <v/>
-      </c>
-      <c r="N55" s="35">
-        <f>revleg_sel</f>
-        <v/>
-      </c>
-      <c r="O55" s="34">
-        <f>ROUND(K55*L55*revleg_sel,0)</f>
-        <v/>
-      </c>
-      <c r="P55" s="36">
-        <f>load_sel</f>
-        <v/>
-      </c>
-      <c r="Q55" s="36">
-        <f>pax_cap*P55</f>
-        <v/>
-      </c>
-      <c r="R55" s="34">
-        <f>Q55*O55</f>
-        <v/>
-      </c>
-      <c r="S55" s="37">
-        <f>E55*discount</f>
-        <v/>
-      </c>
-      <c r="T55" s="38">
-        <f>S55*R55</f>
-        <v/>
-      </c>
-      <c r="U55" s="38">
-        <f>(battery/range_nm)*D55*O55*VLOOKUP(B55,country_opex,3,FALSE)</f>
-        <v/>
-      </c>
-      <c r="V55" s="38">
-        <f>VLOOKUP(B55,country_opex,2,FALSE)*crew_factor</f>
-        <v/>
-      </c>
-      <c r="W55" s="38">
-        <f>VLOOKUP(B55,country_opex,5,FALSE)</f>
-        <v/>
-      </c>
-      <c r="X55" s="38">
-        <f>maint</f>
-        <v/>
-      </c>
-      <c r="Y55" s="38">
-        <f>VLOOKUP(B55,country_opex,7,FALSE)*ins_pct</f>
-        <v/>
-      </c>
-      <c r="Z55" s="38">
-        <f>charge_berth</f>
-        <v/>
-      </c>
-      <c r="AA55" s="38">
-        <f>U55+V55+W55+X55+Y55+Z55</f>
-        <v/>
-      </c>
-      <c r="AB55" s="38">
-        <f>VLOOKUP(B55,country_opex,7,FALSE)/dep_years</f>
-        <v/>
-      </c>
-      <c r="AC55" s="38">
-        <f>T55-AA55</f>
-        <v/>
-      </c>
-      <c r="AD55" s="35">
-        <f>IF(T55=0,"",AC55/T55)</f>
-        <v/>
-      </c>
-      <c r="AE55" s="36">
-        <f>IF(AC55&lt;=0,"",VLOOKUP(B55,country_opex,7,FALSE)/AC55)</f>
-        <v/>
-      </c>
-      <c r="AF55" s="33">
-        <f>((D55*O55/diesel_nmpg)*diesel_co2pg-(battery/range_nm)*D55*O55*VLOOKUP(B55,country_opex,4,FALSE))/1000</f>
-        <v/>
-      </c>
-      <c r="AG55" s="31" t="n">
-        <v>4285</v>
-      </c>
-      <c r="AH55" s="32" t="inlineStr">
-        <is>
-          <t>T3</t>
-        </is>
-      </c>
-      <c r="AI55" s="32" t="inlineStr">
-        <is>
-          <t>med-low</t>
-        </is>
-      </c>
-      <c r="AJ55" s="39" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="AK55" s="34">
-        <f>IF(AG55="","",AG55*AJ55)</f>
-        <v/>
-      </c>
-      <c r="AL55" s="34">
-        <f>IF(OR(AG55="",R55=0),"",MIN(IF(AS55="",9.9E+99,AS55),FLOOR(AK55/R55,1)))</f>
-        <v/>
-      </c>
-      <c r="AM55" s="38">
-        <f>IF(AL55="","",AL55*T55)</f>
-        <v/>
-      </c>
-      <c r="AN55" s="36">
-        <f>IF(OR(AG55="",R55=0),"",MIN(IF(AS55="",9.9E+99,AS55),AK55/R55))</f>
-        <v/>
-      </c>
-      <c r="AO55" s="38">
-        <f>IF(AN55="","",AN55*T55)</f>
-        <v/>
-      </c>
-      <c r="AP55" s="40" t="n"/>
-      <c r="AQ55" s="41" t="n"/>
-      <c r="AR55" s="41" t="n"/>
-      <c r="AS55" s="42" t="n"/>
-      <c r="AT55" s="43">
-        <f>IF(((S55*pax_cap*load_thin*ROUND(K55*L55*revleg_thin,0))-(((battery/range_nm)*D55*ROUND(K55*L55*revleg_thin,0)*VLOOKUP(B55,country_opex,3,FALSE))+V55+W55+X55+Y55+Z55))&lt;=0,"",VLOOKUP(B55,country_opex,7,FALSE)/((S55*pax_cap*load_thin*ROUND(K55*L55*revleg_thin,0))-(((battery/range_nm)*D55*ROUND(K55*L55*revleg_thin,0)*VLOOKUP(B55,country_opex,3,FALSE))+V55+W55+X55+Y55+Z55)))</f>
-        <v/>
-      </c>
-      <c r="AU55" s="43">
-        <f>IF(((S55*pax_cap*load_mid*ROUND(K55*L55*revleg_mid,0))-(((battery/range_nm)*D55*ROUND(K55*L55*revleg_mid,0)*VLOOKUP(B55,country_opex,3,FALSE))+V55+W55+X55+Y55+Z55))&lt;=0,"",VLOOKUP(B55,country_opex,7,FALSE)/((S55*pax_cap*load_mid*ROUND(K55*L55*revleg_mid,0))-(((battery/range_nm)*D55*ROUND(K55*L55*revleg_mid,0)*VLOOKUP(B55,country_opex,3,FALSE))+V55+W55+X55+Y55+Z55)))</f>
-        <v/>
-      </c>
-      <c r="AV55" s="43">
-        <f>IF(((S55*pax_cap*load_full*ROUND(K55*L55*revleg_full,0))-(((battery/range_nm)*D55*ROUND(K55*L55*revleg_full,0)*VLOOKUP(B55,country_opex,3,FALSE))+V55+W55+X55+Y55+Z55))&lt;=0,"",VLOOKUP(B55,country_opex,7,FALSE)/((S55*pax_cap*load_full*ROUND(K55*L55*revleg_full,0))-(((battery/range_nm)*D55*ROUND(K55*L55*revleg_full,0)*VLOOKUP(B55,country_opex,3,FALSE))+V55+W55+X55+Y55+Z55)))</f>
-        <v/>
-      </c>
-      <c r="AW55" s="44" t="n"/>
-      <c r="AX55" s="44" t="n"/>
+      <c r="C55" s="52" t="inlineStr">
+        <is>
+          <t>Ras Al Khaimah → Doha (240.7nm)</t>
+        </is>
+      </c>
     </row>
     <row r="56">
-      <c r="A56" s="29" t="inlineStr">
-        <is>
-          <t>Gulf Authority Rakta</t>
-        </is>
-      </c>
-      <c r="B56" s="29" t="inlineStr">
-        <is>
-          <t>United Arab Emirates</t>
-        </is>
-      </c>
-      <c r="C56" s="30" t="inlineStr">
-        <is>
-          <t>Ras Al Khaimah → Dubai Islands Marina</t>
-        </is>
-      </c>
-      <c r="D56" s="31" t="n">
-        <v>50</v>
-      </c>
-      <c r="E56" s="26" t="n">
-        <v>35</v>
-      </c>
-      <c r="F56" s="32" t="inlineStr">
-        <is>
-          <t>T3</t>
-        </is>
-      </c>
-      <c r="G56" s="32" t="inlineStr">
-        <is>
-          <t>med-low</t>
-        </is>
-      </c>
-      <c r="H56" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="I56" s="33">
-        <f>60*D56/cruise_kt</f>
-        <v/>
-      </c>
-      <c r="J56" s="33">
-        <f>I56+turn_min+dwell_min</f>
-        <v/>
-      </c>
-      <c r="K56" s="34">
-        <f>MIN(10,FLOOR(60*service_hr/J56,1))</f>
-        <v/>
-      </c>
-      <c r="L56" s="34">
-        <f>ROUND(365*mech_uptime*H56,0)</f>
-        <v/>
-      </c>
-      <c r="M56" s="35">
-        <f>mech_uptime</f>
-        <v/>
-      </c>
-      <c r="N56" s="35">
-        <f>revleg_sel</f>
-        <v/>
-      </c>
-      <c r="O56" s="34">
-        <f>ROUND(K56*L56*revleg_sel,0)</f>
-        <v/>
-      </c>
-      <c r="P56" s="36">
-        <f>load_sel</f>
-        <v/>
-      </c>
-      <c r="Q56" s="36">
-        <f>pax_cap*P56</f>
-        <v/>
-      </c>
-      <c r="R56" s="34">
-        <f>Q56*O56</f>
-        <v/>
-      </c>
-      <c r="S56" s="37">
-        <f>E56*discount</f>
-        <v/>
-      </c>
-      <c r="T56" s="38">
-        <f>S56*R56</f>
-        <v/>
-      </c>
-      <c r="U56" s="38">
-        <f>(battery/range_nm)*D56*O56*VLOOKUP(B56,country_opex,3,FALSE)</f>
-        <v/>
-      </c>
-      <c r="V56" s="38">
-        <f>VLOOKUP(B56,country_opex,2,FALSE)*crew_factor</f>
-        <v/>
-      </c>
-      <c r="W56" s="38">
-        <f>VLOOKUP(B56,country_opex,5,FALSE)</f>
-        <v/>
-      </c>
-      <c r="X56" s="38">
-        <f>maint</f>
-        <v/>
-      </c>
-      <c r="Y56" s="38">
-        <f>VLOOKUP(B56,country_opex,7,FALSE)*ins_pct</f>
-        <v/>
-      </c>
-      <c r="Z56" s="38">
-        <f>charge_berth</f>
-        <v/>
-      </c>
-      <c r="AA56" s="38">
-        <f>U56+V56+W56+X56+Y56+Z56</f>
-        <v/>
-      </c>
-      <c r="AB56" s="38">
-        <f>VLOOKUP(B56,country_opex,7,FALSE)/dep_years</f>
-        <v/>
-      </c>
-      <c r="AC56" s="38">
-        <f>T56-AA56</f>
-        <v/>
-      </c>
-      <c r="AD56" s="35">
-        <f>IF(T56=0,"",AC56/T56)</f>
-        <v/>
-      </c>
-      <c r="AE56" s="36">
-        <f>IF(AC56&lt;=0,"",VLOOKUP(B56,country_opex,7,FALSE)/AC56)</f>
-        <v/>
-      </c>
-      <c r="AF56" s="33">
-        <f>((D56*O56/diesel_nmpg)*diesel_co2pg-(battery/range_nm)*D56*O56*VLOOKUP(B56,country_opex,4,FALSE))/1000</f>
-        <v/>
-      </c>
-      <c r="AG56" s="31" t="n">
-        <v>4285</v>
-      </c>
-      <c r="AH56" s="32" t="inlineStr">
-        <is>
-          <t>T3</t>
-        </is>
-      </c>
-      <c r="AI56" s="32" t="inlineStr">
-        <is>
-          <t>med-low</t>
-        </is>
-      </c>
-      <c r="AJ56" s="39" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="AK56" s="34">
-        <f>IF(AG56="","",AG56*AJ56)</f>
-        <v/>
-      </c>
-      <c r="AL56" s="34">
-        <f>IF(OR(AG56="",R56=0),"",MIN(IF(AS56="",9.9E+99,AS56),FLOOR(AK56/R56,1)))</f>
-        <v/>
-      </c>
-      <c r="AM56" s="38">
-        <f>IF(AL56="","",AL56*T56)</f>
-        <v/>
-      </c>
-      <c r="AN56" s="36">
-        <f>IF(OR(AG56="",R56=0),"",MIN(IF(AS56="",9.9E+99,AS56),AK56/R56))</f>
-        <v/>
-      </c>
-      <c r="AO56" s="38">
-        <f>IF(AN56="","",AN56*T56)</f>
-        <v/>
-      </c>
-      <c r="AP56" s="40" t="n"/>
-      <c r="AQ56" s="41" t="n"/>
-      <c r="AR56" s="41" t="n"/>
-      <c r="AS56" s="42" t="n"/>
-      <c r="AT56" s="43">
-        <f>IF(((S56*pax_cap*load_thin*ROUND(K56*L56*revleg_thin,0))-(((battery/range_nm)*D56*ROUND(K56*L56*revleg_thin,0)*VLOOKUP(B56,country_opex,3,FALSE))+V56+W56+X56+Y56+Z56))&lt;=0,"",VLOOKUP(B56,country_opex,7,FALSE)/((S56*pax_cap*load_thin*ROUND(K56*L56*revleg_thin,0))-(((battery/range_nm)*D56*ROUND(K56*L56*revleg_thin,0)*VLOOKUP(B56,country_opex,3,FALSE))+V56+W56+X56+Y56+Z56)))</f>
-        <v/>
-      </c>
-      <c r="AU56" s="43">
-        <f>IF(((S56*pax_cap*load_mid*ROUND(K56*L56*revleg_mid,0))-(((battery/range_nm)*D56*ROUND(K56*L56*revleg_mid,0)*VLOOKUP(B56,country_opex,3,FALSE))+V56+W56+X56+Y56+Z56))&lt;=0,"",VLOOKUP(B56,country_opex,7,FALSE)/((S56*pax_cap*load_mid*ROUND(K56*L56*revleg_mid,0))-(((battery/range_nm)*D56*ROUND(K56*L56*revleg_mid,0)*VLOOKUP(B56,country_opex,3,FALSE))+V56+W56+X56+Y56+Z56)))</f>
-        <v/>
-      </c>
-      <c r="AV56" s="43">
-        <f>IF(((S56*pax_cap*load_full*ROUND(K56*L56*revleg_full,0))-(((battery/range_nm)*D56*ROUND(K56*L56*revleg_full,0)*VLOOKUP(B56,country_opex,3,FALSE))+V56+W56+X56+Y56+Z56))&lt;=0,"",VLOOKUP(B56,country_opex,7,FALSE)/((S56*pax_cap*load_full*ROUND(K56*L56*revleg_full,0))-(((battery/range_nm)*D56*ROUND(K56*L56*revleg_full,0)*VLOOKUP(B56,country_opex,3,FALSE))+V56+W56+X56+Y56+Z56)))</f>
-        <v/>
-      </c>
-      <c r="AW56" s="44" t="n"/>
-      <c r="AX56" s="44" t="n"/>
-    </row>
-    <row r="57">
-      <c r="A57" s="45" t="inlineStr">
-        <is>
-          <t>TOTAL / median</t>
-        </is>
-      </c>
-      <c r="T57" s="46">
-        <f>SUM(T4:T56)</f>
-        <v/>
-      </c>
-      <c r="AC57" s="46">
-        <f>SUM(AC4:AC56)</f>
-        <v/>
-      </c>
-      <c r="AD57" s="47">
-        <f>IF(T57=0,"",AC57/T57)</f>
-        <v/>
-      </c>
-      <c r="AL57" s="48">
-        <f>SUM(AL4:AL56)</f>
-        <v/>
-      </c>
-      <c r="AM57" s="46">
-        <f>SUM(AM4:AM56)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" s="8" t="inlineStr">
-        <is>
-          <t>Market fleet build-up — grounded floor (network-sum of raw vessel fractions per market, rounded once; subset slices excluded; legacy per-corridor-floor totals above kept for reference)</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" s="24" t="inlineStr">
-        <is>
-          <t>Market</t>
-        </is>
-      </c>
-      <c r="B60" s="24" t="inlineStr">
-        <is>
-          <t>Fleet basis</t>
-        </is>
-      </c>
-      <c r="C60" s="24" t="inlineStr">
-        <is>
-          <t>Raw vessels (sum)</t>
-        </is>
-      </c>
-      <c r="D60" s="24" t="inlineStr">
-        <is>
-          <t>Fleet (rounded once)</t>
-        </is>
-      </c>
-      <c r="E60" s="24" t="inlineStr">
-        <is>
-          <t>Market rev/yr (raw sum)</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" s="25" t="inlineStr">
-        <is>
-          <t>Gulf Authority Rakta</t>
-        </is>
-      </c>
-      <c r="B61" s="13" t="inlineStr">
-        <is>
-          <t>network_sum / ceil</t>
-        </is>
-      </c>
-      <c r="C61" s="23">
-        <f>SUMIFS(AN4:AN56,A4:A56,"Gulf Authority Rakta",AP4:AP56,"=",AQ4:AQ56,"=",AR4:AR56,"=")</f>
-        <v/>
-      </c>
-      <c r="D61" s="49">
-        <f>IF(C61=0,0,CEILING(C61,1))</f>
-        <v/>
-      </c>
-      <c r="E61" s="50">
-        <f>SUMIFS(AO4:AO56,A4:A56,"Gulf Authority Rakta",AP4:AP56,"=",AQ4:AQ56,"=",AR4:AR56,"=")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" s="45" t="inlineStr">
-        <is>
-          <t>GROUNDED FLOOR (PUBLISHED)</t>
-        </is>
-      </c>
-      <c r="D62" s="48">
-        <f>SUM(D61:D61)</f>
-        <v/>
-      </c>
-      <c r="E62" s="46">
-        <f>SUM(E61:E61)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" s="51" t="inlineStr">
-        <is>
-          <t>Held for Quanta-LR (&gt;70nm, roadmap H2 2026+):</t>
-        </is>
-      </c>
-      <c r="C64" s="52" t="inlineStr">
-        <is>
-          <t>Ras Al Khaimah → Doha (240.7nm)</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="C65" s="52" t="inlineStr">
-        <is>
-          <t>Ras Al Khaimah → Muscat (263.5nm)</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="C66" s="52" t="inlineStr">
+      <c r="C56" s="52" t="inlineStr">
         <is>
           <t>Ras Al Khaimah → Manama (289.7nm)</t>
         </is>
@@ -12129,7 +10090,7 @@
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:L1"/>
-    <mergeCell ref="A59:L59"/>
+    <mergeCell ref="A48:L48"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/finance/_refresh_rakta.xlsx
+++ b/finance/_refresh_rakta.xlsx
@@ -1307,7 +1307,7 @@
         </is>
       </c>
       <c r="B19" s="12" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="C19" s="13" t="inlineStr">
         <is>
@@ -1326,7 +1326,7 @@
       </c>
       <c r="F19" s="14" t="inlineStr">
         <is>
-          <t>Cap on revenue sailings/day — ~1 sailing/70min in a 12h window; a believable on-demand premium duty cycle, not capacity-max (Jaideep 2026-06-19).</t>
+          <t>Cap on revenue sailings/day — MID headline duty cycle; thin=12 / full=18 bookends in _utilization_scenarios (Jaideep 2026-06-21).</t>
         </is>
       </c>
     </row>
@@ -1603,7 +1603,7 @@
         <v>0.45</v>
       </c>
       <c r="C31" s="19" t="n">
-        <v>0.45</v>
+        <v>0.55</v>
       </c>
       <c r="F31" s="14" t="inlineStr">
         <is>
@@ -1621,7 +1621,7 @@
         <v>0.55</v>
       </c>
       <c r="C32" s="19" t="n">
-        <v>0.55</v>
+        <v>0.65</v>
       </c>
       <c r="F32" s="14" t="inlineStr">
         <is>
@@ -1639,7 +1639,7 @@
         <v>0.7</v>
       </c>
       <c r="C33" s="19" t="n">
-        <v>0.75</v>
+        <v>0.85</v>
       </c>
       <c r="F33" s="14" t="inlineStr">
         <is>
@@ -2186,7 +2186,7 @@
         <v/>
       </c>
       <c r="K4" s="34">
-        <f>MIN(10,FLOOR(60*service_hr/J4,1))</f>
+        <f>MIN(15,FLOOR(60*service_hr/J4,1))</f>
         <v/>
       </c>
       <c r="L4" s="34">
@@ -2372,7 +2372,7 @@
         <v/>
       </c>
       <c r="K5" s="34">
-        <f>MIN(10,FLOOR(60*service_hr/J5,1))</f>
+        <f>MIN(15,FLOOR(60*service_hr/J5,1))</f>
         <v/>
       </c>
       <c r="L5" s="34">
@@ -2558,7 +2558,7 @@
         <v/>
       </c>
       <c r="K6" s="34">
-        <f>MIN(10,FLOOR(60*service_hr/J6,1))</f>
+        <f>MIN(15,FLOOR(60*service_hr/J6,1))</f>
         <v/>
       </c>
       <c r="L6" s="34">
@@ -2744,7 +2744,7 @@
         <v/>
       </c>
       <c r="K7" s="34">
-        <f>MIN(10,FLOOR(60*service_hr/J7,1))</f>
+        <f>MIN(15,FLOOR(60*service_hr/J7,1))</f>
         <v/>
       </c>
       <c r="L7" s="34">
@@ -2930,7 +2930,7 @@
         <v/>
       </c>
       <c r="K8" s="34">
-        <f>MIN(10,FLOOR(60*service_hr/J8,1))</f>
+        <f>MIN(15,FLOOR(60*service_hr/J8,1))</f>
         <v/>
       </c>
       <c r="L8" s="34">
@@ -3116,7 +3116,7 @@
         <v/>
       </c>
       <c r="K9" s="34">
-        <f>MIN(10,FLOOR(60*service_hr/J9,1))</f>
+        <f>MIN(15,FLOOR(60*service_hr/J9,1))</f>
         <v/>
       </c>
       <c r="L9" s="34">
@@ -3302,7 +3302,7 @@
         <v/>
       </c>
       <c r="K10" s="34">
-        <f>MIN(10,FLOOR(60*service_hr/J10,1))</f>
+        <f>MIN(15,FLOOR(60*service_hr/J10,1))</f>
         <v/>
       </c>
       <c r="L10" s="34">
@@ -3488,7 +3488,7 @@
         <v/>
       </c>
       <c r="K11" s="34">
-        <f>MIN(10,FLOOR(60*service_hr/J11,1))</f>
+        <f>MIN(15,FLOOR(60*service_hr/J11,1))</f>
         <v/>
       </c>
       <c r="L11" s="34">
@@ -3674,7 +3674,7 @@
         <v/>
       </c>
       <c r="K12" s="34">
-        <f>MIN(10,FLOOR(60*service_hr/J12,1))</f>
+        <f>MIN(15,FLOOR(60*service_hr/J12,1))</f>
         <v/>
       </c>
       <c r="L12" s="34">
@@ -3860,7 +3860,7 @@
         <v/>
       </c>
       <c r="K13" s="34">
-        <f>MIN(10,FLOOR(60*service_hr/J13,1))</f>
+        <f>MIN(15,FLOOR(60*service_hr/J13,1))</f>
         <v/>
       </c>
       <c r="L13" s="34">
@@ -4046,7 +4046,7 @@
         <v/>
       </c>
       <c r="K14" s="34">
-        <f>MIN(10,FLOOR(60*service_hr/J14,1))</f>
+        <f>MIN(15,FLOOR(60*service_hr/J14,1))</f>
         <v/>
       </c>
       <c r="L14" s="34">
@@ -4232,7 +4232,7 @@
         <v/>
       </c>
       <c r="K15" s="34">
-        <f>MIN(10,FLOOR(60*service_hr/J15,1))</f>
+        <f>MIN(15,FLOOR(60*service_hr/J15,1))</f>
         <v/>
       </c>
       <c r="L15" s="34">
@@ -4418,7 +4418,7 @@
         <v/>
       </c>
       <c r="K16" s="34">
-        <f>MIN(10,FLOOR(60*service_hr/J16,1))</f>
+        <f>MIN(15,FLOOR(60*service_hr/J16,1))</f>
         <v/>
       </c>
       <c r="L16" s="34">
@@ -4604,7 +4604,7 @@
         <v/>
       </c>
       <c r="K17" s="34">
-        <f>MIN(10,FLOOR(60*service_hr/J17,1))</f>
+        <f>MIN(15,FLOOR(60*service_hr/J17,1))</f>
         <v/>
       </c>
       <c r="L17" s="34">
@@ -4790,7 +4790,7 @@
         <v/>
       </c>
       <c r="K18" s="34">
-        <f>MIN(10,FLOOR(60*service_hr/J18,1))</f>
+        <f>MIN(15,FLOOR(60*service_hr/J18,1))</f>
         <v/>
       </c>
       <c r="L18" s="34">
@@ -4976,7 +4976,7 @@
         <v/>
       </c>
       <c r="K19" s="34">
-        <f>MIN(10,FLOOR(60*service_hr/J19,1))</f>
+        <f>MIN(15,FLOOR(60*service_hr/J19,1))</f>
         <v/>
       </c>
       <c r="L19" s="34">
@@ -5162,7 +5162,7 @@
         <v/>
       </c>
       <c r="K20" s="34">
-        <f>MIN(10,FLOOR(60*service_hr/J20,1))</f>
+        <f>MIN(15,FLOOR(60*service_hr/J20,1))</f>
         <v/>
       </c>
       <c r="L20" s="34">
@@ -5348,7 +5348,7 @@
         <v/>
       </c>
       <c r="K21" s="34">
-        <f>MIN(10,FLOOR(60*service_hr/J21,1))</f>
+        <f>MIN(15,FLOOR(60*service_hr/J21,1))</f>
         <v/>
       </c>
       <c r="L21" s="34">
@@ -5534,7 +5534,7 @@
         <v/>
       </c>
       <c r="K22" s="34">
-        <f>MIN(10,FLOOR(60*service_hr/J22,1))</f>
+        <f>MIN(15,FLOOR(60*service_hr/J22,1))</f>
         <v/>
       </c>
       <c r="L22" s="34">
@@ -5720,7 +5720,7 @@
         <v/>
       </c>
       <c r="K23" s="34">
-        <f>MIN(10,FLOOR(60*service_hr/J23,1))</f>
+        <f>MIN(15,FLOOR(60*service_hr/J23,1))</f>
         <v/>
       </c>
       <c r="L23" s="34">
@@ -5906,7 +5906,7 @@
         <v/>
       </c>
       <c r="K24" s="34">
-        <f>MIN(10,FLOOR(60*service_hr/J24,1))</f>
+        <f>MIN(15,FLOOR(60*service_hr/J24,1))</f>
         <v/>
       </c>
       <c r="L24" s="34">
@@ -6092,7 +6092,7 @@
         <v/>
       </c>
       <c r="K25" s="34">
-        <f>MIN(10,FLOOR(60*service_hr/J25,1))</f>
+        <f>MIN(15,FLOOR(60*service_hr/J25,1))</f>
         <v/>
       </c>
       <c r="L25" s="34">
@@ -6278,7 +6278,7 @@
         <v/>
       </c>
       <c r="K26" s="34">
-        <f>MIN(10,FLOOR(60*service_hr/J26,1))</f>
+        <f>MIN(15,FLOOR(60*service_hr/J26,1))</f>
         <v/>
       </c>
       <c r="L26" s="34">
@@ -6464,7 +6464,7 @@
         <v/>
       </c>
       <c r="K27" s="34">
-        <f>MIN(10,FLOOR(60*service_hr/J27,1))</f>
+        <f>MIN(15,FLOOR(60*service_hr/J27,1))</f>
         <v/>
       </c>
       <c r="L27" s="34">
@@ -6650,7 +6650,7 @@
         <v/>
       </c>
       <c r="K28" s="34">
-        <f>MIN(10,FLOOR(60*service_hr/J28,1))</f>
+        <f>MIN(15,FLOOR(60*service_hr/J28,1))</f>
         <v/>
       </c>
       <c r="L28" s="34">
@@ -6836,7 +6836,7 @@
         <v/>
       </c>
       <c r="K29" s="34">
-        <f>MIN(10,FLOOR(60*service_hr/J29,1))</f>
+        <f>MIN(15,FLOOR(60*service_hr/J29,1))</f>
         <v/>
       </c>
       <c r="L29" s="34">
@@ -7022,7 +7022,7 @@
         <v/>
       </c>
       <c r="K30" s="34">
-        <f>MIN(10,FLOOR(60*service_hr/J30,1))</f>
+        <f>MIN(15,FLOOR(60*service_hr/J30,1))</f>
         <v/>
       </c>
       <c r="L30" s="34">
@@ -7208,7 +7208,7 @@
         <v/>
       </c>
       <c r="K31" s="34">
-        <f>MIN(10,FLOOR(60*service_hr/J31,1))</f>
+        <f>MIN(15,FLOOR(60*service_hr/J31,1))</f>
         <v/>
       </c>
       <c r="L31" s="34">
@@ -7394,7 +7394,7 @@
         <v/>
       </c>
       <c r="K32" s="34">
-        <f>MIN(10,FLOOR(60*service_hr/J32,1))</f>
+        <f>MIN(15,FLOOR(60*service_hr/J32,1))</f>
         <v/>
       </c>
       <c r="L32" s="34">
@@ -7580,7 +7580,7 @@
         <v/>
       </c>
       <c r="K33" s="34">
-        <f>MIN(10,FLOOR(60*service_hr/J33,1))</f>
+        <f>MIN(15,FLOOR(60*service_hr/J33,1))</f>
         <v/>
       </c>
       <c r="L33" s="34">
@@ -7766,7 +7766,7 @@
         <v/>
       </c>
       <c r="K34" s="34">
-        <f>MIN(10,FLOOR(60*service_hr/J34,1))</f>
+        <f>MIN(15,FLOOR(60*service_hr/J34,1))</f>
         <v/>
       </c>
       <c r="L34" s="34">
@@ -7952,7 +7952,7 @@
         <v/>
       </c>
       <c r="K35" s="34">
-        <f>MIN(10,FLOOR(60*service_hr/J35,1))</f>
+        <f>MIN(15,FLOOR(60*service_hr/J35,1))</f>
         <v/>
       </c>
       <c r="L35" s="34">
@@ -8138,7 +8138,7 @@
         <v/>
       </c>
       <c r="K36" s="34">
-        <f>MIN(10,FLOOR(60*service_hr/J36,1))</f>
+        <f>MIN(15,FLOOR(60*service_hr/J36,1))</f>
         <v/>
       </c>
       <c r="L36" s="34">
@@ -8324,7 +8324,7 @@
         <v/>
       </c>
       <c r="K37" s="34">
-        <f>MIN(10,FLOOR(60*service_hr/J37,1))</f>
+        <f>MIN(15,FLOOR(60*service_hr/J37,1))</f>
         <v/>
       </c>
       <c r="L37" s="34">
@@ -8510,7 +8510,7 @@
         <v/>
       </c>
       <c r="K38" s="34">
-        <f>MIN(10,FLOOR(60*service_hr/J38,1))</f>
+        <f>MIN(15,FLOOR(60*service_hr/J38,1))</f>
         <v/>
       </c>
       <c r="L38" s="34">
@@ -8696,7 +8696,7 @@
         <v/>
       </c>
       <c r="K39" s="34">
-        <f>MIN(10,FLOOR(60*service_hr/J39,1))</f>
+        <f>MIN(15,FLOOR(60*service_hr/J39,1))</f>
         <v/>
       </c>
       <c r="L39" s="34">
@@ -8882,7 +8882,7 @@
         <v/>
       </c>
       <c r="K40" s="34">
-        <f>MIN(10,FLOOR(60*service_hr/J40,1))</f>
+        <f>MIN(15,FLOOR(60*service_hr/J40,1))</f>
         <v/>
       </c>
       <c r="L40" s="34">
@@ -9068,7 +9068,7 @@
         <v/>
       </c>
       <c r="K41" s="34">
-        <f>MIN(10,FLOOR(60*service_hr/J41,1))</f>
+        <f>MIN(15,FLOOR(60*service_hr/J41,1))</f>
         <v/>
       </c>
       <c r="L41" s="34">
@@ -9254,7 +9254,7 @@
         <v/>
       </c>
       <c r="K42" s="34">
-        <f>MIN(10,FLOOR(60*service_hr/J42,1))</f>
+        <f>MIN(15,FLOOR(60*service_hr/J42,1))</f>
         <v/>
       </c>
       <c r="L42" s="34">
@@ -9440,7 +9440,7 @@
         <v/>
       </c>
       <c r="K43" s="34">
-        <f>MIN(10,FLOOR(60*service_hr/J43,1))</f>
+        <f>MIN(15,FLOOR(60*service_hr/J43,1))</f>
         <v/>
       </c>
       <c r="L43" s="34">
@@ -9626,7 +9626,7 @@
         <v/>
       </c>
       <c r="K44" s="34">
-        <f>MIN(10,FLOOR(60*service_hr/J44,1))</f>
+        <f>MIN(15,FLOOR(60*service_hr/J44,1))</f>
         <v/>
       </c>
       <c r="L44" s="34">
@@ -9812,7 +9812,7 @@
         <v/>
       </c>
       <c r="K45" s="34">
-        <f>MIN(10,FLOOR(60*service_hr/J45,1))</f>
+        <f>MIN(15,FLOOR(60*service_hr/J45,1))</f>
         <v/>
       </c>
       <c r="L45" s="34">

--- a/finance/_refresh_rakta.xlsx
+++ b/finance/_refresh_rakta.xlsx
@@ -1326,7 +1326,7 @@
       </c>
       <c r="F19" s="14" t="inlineStr">
         <is>
-          <t>Cap on revenue sailings/day — MID headline duty cycle; thin=12 / full=18 bookends in _utilization_scenarios (Jaideep 2026-06-21).</t>
+          <t>Cap on revenue sailings/day — 15 across thin/mid/full scenarios (Jaideep 2026-06-21).</t>
         </is>
       </c>
     </row>
@@ -1639,7 +1639,7 @@
         <v>0.7</v>
       </c>
       <c r="C33" s="19" t="n">
-        <v>0.85</v>
+        <v>0.75</v>
       </c>
       <c r="F33" s="14" t="inlineStr">
         <is>

--- a/finance/_refresh_rakta.xlsx
+++ b/finance/_refresh_rakta.xlsx
@@ -27,23 +27,23 @@
     <definedName name="dwell_min">'Assumptions'!$B$18</definedName>
     <definedName name="max_tpd">'Assumptions'!$B$19</definedName>
     <definedName name="crew_factor">'Assumptions'!$B$20</definedName>
-    <definedName name="ins_pct">'Assumptions'!$B$21</definedName>
-    <definedName name="charge_berth">'Assumptions'!$B$22</definedName>
-    <definedName name="mech_uptime">'Assumptions'!$B$23</definedName>
-    <definedName name="capture">'Assumptions'!$B$24</definedName>
-    <definedName name="capture_captive">'Assumptions'!$B$25</definedName>
-    <definedName name="discount">'Assumptions'!$B$26</definedName>
-    <definedName name="diesel_co2pg">'Assumptions'!$B$27</definedName>
-    <definedName name="load_thin">'Assumptions'!$B$31</definedName>
-    <definedName name="revleg_thin">'Assumptions'!$C$31</definedName>
-    <definedName name="load_mid">'Assumptions'!$B$32</definedName>
-    <definedName name="revleg_mid">'Assumptions'!$C$32</definedName>
-    <definedName name="load_full">'Assumptions'!$B$33</definedName>
-    <definedName name="revleg_full">'Assumptions'!$C$33</definedName>
-    <definedName name="band_tbl">'Assumptions'!$A$31:$C$33</definedName>
-    <definedName name="scenario">'Assumptions'!$B$35</definedName>
-    <definedName name="load_sel">'Assumptions'!$B$36</definedName>
-    <definedName name="revleg_sel">'Assumptions'!$B$37</definedName>
+    <definedName name="mech_uptime">'Assumptions'!$B$21</definedName>
+    <definedName name="capture">'Assumptions'!$B$22</definedName>
+    <definedName name="capture_captive">'Assumptions'!$B$23</definedName>
+    <definedName name="discount">'Assumptions'!$B$24</definedName>
+    <definedName name="diesel_co2pg">'Assumptions'!$B$25</definedName>
+    <definedName name="ins_pct">'Assumptions'!$B$29</definedName>
+    <definedName name="charge_berth">'Assumptions'!$B$30</definedName>
+    <definedName name="load_thin">'Assumptions'!$B$34</definedName>
+    <definedName name="revleg_thin">'Assumptions'!$C$34</definedName>
+    <definedName name="load_mid">'Assumptions'!$B$35</definedName>
+    <definedName name="revleg_mid">'Assumptions'!$C$35</definedName>
+    <definedName name="load_full">'Assumptions'!$B$36</definedName>
+    <definedName name="revleg_full">'Assumptions'!$C$36</definedName>
+    <definedName name="band_tbl">'Assumptions'!$A$34:$C$36</definedName>
+    <definedName name="scenario">'Assumptions'!$B$38</definedName>
+    <definedName name="load_sel">'Assumptions'!$B$39</definedName>
+    <definedName name="revleg_sel">'Assumptions'!$B$40</definedName>
     <definedName name="country_opex">'Country opex'!$A$4:$G$4</definedName>
     <definedName name="som_floor_fleet">'Corridor economics'!$D$51</definedName>
     <definedName name="som_floor_rev">'Corridor economics'!$E$51</definedName>
@@ -701,7 +701,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:B27"/>
+  <dimension ref="B2:B36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -780,84 +780,143 @@
     <row r="14">
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>EBITDA  = REVENUE − OPEX   (energy + captain + marina/overhead + maintenance)</t>
+          <t>EBITDA  = REVENUE − OPEX</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="B15" s="4" t="inlineStr">
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    OPEX = energy + crew + berth/port admin + maintenance + vessel insurance + fast-charge berth</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="B16" s="4" t="inlineStr">
         <is>
           <t>PAYBACK = vessel CAPEX ÷ EBITDA</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="B16" s="2" t="inlineStr"/>
-    </row>
     <row r="17">
-      <c r="B17" s="3" t="inlineStr">
-        <is>
-          <t>From demand pool to fleet &amp; market size</t>
-        </is>
-      </c>
+      <c r="B17" s="2" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="B18" s="5" t="inlineStr">
-        <is>
-          <t>Navier serviceable rides/yr = corridor demand pool × capture rate (10% on contested corridors; ~90% on captive sole-operator transfer legs — see the per-row Capture % column)</t>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>OPEX lines (per boat, per year — no double-counting)</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>Vessels supported = FLOOR(Navier rides/yr ÷ pax/yr per boat);  Market rev = vessels × rev/boat. The 'Market sizing' tab rolls these up into the SOM → SAM → TAM ladder.</t>
+          <t>Energy — variable propulsion cost: kWh on revenue sailings × local $/kWh (Country opex tab). Excludes utility demand charges.</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="B20" s="2" t="inlineStr"/>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>Crew — fully-loaded captain + relief: local captain wage × crew FTE factor (Country opex + Assumptions).</t>
+        </is>
+      </c>
     </row>
     <row r="21">
-      <c r="B21" s="3" t="inlineStr">
-        <is>
-          <t>The scenario toggle (what we flex)</t>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>Berth &amp; port admin — fixed annual berth, port fees, and local marine admin (Country opex tab). Excludes vessel H&amp;M+P&amp;I and fast-charge infrastructure.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>'Corridor economics' has a SCENARIO cell = THIN / MID / FULL. It flexes two levers: load factor (how full the boat is) and revenue-leg factor (how many legs earn full fare). MID is the headline. Change that one cell and the whole model recomputes. The right-hand Payback THIN/MID/FULL columns always show all three at once.</t>
+          <t>Maintenance — vessel annual maintenance reserve (Assumptions tab).</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="B23" s="2" t="inlineStr"/>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>Vessel insurance — commercial H&amp;M + P&amp;I as % of regional CAPEX (Assumptions % × Country opex CAPEX column).</t>
+        </is>
+      </c>
     </row>
     <row r="24">
-      <c r="B24" s="3" t="inlineStr">
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>Fast-charge berth — dedicated fast-charge berth slot + utility demand charges (Assumptions default; overridable per market). Separate from per-kWh energy and berth/port admin.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="B25" s="2" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>From demand pool to fleet &amp; market size</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="B27" s="5" t="inlineStr">
+        <is>
+          <t>Navier serviceable rides/yr = corridor demand pool × capture rate (10% on contested corridors; ~90% on captive sole-operator transfer legs — see the per-row Capture % column)</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>Vessels supported = FLOOR(Navier rides/yr ÷ pax/yr per boat);  Market rev = vessels × rev/boat. The 'Market sizing' tab rolls these up into the SOM → SAM → TAM ladder.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="B29" s="2" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>The scenario toggle (what we flex)</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>'Corridor economics' has a SCENARIO cell = THIN / MID / FULL. It flexes load factor (occupancy) and revenue-leg factor (share of legs that earn full fare). Max trips/day is fixed across all three bands (see Assumptions). MID is the headline. Change SCENARIO and the whole model recomputes. Payback THIN/MID/FULL columns always show all three at once.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="B32" s="2" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="B33" s="3" t="inlineStr">
         <is>
           <t>Colour &amp; provenance legend</t>
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="B25" s="6" t="inlineStr">
+    <row r="34">
+      <c r="B34" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">   Yellow = INPUTS you can change (fare, distance, demand, weather).</t>
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="B26" s="7" t="inlineStr">
+    <row r="35">
+      <c r="B35" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">   Green  = COMPUTED by formula.</t>
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="B27" s="2" t="inlineStr">
+    <row r="36">
+      <c r="B36" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">   Every fare &amp; demand figure carries a Source tier (T1 official → T5 modeled) + Confidence (high/med/low). Null beats a wrong number: no published pool → blank, not a guess.</t>
         </is>
@@ -874,7 +933,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F37"/>
+  <dimension ref="A1:F40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -1363,11 +1422,11 @@
     <row r="21">
       <c r="A21" s="11" t="inlineStr">
         <is>
-          <t>Insurance (% of capex/yr)</t>
+          <t>Mechanical uptime</t>
         </is>
       </c>
       <c r="B21" s="17" t="n">
-        <v>0.025</v>
+        <v>0.75</v>
       </c>
       <c r="C21" s="13" t="inlineStr">
         <is>
@@ -1376,7 +1435,7 @@
       </c>
       <c r="D21" s="13" t="inlineStr">
         <is>
-          <t>T3</t>
+          <t>T4</t>
         </is>
       </c>
       <c r="E21" s="13" t="inlineStr">
@@ -1386,29 +1445,25 @@
       </c>
       <c r="F21" s="14" t="inlineStr">
         <is>
-          <t>H&amp;M + P&amp;I for a commercial passenger vessel ~2.5%/yr of capex; scales with regional capex overrides (Jaideep 2026-06-19).</t>
+          <t>Blade luxury aviation ~75-80% reliability uptime</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="11" t="inlineStr">
         <is>
-          <t>Charging &amp; berth (additional to marina+energy)</t>
-        </is>
-      </c>
-      <c r="B22" s="15" t="n">
-        <v>18000</v>
+          <t>Navier capture rate</t>
+        </is>
+      </c>
+      <c r="B22" s="17" t="n">
+        <v>0.1</v>
       </c>
       <c r="C22" s="13" t="inlineStr">
         <is>
-          <t>USD/yr</t>
-        </is>
-      </c>
-      <c r="D22" s="13" t="inlineStr">
-        <is>
-          <t>T3</t>
-        </is>
-      </c>
+          <t>frac</t>
+        </is>
+      </c>
+      <c r="D22" s="13" t="inlineStr"/>
       <c r="E22" s="13" t="inlineStr">
         <is>
           <t>med</t>
@@ -1416,29 +1471,25 @@
       </c>
       <c r="F22" s="14" t="inlineStr">
         <is>
-          <t>Dedicated fast-charge berth + demand charges, ADDITIONAL to marina overhead and energy (Jaideep 2026-06-19). L3-overridable.</t>
+          <t>Navier wins ~10% of a CONTESTED corridor demand pool (locked). Captive sole-operator transfer legs (captive:true / luxury_charter / hospitality archetypes) carry the captive rate instead — see per-row Capture %.</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="11" t="inlineStr">
         <is>
-          <t>Mechanical uptime</t>
+          <t>Captive capture rate (A′ corridors)</t>
         </is>
       </c>
       <c r="B23" s="17" t="n">
-        <v>0.75</v>
+        <v>0.9</v>
       </c>
       <c r="C23" s="13" t="inlineStr">
         <is>
           <t>frac</t>
         </is>
       </c>
-      <c r="D23" s="13" t="inlineStr">
-        <is>
-          <t>T4</t>
-        </is>
-      </c>
+      <c r="D23" s="13" t="inlineStr"/>
       <c r="E23" s="13" t="inlineStr">
         <is>
           <t>med</t>
@@ -1446,255 +1497,303 @@
       </c>
       <c r="F23" s="14" t="inlineStr">
         <is>
-          <t>Blade luxury aviation ~75-80% reliability uptime</t>
+          <t>Sole-operator water-access-only transfer legs (captive:true or luxury_charter/hospitality archetype): Navier IS the transfer fleet — capture ~90%. Applied per-row in the Capture % column.</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="11" t="inlineStr">
         <is>
-          <t>Navier capture rate</t>
-        </is>
-      </c>
-      <c r="B24" s="17" t="n">
-        <v>0.1</v>
+          <t>Discount factor (vs comparable fare)</t>
+        </is>
+      </c>
+      <c r="B24" s="16" t="n">
+        <v>1</v>
       </c>
       <c r="C24" s="13" t="inlineStr">
         <is>
           <t>frac</t>
         </is>
       </c>
-      <c r="D24" s="13" t="inlineStr"/>
+      <c r="D24" s="13" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
       <c r="E24" s="13" t="inlineStr">
         <is>
-          <t>med</t>
+          <t>high</t>
         </is>
       </c>
       <c r="F24" s="14" t="inlineStr">
         <is>
-          <t>Navier wins ~10% of a CONTESTED corridor demand pool (locked). Captive sole-operator transfer legs (captive:true / luxury_charter / hospitality archetypes) carry the captive rate instead — see per-row Capture %.</t>
+          <t>Market parity — better product, not cheaper (locked).</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="11" t="inlineStr">
         <is>
-          <t>Captive capture rate (A′ corridors)</t>
-        </is>
-      </c>
-      <c r="B25" s="17" t="n">
-        <v>0.9</v>
+          <t>Diesel CO₂ per gallon</t>
+        </is>
+      </c>
+      <c r="B25" s="16" t="n">
+        <v>10.21</v>
       </c>
       <c r="C25" s="13" t="inlineStr">
         <is>
+          <t>kg/gal</t>
+        </is>
+      </c>
+      <c r="D25" s="13" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="E25" s="13" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="F25" s="14" t="inlineStr">
+        <is>
+          <t>US EPA: 10.21 kg CO2 per gallon marine/diesel</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="9" t="inlineStr">
+        <is>
+          <t>OPEX defaults  (global fallbacks — localized energy, crew, berth admin on Country opex tab)</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="10" t="inlineStr">
+        <is>
+          <t>Parameter</t>
+        </is>
+      </c>
+      <c r="B28" s="10" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+      <c r="C28" s="10" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="D28" s="10" t="inlineStr">
+        <is>
+          <t>Tier</t>
+        </is>
+      </c>
+      <c r="E28" s="10" t="inlineStr">
+        <is>
+          <t>Conf.</t>
+        </is>
+      </c>
+      <c r="F28" s="10" t="inlineStr">
+        <is>
+          <t>Source / note</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="11" t="inlineStr">
+        <is>
+          <t>Vessel insurance — H&amp;M + P&amp;I (% of CAPEX/yr)</t>
+        </is>
+      </c>
+      <c r="B29" s="17" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="C29" s="13" t="inlineStr">
+        <is>
           <t>frac</t>
         </is>
       </c>
-      <c r="D25" s="13" t="inlineStr"/>
-      <c r="E25" s="13" t="inlineStr">
+      <c r="D29" s="13" t="inlineStr">
+        <is>
+          <t>T3</t>
+        </is>
+      </c>
+      <c r="E29" s="13" t="inlineStr">
         <is>
           <t>med</t>
         </is>
       </c>
-      <c r="F25" s="14" t="inlineStr">
-        <is>
-          <t>Sole-operator water-access-only transfer legs (captive:true or luxury_charter/hospitality archetype): Navier IS the transfer fleet — capture ~90%. Applied per-row in the Capture % column.</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="11" t="inlineStr">
-        <is>
-          <t>Discount factor (vs comparable fare)</t>
-        </is>
-      </c>
-      <c r="B26" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="C26" s="13" t="inlineStr">
-        <is>
-          <t>frac</t>
-        </is>
-      </c>
-      <c r="D26" s="13" t="inlineStr">
-        <is>
-          <t>T1</t>
-        </is>
-      </c>
-      <c r="E26" s="13" t="inlineStr">
-        <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="F26" s="14" t="inlineStr">
-        <is>
-          <t>Market parity — better product, not cheaper (locked).</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="11" t="inlineStr">
-        <is>
-          <t>Diesel CO₂ per gallon</t>
-        </is>
-      </c>
-      <c r="B27" s="16" t="n">
-        <v>10.21</v>
-      </c>
-      <c r="C27" s="13" t="inlineStr">
-        <is>
-          <t>kg/gal</t>
-        </is>
-      </c>
-      <c r="D27" s="13" t="inlineStr">
-        <is>
-          <t>T1</t>
-        </is>
-      </c>
-      <c r="E27" s="13" t="inlineStr">
-        <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="F27" s="14" t="inlineStr">
-        <is>
-          <t>US EPA: 10.21 kg CO2 per gallon marine/diesel</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="9" t="inlineStr">
-        <is>
-          <t>Utilization scenarios  (the two levers we flex)</t>
+      <c r="F29" s="14" t="inlineStr">
+        <is>
+          <t>Commercial vessel H&amp;M + P&amp;I ~2.5%/yr of regional CAPEX. Separate from berth/port admin in Country opex (Jaideep 2026-06-19).. Multiplied by regional CAPEX (Country opex col G). Not included in berth/port admin.</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="10" t="inlineStr">
+      <c r="A30" s="11" t="inlineStr">
+        <is>
+          <t>Fast-charge berth &amp; demand charges (global default)</t>
+        </is>
+      </c>
+      <c r="B30" s="15" t="n">
+        <v>18000</v>
+      </c>
+      <c r="C30" s="13" t="inlineStr">
+        <is>
+          <t>USD/yr</t>
+        </is>
+      </c>
+      <c r="D30" s="13" t="inlineStr">
+        <is>
+          <t>T3</t>
+        </is>
+      </c>
+      <c r="E30" s="13" t="inlineStr">
+        <is>
+          <t>med</t>
+        </is>
+      </c>
+      <c r="F30" s="14" t="inlineStr">
+        <is>
+          <t>Dedicated fast-charge berth slot + utility demand charges. Excludes per-kWh propulsion energy and berth/port admin (Jaideep 2026-06-19). L3-overridable per market.. Dedicated charge berth + utility demand charges. Excludes per-kWh propulsion energy and berth/port admin. L3-overridable per market.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="9" t="inlineStr">
+        <is>
+          <t>Utilization scenarios  (load factor + revenue-leg factor)</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="10" t="inlineStr">
         <is>
           <t>Scenario</t>
         </is>
       </c>
-      <c r="B30" s="10" t="inlineStr">
+      <c r="B33" s="10" t="inlineStr">
         <is>
           <t>Load factor</t>
         </is>
       </c>
-      <c r="C30" s="10" t="inlineStr">
+      <c r="C33" s="10" t="inlineStr">
         <is>
           <t>Rev-leg factor</t>
         </is>
       </c>
-      <c r="D30" s="10" t="inlineStr"/>
-      <c r="E30" s="10" t="inlineStr"/>
-      <c r="F30" s="10" t="inlineStr">
+      <c r="D33" s="10" t="inlineStr"/>
+      <c r="E33" s="10" t="inlineStr"/>
+      <c r="F33" s="10" t="inlineStr">
         <is>
           <t>Note</t>
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" s="18" t="inlineStr">
+    <row r="34">
+      <c r="A34" s="18" t="inlineStr">
         <is>
           <t>THIN</t>
         </is>
       </c>
-      <c r="B31" s="19" t="n">
+      <c r="B34" s="19" t="n">
         <v>0.45</v>
       </c>
-      <c r="C31" s="19" t="n">
+      <c r="C34" s="19" t="n">
         <v>0.55</v>
       </c>
-      <c r="F31" s="14" t="inlineStr">
+      <c r="F34" s="14" t="inlineStr">
         <is>
           <t>thin/one-way/seasonal corridor — conservative floor</t>
         </is>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" s="18" t="inlineStr">
+    <row r="35">
+      <c r="A35" s="18" t="inlineStr">
         <is>
           <t>MID</t>
         </is>
       </c>
-      <c r="B32" s="19" t="n">
+      <c r="B35" s="19" t="n">
         <v>0.55</v>
       </c>
-      <c r="C32" s="19" t="n">
+      <c r="C35" s="19" t="n">
         <v>0.65</v>
       </c>
-      <c r="F32" s="14" t="inlineStr">
+      <c r="F35" s="14" t="inlineStr">
         <is>
           <t>HEADLINE — realistic busy two-way corridor</t>
         </is>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" s="18" t="inlineStr">
+    <row r="36">
+      <c r="A36" s="18" t="inlineStr">
         <is>
           <t>FULL</t>
         </is>
       </c>
-      <c r="B33" s="19" t="n">
+      <c r="B36" s="19" t="n">
         <v>0.7</v>
       </c>
-      <c r="C33" s="19" t="n">
+      <c r="C36" s="19" t="n">
         <v>0.75</v>
       </c>
-      <c r="F33" s="14" t="inlineStr">
+      <c r="F36" s="14" t="inlineStr">
         <is>
           <t>mature/dense corridor — optimistic ceiling</t>
         </is>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" s="20" t="inlineStr">
+    <row r="38">
+      <c r="A38" s="20" t="inlineStr">
         <is>
           <t>SCENARIO (toggle me)</t>
         </is>
       </c>
-      <c r="B35" s="21" t="inlineStr">
+      <c r="B38" s="21" t="inlineStr">
         <is>
           <t>MID</t>
         </is>
       </c>
-      <c r="C35" s="22" t="inlineStr">
+      <c r="C38" s="22" t="inlineStr">
         <is>
           <t>← set THIN / MID / FULL</t>
         </is>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" s="11" t="inlineStr">
+    <row r="39">
+      <c r="A39" s="11" t="inlineStr">
         <is>
           <t>Selected load factor</t>
         </is>
       </c>
-      <c r="B36" s="23">
-        <f>VLOOKUP(scenario,'Assumptions'!$A$31:$C$33,2,FALSE)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="11" t="inlineStr">
+      <c r="B39" s="23">
+        <f>VLOOKUP(scenario,'Assumptions'!$A$34:$C$36,2,FALSE)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="11" t="inlineStr">
         <is>
           <t>Selected rev-leg factor</t>
         </is>
       </c>
-      <c r="B37" s="23">
-        <f>VLOOKUP(scenario,'Assumptions'!$A$31:$C$33,3,FALSE)</f>
+      <c r="B40" s="23">
+        <f>VLOOKUP(scenario,'Assumptions'!$A$34:$C$36,3,FALSE)</f>
         <v/>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="4">
-    <mergeCell ref="A3:F3"/>
+  <mergeCells count="5">
     <mergeCell ref="A14:F14"/>
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A29:F29"/>
+    <mergeCell ref="A32:F32"/>
+    <mergeCell ref="A27:F27"/>
+    <mergeCell ref="A3:F3"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation sqref="B35" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
+    <dataValidation sqref="B38" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
       <formula1>"THIN,MID,FULL"</formula1>
     </dataValidation>
   </dataValidations>
@@ -1724,7 +1823,7 @@
     <row r="1">
       <c r="A1" s="8" t="inlineStr">
         <is>
-          <t>Country opex — L3 localized layer (VLOOKUP target for the engine)</t>
+          <t>Country opex — localized inputs (crew, energy, berth admin, CAPEX)</t>
         </is>
       </c>
     </row>
@@ -1751,7 +1850,7 @@
       </c>
       <c r="E3" s="24" t="inlineStr">
         <is>
-          <t>Marina $/yr</t>
+          <t>Berth &amp; port admin $/yr</t>
         </is>
       </c>
       <c r="F3" s="24" t="inlineStr">
@@ -1766,7 +1865,7 @@
       </c>
       <c r="H3" s="24" t="inlineStr">
         <is>
-          <t>Source notes (captain | energy | marina)</t>
+          <t>Source notes (crew | energy | berth admin)</t>
         </is>
       </c>
     </row>
@@ -1839,10 +1938,10 @@
     <col width="11" customWidth="1" min="20" max="20"/>
     <col width="10" customWidth="1" min="21" max="21"/>
     <col width="10" customWidth="1" min="22" max="22"/>
-    <col width="10" customWidth="1" min="23" max="23"/>
+    <col width="12" customWidth="1" min="23" max="23"/>
     <col width="9" customWidth="1" min="24" max="24"/>
-    <col width="10" customWidth="1" min="25" max="25"/>
-    <col width="11" customWidth="1" min="26" max="26"/>
+    <col width="12" customWidth="1" min="25" max="25"/>
+    <col width="12" customWidth="1" min="26" max="26"/>
     <col width="11" customWidth="1" min="27" max="27"/>
     <col width="10" customWidth="1" min="28" max="28"/>
     <col width="11" customWidth="1" min="29" max="29"/>
@@ -2003,7 +2102,7 @@
       </c>
       <c r="W3" s="24" t="inlineStr">
         <is>
-          <t>Marina/yr</t>
+          <t>Berth &amp; port admin/yr</t>
         </is>
       </c>
       <c r="X3" s="24" t="inlineStr">
@@ -2013,12 +2112,12 @@
       </c>
       <c r="Y3" s="24" t="inlineStr">
         <is>
-          <t>Insurance/yr</t>
+          <t>Vessel insurance/yr</t>
         </is>
       </c>
       <c r="Z3" s="24" t="inlineStr">
         <is>
-          <t>Charge+berth/yr</t>
+          <t>Fast-charge berth/yr</t>
         </is>
       </c>
       <c r="AA3" s="24" t="inlineStr">

--- a/finance/_refresh_rakta.xlsx
+++ b/finance/_refresh_rakta.xlsx
@@ -44,9 +44,9 @@
     <definedName name="scenario">'Assumptions'!$B$38</definedName>
     <definedName name="load_sel">'Assumptions'!$B$39</definedName>
     <definedName name="revleg_sel">'Assumptions'!$B$40</definedName>
-    <definedName name="country_opex">'Country opex'!$A$4:$G$4</definedName>
-    <definedName name="som_floor_fleet">'Corridor economics'!$D$51</definedName>
-    <definedName name="som_floor_rev">'Corridor economics'!$E$51</definedName>
+    <definedName name="country_opex">'Country opex'!$A$4:$G$5</definedName>
+    <definedName name="som_floor_fleet">'Corridor economics'!$D$53</definedName>
+    <definedName name="som_floor_rev">'Corridor economics'!$E$53</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -188,7 +188,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="55">
+  <cellXfs count="57">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
@@ -324,6 +324,12 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="2" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -1807,7 +1813,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H4"/>
+  <dimension ref="A1:H5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1872,28 +1878,58 @@
     <row r="4">
       <c r="A4" s="25" t="inlineStr">
         <is>
-          <t>United Arab Emirates</t>
+          <t>Bahrain</t>
         </is>
       </c>
       <c r="B4" s="26" t="n">
-        <v>40000</v>
+        <v>36000</v>
       </c>
       <c r="C4" s="27" t="n">
-        <v>0.08500000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="D4" s="19" t="n">
-        <v>0.4</v>
+        <v>0.55</v>
       </c>
       <c r="E4" s="26" t="n">
-        <v>22000</v>
+        <v>15000</v>
       </c>
       <c r="F4" s="19" t="n">
-        <v>0.74</v>
+        <v>0.63</v>
       </c>
       <c r="G4" s="26" t="n">
         <v>600000</v>
       </c>
       <c r="H4" s="14" t="inlineStr">
+        <is>
+          <t>GCC expat marine crew, slightly below Saudi. Job ads (Instagram 2026): private boat captain BHD 250-350/mo (~$660-930/mo). Blended 1 commercial tourism-boat captain (~BHD 1,000/mo ~$2,650) + deckhand (~BHD 400/mo ~$1,060) fully-loaded (visa/accom provided) ~= ~$36k/vessel/yr @BHD 0.376. High-income GCC; just below Saudi $42k. | SUBSIDIZED. EWA non-subsidized (expat/commercial) rate 32 fils/kWh = BHD 0.032 = ~$0.085 (GulfInsider/Reddit 2026). GlobalPetrolPrices business BHD 0.029 = $0.077 (Sep 2025). Anchored $0.08. @BHD 0.376 (pegged). | Modeled berth+insurance+admin/vessel/yr. Bahrain marine ops (Manama/Marina) mid-high GCC; below Saudi $18k, above Taiwan $14k. Tagged low. | CAPEX LB-243 US/EU=$900K else $600K</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="25" t="inlineStr">
+        <is>
+          <t>United Arab Emirates</t>
+        </is>
+      </c>
+      <c r="B5" s="26" t="n">
+        <v>40000</v>
+      </c>
+      <c r="C5" s="27" t="n">
+        <v>0.08500000000000001</v>
+      </c>
+      <c r="D5" s="19" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="E5" s="26" t="n">
+        <v>22000</v>
+      </c>
+      <c r="F5" s="19" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="G5" s="26" t="n">
+        <v>600000</v>
+      </c>
+      <c r="H5" s="14" t="inlineStr">
         <is>
           <t>GCC expat marine crew (Dubai). Dubai yacht-group ads: captain AED 5,000-10,000/mo, deckhand AED 2,000-3,500/mo; Morgan &amp; Mallet GCC guide captain $4,200-7,200/mo, deckhand $1,550-2,300/mo. Blended 1 commercial tourism-boat captain (~AED 8,000/mo ~$2,180) + deckhand (~AED 3,000/mo ~$817) fully-loaded incl visa/accommodation/insurance ~= ~$40k/vessel/yr @AED 3.6725. High-income GCC; between Saudi $42k and Bahrain $36k. | DEWA commercial slab tariff AED 0.23/0.28/0.32 per kWh + ~6 fils fuel surcharge (DEWA 2025); utilitybilluae.com business band AED 0.20-0.38/kWh. Effective commercial ~AED 0.30-0.33 = ~$0.082-0.090 @AED 3.6725. Abu Dhabi (ADDC) commercial cheaper. Blended UAE commercial ~$0.085. Subsidized like other GCC but above Saudi $0.074. | Modeled berth+insurance+admin/vessel/yr. Dubai premium marinas (Dubai Marina, Dubai Harbour, Bluewaters) are among the most expensive GCC marine ops; above Saudi $18k and Singapore $20k. Tagged low. | CAPEX LB-243 US/EU=$900K else $600K</t>
         </is>
@@ -1913,7 +1949,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX56"/>
+  <dimension ref="A1:AY61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1958,14 +1994,15 @@
     <col width="9" customWidth="1" min="40" max="40"/>
     <col width="13" customWidth="1" min="41" max="41"/>
     <col width="26" customWidth="1" min="42" max="42"/>
-    <col width="16" customWidth="1" min="43" max="43"/>
+    <col width="14" customWidth="1" min="43" max="43"/>
     <col width="16" customWidth="1" min="44" max="44"/>
-    <col width="9" customWidth="1" min="45" max="45"/>
+    <col width="16" customWidth="1" min="45" max="45"/>
     <col width="9" customWidth="1" min="46" max="46"/>
     <col width="9" customWidth="1" min="47" max="47"/>
     <col width="9" customWidth="1" min="48" max="48"/>
-    <col width="50" customWidth="1" min="49" max="49"/>
+    <col width="9" customWidth="1" min="49" max="49"/>
     <col width="50" customWidth="1" min="50" max="50"/>
+    <col width="50" customWidth="1" min="51" max="51"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2202,40 +2239,45 @@
       </c>
       <c r="AQ3" s="24" t="inlineStr">
         <is>
+          <t>Floor bucket (aggregate status)</t>
+        </is>
+      </c>
+      <c r="AR3" s="24" t="inlineStr">
+        <is>
           <t>Forward SAM (2030-dated; held OUT of grounded floor)</t>
         </is>
       </c>
-      <c r="AR3" s="24" t="inlineStr">
+      <c r="AS3" s="24" t="inlineStr">
         <is>
           <t>Upside tier (LB-99; held OUT of grounded floor)</t>
         </is>
       </c>
-      <c r="AS3" s="24" t="inlineStr">
+      <c r="AT3" s="24" t="inlineStr">
         <is>
           <t>Fleet ceiling (captive villas/25)</t>
         </is>
       </c>
-      <c r="AT3" s="24" t="inlineStr">
+      <c r="AU3" s="24" t="inlineStr">
         <is>
           <t>Payback THIN</t>
         </is>
       </c>
-      <c r="AU3" s="24" t="inlineStr">
+      <c r="AV3" s="24" t="inlineStr">
         <is>
           <t>Payback MID</t>
         </is>
       </c>
-      <c r="AV3" s="24" t="inlineStr">
+      <c r="AW3" s="24" t="inlineStr">
         <is>
           <t>Payback FULL</t>
         </is>
       </c>
-      <c r="AW3" s="24" t="inlineStr">
+      <c r="AX3" s="24" t="inlineStr">
         <is>
           <t>Fare source (provenance)</t>
         </is>
       </c>
-      <c r="AX3" s="24" t="inlineStr">
+      <c r="AY3" s="24" t="inlineStr">
         <is>
           <t>Demand source (provenance)</t>
         </is>
@@ -2249,30 +2291,20 @@
       </c>
       <c r="B4" s="29" t="inlineStr">
         <is>
-          <t>United Arab Emirates</t>
+          <t>Bahrain</t>
         </is>
       </c>
       <c r="C4" s="30" t="inlineStr">
         <is>
-          <t>Al Marjan Island public arrival marina → Rixos Bab Al Bahr beach jetty</t>
+          <t>Sitra (Ad-Dur) Hawar Ferry Terminal → Bahrain Yacht Club</t>
         </is>
       </c>
       <c r="D4" s="31" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="E4" s="26" t="n">
-        <v>35</v>
-      </c>
-      <c r="F4" s="32" t="inlineStr">
-        <is>
-          <t>T3</t>
-        </is>
-      </c>
-      <c r="G4" s="32" t="inlineStr">
-        <is>
-          <t>med-low</t>
-        </is>
-      </c>
+        <v>1.2</v>
+      </c>
+      <c r="E4" s="26" t="n"/>
+      <c r="F4" s="32" t="n"/>
+      <c r="G4" s="32" t="n"/>
       <c r="H4" s="19" t="n">
         <v>1</v>
       </c>
@@ -2372,19 +2404,9 @@
         <f>((D4*O4/diesel_nmpg)*diesel_co2pg-(battery/range_nm)*D4*O4*VLOOKUP(B4,country_opex,4,FALSE))/1000</f>
         <v/>
       </c>
-      <c r="AG4" s="31" t="n">
-        <v>5217</v>
-      </c>
-      <c r="AH4" s="32" t="inlineStr">
-        <is>
-          <t>T3</t>
-        </is>
-      </c>
-      <c r="AI4" s="32" t="inlineStr">
-        <is>
-          <t>med-low</t>
-        </is>
-      </c>
+      <c r="AG4" s="31" t="n"/>
+      <c r="AH4" s="32" t="n"/>
+      <c r="AI4" s="32" t="n"/>
       <c r="AJ4" s="39" t="n">
         <v>0.1</v>
       </c>
@@ -2393,7 +2415,7 @@
         <v/>
       </c>
       <c r="AL4" s="34">
-        <f>IF(OR(AG4="",R4=0),"",MIN(IF(AS4="",9.9E+99,AS4),FLOOR(AK4/R4,1)))</f>
+        <f>IF(OR(AG4="",R4=0),"",MIN(IF(AT4="",9.9E+99,AT4),FLOOR(AK4/R4,1)))</f>
         <v/>
       </c>
       <c r="AM4" s="38">
@@ -2401,7 +2423,7 @@
         <v/>
       </c>
       <c r="AN4" s="36">
-        <f>IF(OR(AG4="",R4=0),"",MIN(IF(AS4="",9.9E+99,AS4),AK4/R4))</f>
+        <f>IF(OR(AG4="",R4=0),"",MIN(IF(AT4="",9.9E+99,AT4),AK4/R4))</f>
         <v/>
       </c>
       <c r="AO4" s="38">
@@ -2409,23 +2431,28 @@
         <v/>
       </c>
       <c r="AP4" s="40" t="n"/>
-      <c r="AQ4" s="41" t="n"/>
+      <c r="AQ4" s="32" t="inlineStr">
+        <is>
+          <t>Estimated</t>
+        </is>
+      </c>
       <c r="AR4" s="41" t="n"/>
-      <c r="AS4" s="42" t="n"/>
-      <c r="AT4" s="43">
+      <c r="AS4" s="41" t="n"/>
+      <c r="AT4" s="42" t="n"/>
+      <c r="AU4" s="43">
         <f>IF(((S4*pax_cap*load_thin*ROUND(K4*L4*revleg_thin,0))-(((battery/range_nm)*D4*ROUND(K4*L4*revleg_thin,0)*VLOOKUP(B4,country_opex,3,FALSE))+V4+W4+X4+Y4+Z4))&lt;=0,"",VLOOKUP(B4,country_opex,7,FALSE)/((S4*pax_cap*load_thin*ROUND(K4*L4*revleg_thin,0))-(((battery/range_nm)*D4*ROUND(K4*L4*revleg_thin,0)*VLOOKUP(B4,country_opex,3,FALSE))+V4+W4+X4+Y4+Z4)))</f>
         <v/>
       </c>
-      <c r="AU4" s="43">
+      <c r="AV4" s="43">
         <f>IF(((S4*pax_cap*load_mid*ROUND(K4*L4*revleg_mid,0))-(((battery/range_nm)*D4*ROUND(K4*L4*revleg_mid,0)*VLOOKUP(B4,country_opex,3,FALSE))+V4+W4+X4+Y4+Z4))&lt;=0,"",VLOOKUP(B4,country_opex,7,FALSE)/((S4*pax_cap*load_mid*ROUND(K4*L4*revleg_mid,0))-(((battery/range_nm)*D4*ROUND(K4*L4*revleg_mid,0)*VLOOKUP(B4,country_opex,3,FALSE))+V4+W4+X4+Y4+Z4)))</f>
         <v/>
       </c>
-      <c r="AV4" s="43">
+      <c r="AW4" s="43">
         <f>IF(((S4*pax_cap*load_full*ROUND(K4*L4*revleg_full,0))-(((battery/range_nm)*D4*ROUND(K4*L4*revleg_full,0)*VLOOKUP(B4,country_opex,3,FALSE))+V4+W4+X4+Y4+Z4))&lt;=0,"",VLOOKUP(B4,country_opex,7,FALSE)/((S4*pax_cap*load_full*ROUND(K4*L4*revleg_full,0))-(((battery/range_nm)*D4*ROUND(K4*L4*revleg_full,0)*VLOOKUP(B4,country_opex,3,FALSE))+V4+W4+X4+Y4+Z4)))</f>
         <v/>
       </c>
-      <c r="AW4" s="44" t="n"/>
       <c r="AX4" s="44" t="n"/>
+      <c r="AY4" s="44" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="29" t="inlineStr">
@@ -2435,30 +2462,20 @@
       </c>
       <c r="B5" s="29" t="inlineStr">
         <is>
-          <t>United Arab Emirates</t>
+          <t>Bahrain</t>
         </is>
       </c>
       <c r="C5" s="30" t="inlineStr">
         <is>
-          <t>Ras Al Khaimah Harbour → RAK Corniche public pier</t>
+          <t>Manama → Eastern Province</t>
         </is>
       </c>
       <c r="D5" s="31" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="E5" s="26" t="n">
-        <v>35</v>
-      </c>
-      <c r="F5" s="32" t="inlineStr">
-        <is>
-          <t>T3</t>
-        </is>
-      </c>
-      <c r="G5" s="32" t="inlineStr">
-        <is>
-          <t>med-low</t>
-        </is>
-      </c>
+        <v>21.2</v>
+      </c>
+      <c r="E5" s="26" t="n"/>
+      <c r="F5" s="32" t="n"/>
+      <c r="G5" s="32" t="n"/>
       <c r="H5" s="19" t="n">
         <v>1</v>
       </c>
@@ -2558,19 +2575,9 @@
         <f>((D5*O5/diesel_nmpg)*diesel_co2pg-(battery/range_nm)*D5*O5*VLOOKUP(B5,country_opex,4,FALSE))/1000</f>
         <v/>
       </c>
-      <c r="AG5" s="31" t="n">
-        <v>5217</v>
-      </c>
-      <c r="AH5" s="32" t="inlineStr">
-        <is>
-          <t>T3</t>
-        </is>
-      </c>
-      <c r="AI5" s="32" t="inlineStr">
-        <is>
-          <t>med-low</t>
-        </is>
-      </c>
+      <c r="AG5" s="31" t="n"/>
+      <c r="AH5" s="32" t="n"/>
+      <c r="AI5" s="32" t="n"/>
       <c r="AJ5" s="39" t="n">
         <v>0.1</v>
       </c>
@@ -2579,7 +2586,7 @@
         <v/>
       </c>
       <c r="AL5" s="34">
-        <f>IF(OR(AG5="",R5=0),"",MIN(IF(AS5="",9.9E+99,AS5),FLOOR(AK5/R5,1)))</f>
+        <f>IF(OR(AG5="",R5=0),"",MIN(IF(AT5="",9.9E+99,AT5),FLOOR(AK5/R5,1)))</f>
         <v/>
       </c>
       <c r="AM5" s="38">
@@ -2587,7 +2594,7 @@
         <v/>
       </c>
       <c r="AN5" s="36">
-        <f>IF(OR(AG5="",R5=0),"",MIN(IF(AS5="",9.9E+99,AS5),AK5/R5))</f>
+        <f>IF(OR(AG5="",R5=0),"",MIN(IF(AT5="",9.9E+99,AT5),AK5/R5))</f>
         <v/>
       </c>
       <c r="AO5" s="38">
@@ -2595,23 +2602,28 @@
         <v/>
       </c>
       <c r="AP5" s="40" t="n"/>
-      <c r="AQ5" s="41" t="n"/>
+      <c r="AQ5" s="32" t="inlineStr">
+        <is>
+          <t>Estimated</t>
+        </is>
+      </c>
       <c r="AR5" s="41" t="n"/>
-      <c r="AS5" s="42" t="n"/>
-      <c r="AT5" s="43">
+      <c r="AS5" s="41" t="n"/>
+      <c r="AT5" s="42" t="n"/>
+      <c r="AU5" s="43">
         <f>IF(((S5*pax_cap*load_thin*ROUND(K5*L5*revleg_thin,0))-(((battery/range_nm)*D5*ROUND(K5*L5*revleg_thin,0)*VLOOKUP(B5,country_opex,3,FALSE))+V5+W5+X5+Y5+Z5))&lt;=0,"",VLOOKUP(B5,country_opex,7,FALSE)/((S5*pax_cap*load_thin*ROUND(K5*L5*revleg_thin,0))-(((battery/range_nm)*D5*ROUND(K5*L5*revleg_thin,0)*VLOOKUP(B5,country_opex,3,FALSE))+V5+W5+X5+Y5+Z5)))</f>
         <v/>
       </c>
-      <c r="AU5" s="43">
+      <c r="AV5" s="43">
         <f>IF(((S5*pax_cap*load_mid*ROUND(K5*L5*revleg_mid,0))-(((battery/range_nm)*D5*ROUND(K5*L5*revleg_mid,0)*VLOOKUP(B5,country_opex,3,FALSE))+V5+W5+X5+Y5+Z5))&lt;=0,"",VLOOKUP(B5,country_opex,7,FALSE)/((S5*pax_cap*load_mid*ROUND(K5*L5*revleg_mid,0))-(((battery/range_nm)*D5*ROUND(K5*L5*revleg_mid,0)*VLOOKUP(B5,country_opex,3,FALSE))+V5+W5+X5+Y5+Z5)))</f>
         <v/>
       </c>
-      <c r="AV5" s="43">
+      <c r="AW5" s="43">
         <f>IF(((S5*pax_cap*load_full*ROUND(K5*L5*revleg_full,0))-(((battery/range_nm)*D5*ROUND(K5*L5*revleg_full,0)*VLOOKUP(B5,country_opex,3,FALSE))+V5+W5+X5+Y5+Z5))&lt;=0,"",VLOOKUP(B5,country_opex,7,FALSE)/((S5*pax_cap*load_full*ROUND(K5*L5*revleg_full,0))-(((battery/range_nm)*D5*ROUND(K5*L5*revleg_full,0)*VLOOKUP(B5,country_opex,3,FALSE))+V5+W5+X5+Y5+Z5)))</f>
         <v/>
       </c>
-      <c r="AW5" s="44" t="n"/>
       <c r="AX5" s="44" t="n"/>
+      <c r="AY5" s="44" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="29" t="inlineStr">
@@ -2626,11 +2638,11 @@
       </c>
       <c r="C6" s="30" t="inlineStr">
         <is>
-          <t>Marjan Island Resort &amp; Spa beach jetty → Hampton by Hilton Marjan Island beach landing</t>
+          <t>Al Marjan Island public arrival marina → Rixos Bab Al Bahr beach jetty</t>
         </is>
       </c>
       <c r="D6" s="31" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="E6" s="26" t="n">
         <v>35</v>
@@ -2765,7 +2777,7 @@
         <v/>
       </c>
       <c r="AL6" s="34">
-        <f>IF(OR(AG6="",R6=0),"",MIN(IF(AS6="",9.9E+99,AS6),FLOOR(AK6/R6,1)))</f>
+        <f>IF(OR(AG6="",R6=0),"",MIN(IF(AT6="",9.9E+99,AT6),FLOOR(AK6/R6,1)))</f>
         <v/>
       </c>
       <c r="AM6" s="38">
@@ -2773,7 +2785,7 @@
         <v/>
       </c>
       <c r="AN6" s="36">
-        <f>IF(OR(AG6="",R6=0),"",MIN(IF(AS6="",9.9E+99,AS6),AK6/R6))</f>
+        <f>IF(OR(AG6="",R6=0),"",MIN(IF(AT6="",9.9E+99,AT6),AK6/R6))</f>
         <v/>
       </c>
       <c r="AO6" s="38">
@@ -2781,23 +2793,28 @@
         <v/>
       </c>
       <c r="AP6" s="40" t="n"/>
-      <c r="AQ6" s="41" t="n"/>
+      <c r="AQ6" s="32" t="inlineStr">
+        <is>
+          <t>Grounded</t>
+        </is>
+      </c>
       <c r="AR6" s="41" t="n"/>
-      <c r="AS6" s="42" t="n"/>
-      <c r="AT6" s="43">
+      <c r="AS6" s="41" t="n"/>
+      <c r="AT6" s="42" t="n"/>
+      <c r="AU6" s="43">
         <f>IF(((S6*pax_cap*load_thin*ROUND(K6*L6*revleg_thin,0))-(((battery/range_nm)*D6*ROUND(K6*L6*revleg_thin,0)*VLOOKUP(B6,country_opex,3,FALSE))+V6+W6+X6+Y6+Z6))&lt;=0,"",VLOOKUP(B6,country_opex,7,FALSE)/((S6*pax_cap*load_thin*ROUND(K6*L6*revleg_thin,0))-(((battery/range_nm)*D6*ROUND(K6*L6*revleg_thin,0)*VLOOKUP(B6,country_opex,3,FALSE))+V6+W6+X6+Y6+Z6)))</f>
         <v/>
       </c>
-      <c r="AU6" s="43">
+      <c r="AV6" s="43">
         <f>IF(((S6*pax_cap*load_mid*ROUND(K6*L6*revleg_mid,0))-(((battery/range_nm)*D6*ROUND(K6*L6*revleg_mid,0)*VLOOKUP(B6,country_opex,3,FALSE))+V6+W6+X6+Y6+Z6))&lt;=0,"",VLOOKUP(B6,country_opex,7,FALSE)/((S6*pax_cap*load_mid*ROUND(K6*L6*revleg_mid,0))-(((battery/range_nm)*D6*ROUND(K6*L6*revleg_mid,0)*VLOOKUP(B6,country_opex,3,FALSE))+V6+W6+X6+Y6+Z6)))</f>
         <v/>
       </c>
-      <c r="AV6" s="43">
+      <c r="AW6" s="43">
         <f>IF(((S6*pax_cap*load_full*ROUND(K6*L6*revleg_full,0))-(((battery/range_nm)*D6*ROUND(K6*L6*revleg_full,0)*VLOOKUP(B6,country_opex,3,FALSE))+V6+W6+X6+Y6+Z6))&lt;=0,"",VLOOKUP(B6,country_opex,7,FALSE)/((S6*pax_cap*load_full*ROUND(K6*L6*revleg_full,0))-(((battery/range_nm)*D6*ROUND(K6*L6*revleg_full,0)*VLOOKUP(B6,country_opex,3,FALSE))+V6+W6+X6+Y6+Z6)))</f>
         <v/>
       </c>
-      <c r="AW6" s="44" t="n"/>
       <c r="AX6" s="44" t="n"/>
+      <c r="AY6" s="44" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="29" t="inlineStr">
@@ -2812,11 +2829,11 @@
       </c>
       <c r="C7" s="30" t="inlineStr">
         <is>
-          <t>Wynn Al Marjan Island arrival lagoon → Marjan Island Resort &amp; Spa beach jetty</t>
+          <t>Marjan Island Resort &amp; Spa beach jetty → Hampton by Hilton Marjan Island beach landing</t>
         </is>
       </c>
       <c r="D7" s="31" t="n">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="E7" s="26" t="n">
         <v>35</v>
@@ -2951,7 +2968,7 @@
         <v/>
       </c>
       <c r="AL7" s="34">
-        <f>IF(OR(AG7="",R7=0),"",MIN(IF(AS7="",9.9E+99,AS7),FLOOR(AK7/R7,1)))</f>
+        <f>IF(OR(AG7="",R7=0),"",MIN(IF(AT7="",9.9E+99,AT7),FLOOR(AK7/R7,1)))</f>
         <v/>
       </c>
       <c r="AM7" s="38">
@@ -2959,7 +2976,7 @@
         <v/>
       </c>
       <c r="AN7" s="36">
-        <f>IF(OR(AG7="",R7=0),"",MIN(IF(AS7="",9.9E+99,AS7),AK7/R7))</f>
+        <f>IF(OR(AG7="",R7=0),"",MIN(IF(AT7="",9.9E+99,AT7),AK7/R7))</f>
         <v/>
       </c>
       <c r="AO7" s="38">
@@ -2967,23 +2984,28 @@
         <v/>
       </c>
       <c r="AP7" s="40" t="n"/>
-      <c r="AQ7" s="41" t="n"/>
+      <c r="AQ7" s="32" t="inlineStr">
+        <is>
+          <t>Grounded</t>
+        </is>
+      </c>
       <c r="AR7" s="41" t="n"/>
-      <c r="AS7" s="42" t="n"/>
-      <c r="AT7" s="43">
+      <c r="AS7" s="41" t="n"/>
+      <c r="AT7" s="42" t="n"/>
+      <c r="AU7" s="43">
         <f>IF(((S7*pax_cap*load_thin*ROUND(K7*L7*revleg_thin,0))-(((battery/range_nm)*D7*ROUND(K7*L7*revleg_thin,0)*VLOOKUP(B7,country_opex,3,FALSE))+V7+W7+X7+Y7+Z7))&lt;=0,"",VLOOKUP(B7,country_opex,7,FALSE)/((S7*pax_cap*load_thin*ROUND(K7*L7*revleg_thin,0))-(((battery/range_nm)*D7*ROUND(K7*L7*revleg_thin,0)*VLOOKUP(B7,country_opex,3,FALSE))+V7+W7+X7+Y7+Z7)))</f>
         <v/>
       </c>
-      <c r="AU7" s="43">
+      <c r="AV7" s="43">
         <f>IF(((S7*pax_cap*load_mid*ROUND(K7*L7*revleg_mid,0))-(((battery/range_nm)*D7*ROUND(K7*L7*revleg_mid,0)*VLOOKUP(B7,country_opex,3,FALSE))+V7+W7+X7+Y7+Z7))&lt;=0,"",VLOOKUP(B7,country_opex,7,FALSE)/((S7*pax_cap*load_mid*ROUND(K7*L7*revleg_mid,0))-(((battery/range_nm)*D7*ROUND(K7*L7*revleg_mid,0)*VLOOKUP(B7,country_opex,3,FALSE))+V7+W7+X7+Y7+Z7)))</f>
         <v/>
       </c>
-      <c r="AV7" s="43">
+      <c r="AW7" s="43">
         <f>IF(((S7*pax_cap*load_full*ROUND(K7*L7*revleg_full,0))-(((battery/range_nm)*D7*ROUND(K7*L7*revleg_full,0)*VLOOKUP(B7,country_opex,3,FALSE))+V7+W7+X7+Y7+Z7))&lt;=0,"",VLOOKUP(B7,country_opex,7,FALSE)/((S7*pax_cap*load_full*ROUND(K7*L7*revleg_full,0))-(((battery/range_nm)*D7*ROUND(K7*L7*revleg_full,0)*VLOOKUP(B7,country_opex,3,FALSE))+V7+W7+X7+Y7+Z7)))</f>
         <v/>
       </c>
-      <c r="AW7" s="44" t="n"/>
       <c r="AX7" s="44" t="n"/>
+      <c r="AY7" s="44" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="29" t="inlineStr">
@@ -2998,11 +3020,11 @@
       </c>
       <c r="C8" s="30" t="inlineStr">
         <is>
-          <t>Anantara Mina Al Arab Ras Al Khaimah Resort jetty → InterContinental Ras Al Khaimah Mina Al Arab Resort &amp; Spa jetty</t>
+          <t>Ras Al Khaimah Harbour → RAK Corniche public pier</t>
         </is>
       </c>
       <c r="D8" s="31" t="n">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="E8" s="26" t="n">
         <v>35</v>
@@ -3137,7 +3159,7 @@
         <v/>
       </c>
       <c r="AL8" s="34">
-        <f>IF(OR(AG8="",R8=0),"",MIN(IF(AS8="",9.9E+99,AS8),FLOOR(AK8/R8,1)))</f>
+        <f>IF(OR(AG8="",R8=0),"",MIN(IF(AT8="",9.9E+99,AT8),FLOOR(AK8/R8,1)))</f>
         <v/>
       </c>
       <c r="AM8" s="38">
@@ -3145,7 +3167,7 @@
         <v/>
       </c>
       <c r="AN8" s="36">
-        <f>IF(OR(AG8="",R8=0),"",MIN(IF(AS8="",9.9E+99,AS8),AK8/R8))</f>
+        <f>IF(OR(AG8="",R8=0),"",MIN(IF(AT8="",9.9E+99,AT8),AK8/R8))</f>
         <v/>
       </c>
       <c r="AO8" s="38">
@@ -3153,23 +3175,28 @@
         <v/>
       </c>
       <c r="AP8" s="40" t="n"/>
-      <c r="AQ8" s="41" t="n"/>
+      <c r="AQ8" s="32" t="inlineStr">
+        <is>
+          <t>Grounded</t>
+        </is>
+      </c>
       <c r="AR8" s="41" t="n"/>
-      <c r="AS8" s="42" t="n"/>
-      <c r="AT8" s="43">
+      <c r="AS8" s="41" t="n"/>
+      <c r="AT8" s="42" t="n"/>
+      <c r="AU8" s="43">
         <f>IF(((S8*pax_cap*load_thin*ROUND(K8*L8*revleg_thin,0))-(((battery/range_nm)*D8*ROUND(K8*L8*revleg_thin,0)*VLOOKUP(B8,country_opex,3,FALSE))+V8+W8+X8+Y8+Z8))&lt;=0,"",VLOOKUP(B8,country_opex,7,FALSE)/((S8*pax_cap*load_thin*ROUND(K8*L8*revleg_thin,0))-(((battery/range_nm)*D8*ROUND(K8*L8*revleg_thin,0)*VLOOKUP(B8,country_opex,3,FALSE))+V8+W8+X8+Y8+Z8)))</f>
         <v/>
       </c>
-      <c r="AU8" s="43">
+      <c r="AV8" s="43">
         <f>IF(((S8*pax_cap*load_mid*ROUND(K8*L8*revleg_mid,0))-(((battery/range_nm)*D8*ROUND(K8*L8*revleg_mid,0)*VLOOKUP(B8,country_opex,3,FALSE))+V8+W8+X8+Y8+Z8))&lt;=0,"",VLOOKUP(B8,country_opex,7,FALSE)/((S8*pax_cap*load_mid*ROUND(K8*L8*revleg_mid,0))-(((battery/range_nm)*D8*ROUND(K8*L8*revleg_mid,0)*VLOOKUP(B8,country_opex,3,FALSE))+V8+W8+X8+Y8+Z8)))</f>
         <v/>
       </c>
-      <c r="AV8" s="43">
+      <c r="AW8" s="43">
         <f>IF(((S8*pax_cap*load_full*ROUND(K8*L8*revleg_full,0))-(((battery/range_nm)*D8*ROUND(K8*L8*revleg_full,0)*VLOOKUP(B8,country_opex,3,FALSE))+V8+W8+X8+Y8+Z8))&lt;=0,"",VLOOKUP(B8,country_opex,7,FALSE)/((S8*pax_cap*load_full*ROUND(K8*L8*revleg_full,0))-(((battery/range_nm)*D8*ROUND(K8*L8*revleg_full,0)*VLOOKUP(B8,country_opex,3,FALSE))+V8+W8+X8+Y8+Z8)))</f>
         <v/>
       </c>
-      <c r="AW8" s="44" t="n"/>
       <c r="AX8" s="44" t="n"/>
+      <c r="AY8" s="44" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="29" t="inlineStr">
@@ -3184,11 +3211,11 @@
       </c>
       <c r="C9" s="30" t="inlineStr">
         <is>
-          <t>Al Hamra Marina &amp; Royal Yacht Club RAK → Waldorf Astoria Ras Al Khaimah jetty</t>
+          <t>Anantara Mina Al Arab Ras Al Khaimah Resort jetty → InterContinental Ras Al Khaimah Mina Al Arab Resort &amp; Spa jetty</t>
         </is>
       </c>
       <c r="D9" s="31" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="E9" s="26" t="n">
         <v>35</v>
@@ -3323,7 +3350,7 @@
         <v/>
       </c>
       <c r="AL9" s="34">
-        <f>IF(OR(AG9="",R9=0),"",MIN(IF(AS9="",9.9E+99,AS9),FLOOR(AK9/R9,1)))</f>
+        <f>IF(OR(AG9="",R9=0),"",MIN(IF(AT9="",9.9E+99,AT9),FLOOR(AK9/R9,1)))</f>
         <v/>
       </c>
       <c r="AM9" s="38">
@@ -3331,7 +3358,7 @@
         <v/>
       </c>
       <c r="AN9" s="36">
-        <f>IF(OR(AG9="",R9=0),"",MIN(IF(AS9="",9.9E+99,AS9),AK9/R9))</f>
+        <f>IF(OR(AG9="",R9=0),"",MIN(IF(AT9="",9.9E+99,AT9),AK9/R9))</f>
         <v/>
       </c>
       <c r="AO9" s="38">
@@ -3339,23 +3366,28 @@
         <v/>
       </c>
       <c r="AP9" s="40" t="n"/>
-      <c r="AQ9" s="41" t="n"/>
+      <c r="AQ9" s="32" t="inlineStr">
+        <is>
+          <t>Grounded</t>
+        </is>
+      </c>
       <c r="AR9" s="41" t="n"/>
-      <c r="AS9" s="42" t="n"/>
-      <c r="AT9" s="43">
+      <c r="AS9" s="41" t="n"/>
+      <c r="AT9" s="42" t="n"/>
+      <c r="AU9" s="43">
         <f>IF(((S9*pax_cap*load_thin*ROUND(K9*L9*revleg_thin,0))-(((battery/range_nm)*D9*ROUND(K9*L9*revleg_thin,0)*VLOOKUP(B9,country_opex,3,FALSE))+V9+W9+X9+Y9+Z9))&lt;=0,"",VLOOKUP(B9,country_opex,7,FALSE)/((S9*pax_cap*load_thin*ROUND(K9*L9*revleg_thin,0))-(((battery/range_nm)*D9*ROUND(K9*L9*revleg_thin,0)*VLOOKUP(B9,country_opex,3,FALSE))+V9+W9+X9+Y9+Z9)))</f>
         <v/>
       </c>
-      <c r="AU9" s="43">
+      <c r="AV9" s="43">
         <f>IF(((S9*pax_cap*load_mid*ROUND(K9*L9*revleg_mid,0))-(((battery/range_nm)*D9*ROUND(K9*L9*revleg_mid,0)*VLOOKUP(B9,country_opex,3,FALSE))+V9+W9+X9+Y9+Z9))&lt;=0,"",VLOOKUP(B9,country_opex,7,FALSE)/((S9*pax_cap*load_mid*ROUND(K9*L9*revleg_mid,0))-(((battery/range_nm)*D9*ROUND(K9*L9*revleg_mid,0)*VLOOKUP(B9,country_opex,3,FALSE))+V9+W9+X9+Y9+Z9)))</f>
         <v/>
       </c>
-      <c r="AV9" s="43">
+      <c r="AW9" s="43">
         <f>IF(((S9*pax_cap*load_full*ROUND(K9*L9*revleg_full,0))-(((battery/range_nm)*D9*ROUND(K9*L9*revleg_full,0)*VLOOKUP(B9,country_opex,3,FALSE))+V9+W9+X9+Y9+Z9))&lt;=0,"",VLOOKUP(B9,country_opex,7,FALSE)/((S9*pax_cap*load_full*ROUND(K9*L9*revleg_full,0))-(((battery/range_nm)*D9*ROUND(K9*L9*revleg_full,0)*VLOOKUP(B9,country_opex,3,FALSE))+V9+W9+X9+Y9+Z9)))</f>
         <v/>
       </c>
-      <c r="AW9" s="44" t="n"/>
       <c r="AX9" s="44" t="n"/>
+      <c r="AY9" s="44" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="29" t="inlineStr">
@@ -3370,11 +3402,11 @@
       </c>
       <c r="C10" s="30" t="inlineStr">
         <is>
-          <t>Al Marjan Island public arrival marina → Hampton by Hilton Marjan Island beach landing</t>
+          <t>Wynn Al Marjan Island arrival lagoon → Marjan Island Resort &amp; Spa beach jetty</t>
         </is>
       </c>
       <c r="D10" s="31" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="E10" s="26" t="n">
         <v>35</v>
@@ -3509,7 +3541,7 @@
         <v/>
       </c>
       <c r="AL10" s="34">
-        <f>IF(OR(AG10="",R10=0),"",MIN(IF(AS10="",9.9E+99,AS10),FLOOR(AK10/R10,1)))</f>
+        <f>IF(OR(AG10="",R10=0),"",MIN(IF(AT10="",9.9E+99,AT10),FLOOR(AK10/R10,1)))</f>
         <v/>
       </c>
       <c r="AM10" s="38">
@@ -3517,7 +3549,7 @@
         <v/>
       </c>
       <c r="AN10" s="36">
-        <f>IF(OR(AG10="",R10=0),"",MIN(IF(AS10="",9.9E+99,AS10),AK10/R10))</f>
+        <f>IF(OR(AG10="",R10=0),"",MIN(IF(AT10="",9.9E+99,AT10),AK10/R10))</f>
         <v/>
       </c>
       <c r="AO10" s="38">
@@ -3525,23 +3557,28 @@
         <v/>
       </c>
       <c r="AP10" s="40" t="n"/>
-      <c r="AQ10" s="41" t="n"/>
+      <c r="AQ10" s="32" t="inlineStr">
+        <is>
+          <t>Grounded</t>
+        </is>
+      </c>
       <c r="AR10" s="41" t="n"/>
-      <c r="AS10" s="42" t="n"/>
-      <c r="AT10" s="43">
+      <c r="AS10" s="41" t="n"/>
+      <c r="AT10" s="42" t="n"/>
+      <c r="AU10" s="43">
         <f>IF(((S10*pax_cap*load_thin*ROUND(K10*L10*revleg_thin,0))-(((battery/range_nm)*D10*ROUND(K10*L10*revleg_thin,0)*VLOOKUP(B10,country_opex,3,FALSE))+V10+W10+X10+Y10+Z10))&lt;=0,"",VLOOKUP(B10,country_opex,7,FALSE)/((S10*pax_cap*load_thin*ROUND(K10*L10*revleg_thin,0))-(((battery/range_nm)*D10*ROUND(K10*L10*revleg_thin,0)*VLOOKUP(B10,country_opex,3,FALSE))+V10+W10+X10+Y10+Z10)))</f>
         <v/>
       </c>
-      <c r="AU10" s="43">
+      <c r="AV10" s="43">
         <f>IF(((S10*pax_cap*load_mid*ROUND(K10*L10*revleg_mid,0))-(((battery/range_nm)*D10*ROUND(K10*L10*revleg_mid,0)*VLOOKUP(B10,country_opex,3,FALSE))+V10+W10+X10+Y10+Z10))&lt;=0,"",VLOOKUP(B10,country_opex,7,FALSE)/((S10*pax_cap*load_mid*ROUND(K10*L10*revleg_mid,0))-(((battery/range_nm)*D10*ROUND(K10*L10*revleg_mid,0)*VLOOKUP(B10,country_opex,3,FALSE))+V10+W10+X10+Y10+Z10)))</f>
         <v/>
       </c>
-      <c r="AV10" s="43">
+      <c r="AW10" s="43">
         <f>IF(((S10*pax_cap*load_full*ROUND(K10*L10*revleg_full,0))-(((battery/range_nm)*D10*ROUND(K10*L10*revleg_full,0)*VLOOKUP(B10,country_opex,3,FALSE))+V10+W10+X10+Y10+Z10))&lt;=0,"",VLOOKUP(B10,country_opex,7,FALSE)/((S10*pax_cap*load_full*ROUND(K10*L10*revleg_full,0))-(((battery/range_nm)*D10*ROUND(K10*L10*revleg_full,0)*VLOOKUP(B10,country_opex,3,FALSE))+V10+W10+X10+Y10+Z10)))</f>
         <v/>
       </c>
-      <c r="AW10" s="44" t="n"/>
       <c r="AX10" s="44" t="n"/>
+      <c r="AY10" s="44" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="29" t="inlineStr">
@@ -3556,11 +3593,11 @@
       </c>
       <c r="C11" s="30" t="inlineStr">
         <is>
-          <t>Mina Al Arab marina / lagoon basin → InterContinental Ras Al Khaimah Mina Al Arab Resort &amp; Spa jetty</t>
+          <t>Al Hamra Marina &amp; Royal Yacht Club RAK → Waldorf Astoria Ras Al Khaimah jetty</t>
         </is>
       </c>
       <c r="D11" s="31" t="n">
-        <v>0.9</v>
+        <v>0.7</v>
       </c>
       <c r="E11" s="26" t="n">
         <v>35</v>
@@ -3695,7 +3732,7 @@
         <v/>
       </c>
       <c r="AL11" s="34">
-        <f>IF(OR(AG11="",R11=0),"",MIN(IF(AS11="",9.9E+99,AS11),FLOOR(AK11/R11,1)))</f>
+        <f>IF(OR(AG11="",R11=0),"",MIN(IF(AT11="",9.9E+99,AT11),FLOOR(AK11/R11,1)))</f>
         <v/>
       </c>
       <c r="AM11" s="38">
@@ -3703,7 +3740,7 @@
         <v/>
       </c>
       <c r="AN11" s="36">
-        <f>IF(OR(AG11="",R11=0),"",MIN(IF(AS11="",9.9E+99,AS11),AK11/R11))</f>
+        <f>IF(OR(AG11="",R11=0),"",MIN(IF(AT11="",9.9E+99,AT11),AK11/R11))</f>
         <v/>
       </c>
       <c r="AO11" s="38">
@@ -3711,23 +3748,28 @@
         <v/>
       </c>
       <c r="AP11" s="40" t="n"/>
-      <c r="AQ11" s="41" t="n"/>
+      <c r="AQ11" s="32" t="inlineStr">
+        <is>
+          <t>Grounded</t>
+        </is>
+      </c>
       <c r="AR11" s="41" t="n"/>
-      <c r="AS11" s="42" t="n"/>
-      <c r="AT11" s="43">
+      <c r="AS11" s="41" t="n"/>
+      <c r="AT11" s="42" t="n"/>
+      <c r="AU11" s="43">
         <f>IF(((S11*pax_cap*load_thin*ROUND(K11*L11*revleg_thin,0))-(((battery/range_nm)*D11*ROUND(K11*L11*revleg_thin,0)*VLOOKUP(B11,country_opex,3,FALSE))+V11+W11+X11+Y11+Z11))&lt;=0,"",VLOOKUP(B11,country_opex,7,FALSE)/((S11*pax_cap*load_thin*ROUND(K11*L11*revleg_thin,0))-(((battery/range_nm)*D11*ROUND(K11*L11*revleg_thin,0)*VLOOKUP(B11,country_opex,3,FALSE))+V11+W11+X11+Y11+Z11)))</f>
         <v/>
       </c>
-      <c r="AU11" s="43">
+      <c r="AV11" s="43">
         <f>IF(((S11*pax_cap*load_mid*ROUND(K11*L11*revleg_mid,0))-(((battery/range_nm)*D11*ROUND(K11*L11*revleg_mid,0)*VLOOKUP(B11,country_opex,3,FALSE))+V11+W11+X11+Y11+Z11))&lt;=0,"",VLOOKUP(B11,country_opex,7,FALSE)/((S11*pax_cap*load_mid*ROUND(K11*L11*revleg_mid,0))-(((battery/range_nm)*D11*ROUND(K11*L11*revleg_mid,0)*VLOOKUP(B11,country_opex,3,FALSE))+V11+W11+X11+Y11+Z11)))</f>
         <v/>
       </c>
-      <c r="AV11" s="43">
+      <c r="AW11" s="43">
         <f>IF(((S11*pax_cap*load_full*ROUND(K11*L11*revleg_full,0))-(((battery/range_nm)*D11*ROUND(K11*L11*revleg_full,0)*VLOOKUP(B11,country_opex,3,FALSE))+V11+W11+X11+Y11+Z11))&lt;=0,"",VLOOKUP(B11,country_opex,7,FALSE)/((S11*pax_cap*load_full*ROUND(K11*L11*revleg_full,0))-(((battery/range_nm)*D11*ROUND(K11*L11*revleg_full,0)*VLOOKUP(B11,country_opex,3,FALSE))+V11+W11+X11+Y11+Z11)))</f>
         <v/>
       </c>
-      <c r="AW11" s="44" t="n"/>
       <c r="AX11" s="44" t="n"/>
+      <c r="AY11" s="44" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="29" t="inlineStr">
@@ -3742,11 +3784,11 @@
       </c>
       <c r="C12" s="30" t="inlineStr">
         <is>
-          <t>Anantara Mina Al Arab Ras Al Khaimah Resort jetty → Mina Al Arab marina / lagoon basin</t>
+          <t>Al Marjan Island public arrival marina → Hampton by Hilton Marjan Island beach landing</t>
         </is>
       </c>
       <c r="D12" s="31" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="E12" s="26" t="n">
         <v>35</v>
@@ -3881,7 +3923,7 @@
         <v/>
       </c>
       <c r="AL12" s="34">
-        <f>IF(OR(AG12="",R12=0),"",MIN(IF(AS12="",9.9E+99,AS12),FLOOR(AK12/R12,1)))</f>
+        <f>IF(OR(AG12="",R12=0),"",MIN(IF(AT12="",9.9E+99,AT12),FLOOR(AK12/R12,1)))</f>
         <v/>
       </c>
       <c r="AM12" s="38">
@@ -3889,7 +3931,7 @@
         <v/>
       </c>
       <c r="AN12" s="36">
-        <f>IF(OR(AG12="",R12=0),"",MIN(IF(AS12="",9.9E+99,AS12),AK12/R12))</f>
+        <f>IF(OR(AG12="",R12=0),"",MIN(IF(AT12="",9.9E+99,AT12),AK12/R12))</f>
         <v/>
       </c>
       <c r="AO12" s="38">
@@ -3897,23 +3939,28 @@
         <v/>
       </c>
       <c r="AP12" s="40" t="n"/>
-      <c r="AQ12" s="41" t="n"/>
+      <c r="AQ12" s="32" t="inlineStr">
+        <is>
+          <t>Grounded</t>
+        </is>
+      </c>
       <c r="AR12" s="41" t="n"/>
-      <c r="AS12" s="42" t="n"/>
-      <c r="AT12" s="43">
+      <c r="AS12" s="41" t="n"/>
+      <c r="AT12" s="42" t="n"/>
+      <c r="AU12" s="43">
         <f>IF(((S12*pax_cap*load_thin*ROUND(K12*L12*revleg_thin,0))-(((battery/range_nm)*D12*ROUND(K12*L12*revleg_thin,0)*VLOOKUP(B12,country_opex,3,FALSE))+V12+W12+X12+Y12+Z12))&lt;=0,"",VLOOKUP(B12,country_opex,7,FALSE)/((S12*pax_cap*load_thin*ROUND(K12*L12*revleg_thin,0))-(((battery/range_nm)*D12*ROUND(K12*L12*revleg_thin,0)*VLOOKUP(B12,country_opex,3,FALSE))+V12+W12+X12+Y12+Z12)))</f>
         <v/>
       </c>
-      <c r="AU12" s="43">
+      <c r="AV12" s="43">
         <f>IF(((S12*pax_cap*load_mid*ROUND(K12*L12*revleg_mid,0))-(((battery/range_nm)*D12*ROUND(K12*L12*revleg_mid,0)*VLOOKUP(B12,country_opex,3,FALSE))+V12+W12+X12+Y12+Z12))&lt;=0,"",VLOOKUP(B12,country_opex,7,FALSE)/((S12*pax_cap*load_mid*ROUND(K12*L12*revleg_mid,0))-(((battery/range_nm)*D12*ROUND(K12*L12*revleg_mid,0)*VLOOKUP(B12,country_opex,3,FALSE))+V12+W12+X12+Y12+Z12)))</f>
         <v/>
       </c>
-      <c r="AV12" s="43">
+      <c r="AW12" s="43">
         <f>IF(((S12*pax_cap*load_full*ROUND(K12*L12*revleg_full,0))-(((battery/range_nm)*D12*ROUND(K12*L12*revleg_full,0)*VLOOKUP(B12,country_opex,3,FALSE))+V12+W12+X12+Y12+Z12))&lt;=0,"",VLOOKUP(B12,country_opex,7,FALSE)/((S12*pax_cap*load_full*ROUND(K12*L12*revleg_full,0))-(((battery/range_nm)*D12*ROUND(K12*L12*revleg_full,0)*VLOOKUP(B12,country_opex,3,FALSE))+V12+W12+X12+Y12+Z12)))</f>
         <v/>
       </c>
-      <c r="AW12" s="44" t="n"/>
       <c r="AX12" s="44" t="n"/>
+      <c r="AY12" s="44" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="29" t="inlineStr">
@@ -3928,11 +3975,11 @@
       </c>
       <c r="C13" s="30" t="inlineStr">
         <is>
-          <t>Rixos Bab Al Bahr beach jetty → Hampton by Hilton Marjan Island beach landing</t>
+          <t>Anantara Mina Al Arab Ras Al Khaimah Resort jetty → Mina Al Arab marina / lagoon basin</t>
         </is>
       </c>
       <c r="D13" s="31" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="E13" s="26" t="n">
         <v>35</v>
@@ -4067,7 +4114,7 @@
         <v/>
       </c>
       <c r="AL13" s="34">
-        <f>IF(OR(AG13="",R13=0),"",MIN(IF(AS13="",9.9E+99,AS13),FLOOR(AK13/R13,1)))</f>
+        <f>IF(OR(AG13="",R13=0),"",MIN(IF(AT13="",9.9E+99,AT13),FLOOR(AK13/R13,1)))</f>
         <v/>
       </c>
       <c r="AM13" s="38">
@@ -4075,7 +4122,7 @@
         <v/>
       </c>
       <c r="AN13" s="36">
-        <f>IF(OR(AG13="",R13=0),"",MIN(IF(AS13="",9.9E+99,AS13),AK13/R13))</f>
+        <f>IF(OR(AG13="",R13=0),"",MIN(IF(AT13="",9.9E+99,AT13),AK13/R13))</f>
         <v/>
       </c>
       <c r="AO13" s="38">
@@ -4083,23 +4130,28 @@
         <v/>
       </c>
       <c r="AP13" s="40" t="n"/>
-      <c r="AQ13" s="41" t="n"/>
+      <c r="AQ13" s="32" t="inlineStr">
+        <is>
+          <t>Grounded</t>
+        </is>
+      </c>
       <c r="AR13" s="41" t="n"/>
-      <c r="AS13" s="42" t="n"/>
-      <c r="AT13" s="43">
+      <c r="AS13" s="41" t="n"/>
+      <c r="AT13" s="42" t="n"/>
+      <c r="AU13" s="43">
         <f>IF(((S13*pax_cap*load_thin*ROUND(K13*L13*revleg_thin,0))-(((battery/range_nm)*D13*ROUND(K13*L13*revleg_thin,0)*VLOOKUP(B13,country_opex,3,FALSE))+V13+W13+X13+Y13+Z13))&lt;=0,"",VLOOKUP(B13,country_opex,7,FALSE)/((S13*pax_cap*load_thin*ROUND(K13*L13*revleg_thin,0))-(((battery/range_nm)*D13*ROUND(K13*L13*revleg_thin,0)*VLOOKUP(B13,country_opex,3,FALSE))+V13+W13+X13+Y13+Z13)))</f>
         <v/>
       </c>
-      <c r="AU13" s="43">
+      <c r="AV13" s="43">
         <f>IF(((S13*pax_cap*load_mid*ROUND(K13*L13*revleg_mid,0))-(((battery/range_nm)*D13*ROUND(K13*L13*revleg_mid,0)*VLOOKUP(B13,country_opex,3,FALSE))+V13+W13+X13+Y13+Z13))&lt;=0,"",VLOOKUP(B13,country_opex,7,FALSE)/((S13*pax_cap*load_mid*ROUND(K13*L13*revleg_mid,0))-(((battery/range_nm)*D13*ROUND(K13*L13*revleg_mid,0)*VLOOKUP(B13,country_opex,3,FALSE))+V13+W13+X13+Y13+Z13)))</f>
         <v/>
       </c>
-      <c r="AV13" s="43">
+      <c r="AW13" s="43">
         <f>IF(((S13*pax_cap*load_full*ROUND(K13*L13*revleg_full,0))-(((battery/range_nm)*D13*ROUND(K13*L13*revleg_full,0)*VLOOKUP(B13,country_opex,3,FALSE))+V13+W13+X13+Y13+Z13))&lt;=0,"",VLOOKUP(B13,country_opex,7,FALSE)/((S13*pax_cap*load_full*ROUND(K13*L13*revleg_full,0))-(((battery/range_nm)*D13*ROUND(K13*L13*revleg_full,0)*VLOOKUP(B13,country_opex,3,FALSE))+V13+W13+X13+Y13+Z13)))</f>
         <v/>
       </c>
-      <c r="AW13" s="44" t="n"/>
       <c r="AX13" s="44" t="n"/>
+      <c r="AY13" s="44" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="29" t="inlineStr">
@@ -4114,11 +4166,11 @@
       </c>
       <c r="C14" s="30" t="inlineStr">
         <is>
-          <t>Wynn Al Marjan Island arrival lagoon → Hampton by Hilton Marjan Island beach landing</t>
+          <t>Mina Al Arab marina / lagoon basin → InterContinental Ras Al Khaimah Mina Al Arab Resort &amp; Spa jetty</t>
         </is>
       </c>
       <c r="D14" s="31" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="E14" s="26" t="n">
         <v>35</v>
@@ -4253,7 +4305,7 @@
         <v/>
       </c>
       <c r="AL14" s="34">
-        <f>IF(OR(AG14="",R14=0),"",MIN(IF(AS14="",9.9E+99,AS14),FLOOR(AK14/R14,1)))</f>
+        <f>IF(OR(AG14="",R14=0),"",MIN(IF(AT14="",9.9E+99,AT14),FLOOR(AK14/R14,1)))</f>
         <v/>
       </c>
       <c r="AM14" s="38">
@@ -4261,7 +4313,7 @@
         <v/>
       </c>
       <c r="AN14" s="36">
-        <f>IF(OR(AG14="",R14=0),"",MIN(IF(AS14="",9.9E+99,AS14),AK14/R14))</f>
+        <f>IF(OR(AG14="",R14=0),"",MIN(IF(AT14="",9.9E+99,AT14),AK14/R14))</f>
         <v/>
       </c>
       <c r="AO14" s="38">
@@ -4269,23 +4321,28 @@
         <v/>
       </c>
       <c r="AP14" s="40" t="n"/>
-      <c r="AQ14" s="41" t="n"/>
+      <c r="AQ14" s="32" t="inlineStr">
+        <is>
+          <t>Grounded</t>
+        </is>
+      </c>
       <c r="AR14" s="41" t="n"/>
-      <c r="AS14" s="42" t="n"/>
-      <c r="AT14" s="43">
+      <c r="AS14" s="41" t="n"/>
+      <c r="AT14" s="42" t="n"/>
+      <c r="AU14" s="43">
         <f>IF(((S14*pax_cap*load_thin*ROUND(K14*L14*revleg_thin,0))-(((battery/range_nm)*D14*ROUND(K14*L14*revleg_thin,0)*VLOOKUP(B14,country_opex,3,FALSE))+V14+W14+X14+Y14+Z14))&lt;=0,"",VLOOKUP(B14,country_opex,7,FALSE)/((S14*pax_cap*load_thin*ROUND(K14*L14*revleg_thin,0))-(((battery/range_nm)*D14*ROUND(K14*L14*revleg_thin,0)*VLOOKUP(B14,country_opex,3,FALSE))+V14+W14+X14+Y14+Z14)))</f>
         <v/>
       </c>
-      <c r="AU14" s="43">
+      <c r="AV14" s="43">
         <f>IF(((S14*pax_cap*load_mid*ROUND(K14*L14*revleg_mid,0))-(((battery/range_nm)*D14*ROUND(K14*L14*revleg_mid,0)*VLOOKUP(B14,country_opex,3,FALSE))+V14+W14+X14+Y14+Z14))&lt;=0,"",VLOOKUP(B14,country_opex,7,FALSE)/((S14*pax_cap*load_mid*ROUND(K14*L14*revleg_mid,0))-(((battery/range_nm)*D14*ROUND(K14*L14*revleg_mid,0)*VLOOKUP(B14,country_opex,3,FALSE))+V14+W14+X14+Y14+Z14)))</f>
         <v/>
       </c>
-      <c r="AV14" s="43">
+      <c r="AW14" s="43">
         <f>IF(((S14*pax_cap*load_full*ROUND(K14*L14*revleg_full,0))-(((battery/range_nm)*D14*ROUND(K14*L14*revleg_full,0)*VLOOKUP(B14,country_opex,3,FALSE))+V14+W14+X14+Y14+Z14))&lt;=0,"",VLOOKUP(B14,country_opex,7,FALSE)/((S14*pax_cap*load_full*ROUND(K14*L14*revleg_full,0))-(((battery/range_nm)*D14*ROUND(K14*L14*revleg_full,0)*VLOOKUP(B14,country_opex,3,FALSE))+V14+W14+X14+Y14+Z14)))</f>
         <v/>
       </c>
-      <c r="AW14" s="44" t="n"/>
       <c r="AX14" s="44" t="n"/>
+      <c r="AY14" s="44" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="29" t="inlineStr">
@@ -4300,11 +4357,11 @@
       </c>
       <c r="C15" s="30" t="inlineStr">
         <is>
-          <t>Ras Al Khaimah Harbour → Hilton Garden Inn Ras Al Khaimah (Corniche) jetty</t>
+          <t>Rixos Bab Al Bahr beach jetty → Hampton by Hilton Marjan Island beach landing</t>
         </is>
       </c>
       <c r="D15" s="31" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="E15" s="26" t="n">
         <v>35</v>
@@ -4439,7 +4496,7 @@
         <v/>
       </c>
       <c r="AL15" s="34">
-        <f>IF(OR(AG15="",R15=0),"",MIN(IF(AS15="",9.9E+99,AS15),FLOOR(AK15/R15,1)))</f>
+        <f>IF(OR(AG15="",R15=0),"",MIN(IF(AT15="",9.9E+99,AT15),FLOOR(AK15/R15,1)))</f>
         <v/>
       </c>
       <c r="AM15" s="38">
@@ -4447,7 +4504,7 @@
         <v/>
       </c>
       <c r="AN15" s="36">
-        <f>IF(OR(AG15="",R15=0),"",MIN(IF(AS15="",9.9E+99,AS15),AK15/R15))</f>
+        <f>IF(OR(AG15="",R15=0),"",MIN(IF(AT15="",9.9E+99,AT15),AK15/R15))</f>
         <v/>
       </c>
       <c r="AO15" s="38">
@@ -4455,23 +4512,28 @@
         <v/>
       </c>
       <c r="AP15" s="40" t="n"/>
-      <c r="AQ15" s="41" t="n"/>
+      <c r="AQ15" s="32" t="inlineStr">
+        <is>
+          <t>Grounded</t>
+        </is>
+      </c>
       <c r="AR15" s="41" t="n"/>
-      <c r="AS15" s="42" t="n"/>
-      <c r="AT15" s="43">
+      <c r="AS15" s="41" t="n"/>
+      <c r="AT15" s="42" t="n"/>
+      <c r="AU15" s="43">
         <f>IF(((S15*pax_cap*load_thin*ROUND(K15*L15*revleg_thin,0))-(((battery/range_nm)*D15*ROUND(K15*L15*revleg_thin,0)*VLOOKUP(B15,country_opex,3,FALSE))+V15+W15+X15+Y15+Z15))&lt;=0,"",VLOOKUP(B15,country_opex,7,FALSE)/((S15*pax_cap*load_thin*ROUND(K15*L15*revleg_thin,0))-(((battery/range_nm)*D15*ROUND(K15*L15*revleg_thin,0)*VLOOKUP(B15,country_opex,3,FALSE))+V15+W15+X15+Y15+Z15)))</f>
         <v/>
       </c>
-      <c r="AU15" s="43">
+      <c r="AV15" s="43">
         <f>IF(((S15*pax_cap*load_mid*ROUND(K15*L15*revleg_mid,0))-(((battery/range_nm)*D15*ROUND(K15*L15*revleg_mid,0)*VLOOKUP(B15,country_opex,3,FALSE))+V15+W15+X15+Y15+Z15))&lt;=0,"",VLOOKUP(B15,country_opex,7,FALSE)/((S15*pax_cap*load_mid*ROUND(K15*L15*revleg_mid,0))-(((battery/range_nm)*D15*ROUND(K15*L15*revleg_mid,0)*VLOOKUP(B15,country_opex,3,FALSE))+V15+W15+X15+Y15+Z15)))</f>
         <v/>
       </c>
-      <c r="AV15" s="43">
+      <c r="AW15" s="43">
         <f>IF(((S15*pax_cap*load_full*ROUND(K15*L15*revleg_full,0))-(((battery/range_nm)*D15*ROUND(K15*L15*revleg_full,0)*VLOOKUP(B15,country_opex,3,FALSE))+V15+W15+X15+Y15+Z15))&lt;=0,"",VLOOKUP(B15,country_opex,7,FALSE)/((S15*pax_cap*load_full*ROUND(K15*L15*revleg_full,0))-(((battery/range_nm)*D15*ROUND(K15*L15*revleg_full,0)*VLOOKUP(B15,country_opex,3,FALSE))+V15+W15+X15+Y15+Z15)))</f>
         <v/>
       </c>
-      <c r="AW15" s="44" t="n"/>
       <c r="AX15" s="44" t="n"/>
+      <c r="AY15" s="44" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="29" t="inlineStr">
@@ -4486,11 +4548,11 @@
       </c>
       <c r="C16" s="30" t="inlineStr">
         <is>
-          <t>Hilton Garden Inn Ras Al Khaimah (Corniche) jetty → RAK Corniche public pier</t>
+          <t>Wynn Al Marjan Island arrival lagoon → Hampton by Hilton Marjan Island beach landing</t>
         </is>
       </c>
       <c r="D16" s="31" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="E16" s="26" t="n">
         <v>35</v>
@@ -4625,7 +4687,7 @@
         <v/>
       </c>
       <c r="AL16" s="34">
-        <f>IF(OR(AG16="",R16=0),"",MIN(IF(AS16="",9.9E+99,AS16),FLOOR(AK16/R16,1)))</f>
+        <f>IF(OR(AG16="",R16=0),"",MIN(IF(AT16="",9.9E+99,AT16),FLOOR(AK16/R16,1)))</f>
         <v/>
       </c>
       <c r="AM16" s="38">
@@ -4633,7 +4695,7 @@
         <v/>
       </c>
       <c r="AN16" s="36">
-        <f>IF(OR(AG16="",R16=0),"",MIN(IF(AS16="",9.9E+99,AS16),AK16/R16))</f>
+        <f>IF(OR(AG16="",R16=0),"",MIN(IF(AT16="",9.9E+99,AT16),AK16/R16))</f>
         <v/>
       </c>
       <c r="AO16" s="38">
@@ -4641,23 +4703,28 @@
         <v/>
       </c>
       <c r="AP16" s="40" t="n"/>
-      <c r="AQ16" s="41" t="n"/>
+      <c r="AQ16" s="32" t="inlineStr">
+        <is>
+          <t>Grounded</t>
+        </is>
+      </c>
       <c r="AR16" s="41" t="n"/>
-      <c r="AS16" s="42" t="n"/>
-      <c r="AT16" s="43">
+      <c r="AS16" s="41" t="n"/>
+      <c r="AT16" s="42" t="n"/>
+      <c r="AU16" s="43">
         <f>IF(((S16*pax_cap*load_thin*ROUND(K16*L16*revleg_thin,0))-(((battery/range_nm)*D16*ROUND(K16*L16*revleg_thin,0)*VLOOKUP(B16,country_opex,3,FALSE))+V16+W16+X16+Y16+Z16))&lt;=0,"",VLOOKUP(B16,country_opex,7,FALSE)/((S16*pax_cap*load_thin*ROUND(K16*L16*revleg_thin,0))-(((battery/range_nm)*D16*ROUND(K16*L16*revleg_thin,0)*VLOOKUP(B16,country_opex,3,FALSE))+V16+W16+X16+Y16+Z16)))</f>
         <v/>
       </c>
-      <c r="AU16" s="43">
+      <c r="AV16" s="43">
         <f>IF(((S16*pax_cap*load_mid*ROUND(K16*L16*revleg_mid,0))-(((battery/range_nm)*D16*ROUND(K16*L16*revleg_mid,0)*VLOOKUP(B16,country_opex,3,FALSE))+V16+W16+X16+Y16+Z16))&lt;=0,"",VLOOKUP(B16,country_opex,7,FALSE)/((S16*pax_cap*load_mid*ROUND(K16*L16*revleg_mid,0))-(((battery/range_nm)*D16*ROUND(K16*L16*revleg_mid,0)*VLOOKUP(B16,country_opex,3,FALSE))+V16+W16+X16+Y16+Z16)))</f>
         <v/>
       </c>
-      <c r="AV16" s="43">
+      <c r="AW16" s="43">
         <f>IF(((S16*pax_cap*load_full*ROUND(K16*L16*revleg_full,0))-(((battery/range_nm)*D16*ROUND(K16*L16*revleg_full,0)*VLOOKUP(B16,country_opex,3,FALSE))+V16+W16+X16+Y16+Z16))&lt;=0,"",VLOOKUP(B16,country_opex,7,FALSE)/((S16*pax_cap*load_full*ROUND(K16*L16*revleg_full,0))-(((battery/range_nm)*D16*ROUND(K16*L16*revleg_full,0)*VLOOKUP(B16,country_opex,3,FALSE))+V16+W16+X16+Y16+Z16)))</f>
         <v/>
       </c>
-      <c r="AW16" s="44" t="n"/>
       <c r="AX16" s="44" t="n"/>
+      <c r="AY16" s="44" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="29" t="inlineStr">
@@ -4672,11 +4739,11 @@
       </c>
       <c r="C17" s="30" t="inlineStr">
         <is>
-          <t>Bin Majid Beach Resort jetty → Acacia by Bin Majid jetty</t>
+          <t>Ras Al Khaimah Harbour → Hilton Garden Inn Ras Al Khaimah (Corniche) jetty</t>
         </is>
       </c>
       <c r="D17" s="31" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="E17" s="26" t="n">
         <v>35</v>
@@ -4811,7 +4878,7 @@
         <v/>
       </c>
       <c r="AL17" s="34">
-        <f>IF(OR(AG17="",R17=0),"",MIN(IF(AS17="",9.9E+99,AS17),FLOOR(AK17/R17,1)))</f>
+        <f>IF(OR(AG17="",R17=0),"",MIN(IF(AT17="",9.9E+99,AT17),FLOOR(AK17/R17,1)))</f>
         <v/>
       </c>
       <c r="AM17" s="38">
@@ -4819,7 +4886,7 @@
         <v/>
       </c>
       <c r="AN17" s="36">
-        <f>IF(OR(AG17="",R17=0),"",MIN(IF(AS17="",9.9E+99,AS17),AK17/R17))</f>
+        <f>IF(OR(AG17="",R17=0),"",MIN(IF(AT17="",9.9E+99,AT17),AK17/R17))</f>
         <v/>
       </c>
       <c r="AO17" s="38">
@@ -4827,23 +4894,28 @@
         <v/>
       </c>
       <c r="AP17" s="40" t="n"/>
-      <c r="AQ17" s="41" t="n"/>
+      <c r="AQ17" s="32" t="inlineStr">
+        <is>
+          <t>Grounded</t>
+        </is>
+      </c>
       <c r="AR17" s="41" t="n"/>
-      <c r="AS17" s="42" t="n"/>
-      <c r="AT17" s="43">
+      <c r="AS17" s="41" t="n"/>
+      <c r="AT17" s="42" t="n"/>
+      <c r="AU17" s="43">
         <f>IF(((S17*pax_cap*load_thin*ROUND(K17*L17*revleg_thin,0))-(((battery/range_nm)*D17*ROUND(K17*L17*revleg_thin,0)*VLOOKUP(B17,country_opex,3,FALSE))+V17+W17+X17+Y17+Z17))&lt;=0,"",VLOOKUP(B17,country_opex,7,FALSE)/((S17*pax_cap*load_thin*ROUND(K17*L17*revleg_thin,0))-(((battery/range_nm)*D17*ROUND(K17*L17*revleg_thin,0)*VLOOKUP(B17,country_opex,3,FALSE))+V17+W17+X17+Y17+Z17)))</f>
         <v/>
       </c>
-      <c r="AU17" s="43">
+      <c r="AV17" s="43">
         <f>IF(((S17*pax_cap*load_mid*ROUND(K17*L17*revleg_mid,0))-(((battery/range_nm)*D17*ROUND(K17*L17*revleg_mid,0)*VLOOKUP(B17,country_opex,3,FALSE))+V17+W17+X17+Y17+Z17))&lt;=0,"",VLOOKUP(B17,country_opex,7,FALSE)/((S17*pax_cap*load_mid*ROUND(K17*L17*revleg_mid,0))-(((battery/range_nm)*D17*ROUND(K17*L17*revleg_mid,0)*VLOOKUP(B17,country_opex,3,FALSE))+V17+W17+X17+Y17+Z17)))</f>
         <v/>
       </c>
-      <c r="AV17" s="43">
+      <c r="AW17" s="43">
         <f>IF(((S17*pax_cap*load_full*ROUND(K17*L17*revleg_full,0))-(((battery/range_nm)*D17*ROUND(K17*L17*revleg_full,0)*VLOOKUP(B17,country_opex,3,FALSE))+V17+W17+X17+Y17+Z17))&lt;=0,"",VLOOKUP(B17,country_opex,7,FALSE)/((S17*pax_cap*load_full*ROUND(K17*L17*revleg_full,0))-(((battery/range_nm)*D17*ROUND(K17*L17*revleg_full,0)*VLOOKUP(B17,country_opex,3,FALSE))+V17+W17+X17+Y17+Z17)))</f>
         <v/>
       </c>
-      <c r="AW17" s="44" t="n"/>
       <c r="AX17" s="44" t="n"/>
+      <c r="AY17" s="44" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="29" t="inlineStr">
@@ -4858,11 +4930,11 @@
       </c>
       <c r="C18" s="30" t="inlineStr">
         <is>
-          <t>Al Zorah Marina 1 → Ajman Marina</t>
+          <t>Bin Majid Beach Resort jetty → Acacia by Bin Majid jetty</t>
         </is>
       </c>
       <c r="D18" s="31" t="n">
-        <v>1.6</v>
+        <v>1.2</v>
       </c>
       <c r="E18" s="26" t="n">
         <v>35</v>
@@ -4997,7 +5069,7 @@
         <v/>
       </c>
       <c r="AL18" s="34">
-        <f>IF(OR(AG18="",R18=0),"",MIN(IF(AS18="",9.9E+99,AS18),FLOOR(AK18/R18,1)))</f>
+        <f>IF(OR(AG18="",R18=0),"",MIN(IF(AT18="",9.9E+99,AT18),FLOOR(AK18/R18,1)))</f>
         <v/>
       </c>
       <c r="AM18" s="38">
@@ -5005,7 +5077,7 @@
         <v/>
       </c>
       <c r="AN18" s="36">
-        <f>IF(OR(AG18="",R18=0),"",MIN(IF(AS18="",9.9E+99,AS18),AK18/R18))</f>
+        <f>IF(OR(AG18="",R18=0),"",MIN(IF(AT18="",9.9E+99,AT18),AK18/R18))</f>
         <v/>
       </c>
       <c r="AO18" s="38">
@@ -5013,23 +5085,28 @@
         <v/>
       </c>
       <c r="AP18" s="40" t="n"/>
-      <c r="AQ18" s="41" t="n"/>
+      <c r="AQ18" s="32" t="inlineStr">
+        <is>
+          <t>Grounded</t>
+        </is>
+      </c>
       <c r="AR18" s="41" t="n"/>
-      <c r="AS18" s="42" t="n"/>
-      <c r="AT18" s="43">
+      <c r="AS18" s="41" t="n"/>
+      <c r="AT18" s="42" t="n"/>
+      <c r="AU18" s="43">
         <f>IF(((S18*pax_cap*load_thin*ROUND(K18*L18*revleg_thin,0))-(((battery/range_nm)*D18*ROUND(K18*L18*revleg_thin,0)*VLOOKUP(B18,country_opex,3,FALSE))+V18+W18+X18+Y18+Z18))&lt;=0,"",VLOOKUP(B18,country_opex,7,FALSE)/((S18*pax_cap*load_thin*ROUND(K18*L18*revleg_thin,0))-(((battery/range_nm)*D18*ROUND(K18*L18*revleg_thin,0)*VLOOKUP(B18,country_opex,3,FALSE))+V18+W18+X18+Y18+Z18)))</f>
         <v/>
       </c>
-      <c r="AU18" s="43">
+      <c r="AV18" s="43">
         <f>IF(((S18*pax_cap*load_mid*ROUND(K18*L18*revleg_mid,0))-(((battery/range_nm)*D18*ROUND(K18*L18*revleg_mid,0)*VLOOKUP(B18,country_opex,3,FALSE))+V18+W18+X18+Y18+Z18))&lt;=0,"",VLOOKUP(B18,country_opex,7,FALSE)/((S18*pax_cap*load_mid*ROUND(K18*L18*revleg_mid,0))-(((battery/range_nm)*D18*ROUND(K18*L18*revleg_mid,0)*VLOOKUP(B18,country_opex,3,FALSE))+V18+W18+X18+Y18+Z18)))</f>
         <v/>
       </c>
-      <c r="AV18" s="43">
+      <c r="AW18" s="43">
         <f>IF(((S18*pax_cap*load_full*ROUND(K18*L18*revleg_full,0))-(((battery/range_nm)*D18*ROUND(K18*L18*revleg_full,0)*VLOOKUP(B18,country_opex,3,FALSE))+V18+W18+X18+Y18+Z18))&lt;=0,"",VLOOKUP(B18,country_opex,7,FALSE)/((S18*pax_cap*load_full*ROUND(K18*L18*revleg_full,0))-(((battery/range_nm)*D18*ROUND(K18*L18*revleg_full,0)*VLOOKUP(B18,country_opex,3,FALSE))+V18+W18+X18+Y18+Z18)))</f>
         <v/>
       </c>
-      <c r="AW18" s="44" t="n"/>
       <c r="AX18" s="44" t="n"/>
+      <c r="AY18" s="44" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="29" t="inlineStr">
@@ -5044,11 +5121,11 @@
       </c>
       <c r="C19" s="30" t="inlineStr">
         <is>
-          <t>Raksa → Ras Al Khaimah Harbour</t>
+          <t>Hilton Garden Inn Ras Al Khaimah (Corniche) jetty → RAK Corniche public pier</t>
         </is>
       </c>
       <c r="D19" s="31" t="n">
-        <v>1.9</v>
+        <v>1.2</v>
       </c>
       <c r="E19" s="26" t="n">
         <v>35</v>
@@ -5183,7 +5260,7 @@
         <v/>
       </c>
       <c r="AL19" s="34">
-        <f>IF(OR(AG19="",R19=0),"",MIN(IF(AS19="",9.9E+99,AS19),FLOOR(AK19/R19,1)))</f>
+        <f>IF(OR(AG19="",R19=0),"",MIN(IF(AT19="",9.9E+99,AT19),FLOOR(AK19/R19,1)))</f>
         <v/>
       </c>
       <c r="AM19" s="38">
@@ -5191,7 +5268,7 @@
         <v/>
       </c>
       <c r="AN19" s="36">
-        <f>IF(OR(AG19="",R19=0),"",MIN(IF(AS19="",9.9E+99,AS19),AK19/R19))</f>
+        <f>IF(OR(AG19="",R19=0),"",MIN(IF(AT19="",9.9E+99,AT19),AK19/R19))</f>
         <v/>
       </c>
       <c r="AO19" s="38">
@@ -5199,23 +5276,28 @@
         <v/>
       </c>
       <c r="AP19" s="40" t="n"/>
-      <c r="AQ19" s="41" t="n"/>
+      <c r="AQ19" s="32" t="inlineStr">
+        <is>
+          <t>Grounded</t>
+        </is>
+      </c>
       <c r="AR19" s="41" t="n"/>
-      <c r="AS19" s="42" t="n"/>
-      <c r="AT19" s="43">
+      <c r="AS19" s="41" t="n"/>
+      <c r="AT19" s="42" t="n"/>
+      <c r="AU19" s="43">
         <f>IF(((S19*pax_cap*load_thin*ROUND(K19*L19*revleg_thin,0))-(((battery/range_nm)*D19*ROUND(K19*L19*revleg_thin,0)*VLOOKUP(B19,country_opex,3,FALSE))+V19+W19+X19+Y19+Z19))&lt;=0,"",VLOOKUP(B19,country_opex,7,FALSE)/((S19*pax_cap*load_thin*ROUND(K19*L19*revleg_thin,0))-(((battery/range_nm)*D19*ROUND(K19*L19*revleg_thin,0)*VLOOKUP(B19,country_opex,3,FALSE))+V19+W19+X19+Y19+Z19)))</f>
         <v/>
       </c>
-      <c r="AU19" s="43">
+      <c r="AV19" s="43">
         <f>IF(((S19*pax_cap*load_mid*ROUND(K19*L19*revleg_mid,0))-(((battery/range_nm)*D19*ROUND(K19*L19*revleg_mid,0)*VLOOKUP(B19,country_opex,3,FALSE))+V19+W19+X19+Y19+Z19))&lt;=0,"",VLOOKUP(B19,country_opex,7,FALSE)/((S19*pax_cap*load_mid*ROUND(K19*L19*revleg_mid,0))-(((battery/range_nm)*D19*ROUND(K19*L19*revleg_mid,0)*VLOOKUP(B19,country_opex,3,FALSE))+V19+W19+X19+Y19+Z19)))</f>
         <v/>
       </c>
-      <c r="AV19" s="43">
+      <c r="AW19" s="43">
         <f>IF(((S19*pax_cap*load_full*ROUND(K19*L19*revleg_full,0))-(((battery/range_nm)*D19*ROUND(K19*L19*revleg_full,0)*VLOOKUP(B19,country_opex,3,FALSE))+V19+W19+X19+Y19+Z19))&lt;=0,"",VLOOKUP(B19,country_opex,7,FALSE)/((S19*pax_cap*load_full*ROUND(K19*L19*revleg_full,0))-(((battery/range_nm)*D19*ROUND(K19*L19*revleg_full,0)*VLOOKUP(B19,country_opex,3,FALSE))+V19+W19+X19+Y19+Z19)))</f>
         <v/>
       </c>
-      <c r="AW19" s="44" t="n"/>
       <c r="AX19" s="44" t="n"/>
+      <c r="AY19" s="44" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="29" t="inlineStr">
@@ -5230,11 +5312,11 @@
       </c>
       <c r="C20" s="30" t="inlineStr">
         <is>
-          <t>Sha'am Fishing Boat Harbour → Sha'am coastal staging point</t>
+          <t>Al Zorah Marina 1 → Ajman Marina</t>
         </is>
       </c>
       <c r="D20" s="31" t="n">
-        <v>2.1</v>
+        <v>1.6</v>
       </c>
       <c r="E20" s="26" t="n">
         <v>35</v>
@@ -5369,7 +5451,7 @@
         <v/>
       </c>
       <c r="AL20" s="34">
-        <f>IF(OR(AG20="",R20=0),"",MIN(IF(AS20="",9.9E+99,AS20),FLOOR(AK20/R20,1)))</f>
+        <f>IF(OR(AG20="",R20=0),"",MIN(IF(AT20="",9.9E+99,AT20),FLOOR(AK20/R20,1)))</f>
         <v/>
       </c>
       <c r="AM20" s="38">
@@ -5377,7 +5459,7 @@
         <v/>
       </c>
       <c r="AN20" s="36">
-        <f>IF(OR(AG20="",R20=0),"",MIN(IF(AS20="",9.9E+99,AS20),AK20/R20))</f>
+        <f>IF(OR(AG20="",R20=0),"",MIN(IF(AT20="",9.9E+99,AT20),AK20/R20))</f>
         <v/>
       </c>
       <c r="AO20" s="38">
@@ -5385,23 +5467,28 @@
         <v/>
       </c>
       <c r="AP20" s="40" t="n"/>
-      <c r="AQ20" s="41" t="n"/>
+      <c r="AQ20" s="32" t="inlineStr">
+        <is>
+          <t>Grounded</t>
+        </is>
+      </c>
       <c r="AR20" s="41" t="n"/>
-      <c r="AS20" s="42" t="n"/>
-      <c r="AT20" s="43">
+      <c r="AS20" s="41" t="n"/>
+      <c r="AT20" s="42" t="n"/>
+      <c r="AU20" s="43">
         <f>IF(((S20*pax_cap*load_thin*ROUND(K20*L20*revleg_thin,0))-(((battery/range_nm)*D20*ROUND(K20*L20*revleg_thin,0)*VLOOKUP(B20,country_opex,3,FALSE))+V20+W20+X20+Y20+Z20))&lt;=0,"",VLOOKUP(B20,country_opex,7,FALSE)/((S20*pax_cap*load_thin*ROUND(K20*L20*revleg_thin,0))-(((battery/range_nm)*D20*ROUND(K20*L20*revleg_thin,0)*VLOOKUP(B20,country_opex,3,FALSE))+V20+W20+X20+Y20+Z20)))</f>
         <v/>
       </c>
-      <c r="AU20" s="43">
+      <c r="AV20" s="43">
         <f>IF(((S20*pax_cap*load_mid*ROUND(K20*L20*revleg_mid,0))-(((battery/range_nm)*D20*ROUND(K20*L20*revleg_mid,0)*VLOOKUP(B20,country_opex,3,FALSE))+V20+W20+X20+Y20+Z20))&lt;=0,"",VLOOKUP(B20,country_opex,7,FALSE)/((S20*pax_cap*load_mid*ROUND(K20*L20*revleg_mid,0))-(((battery/range_nm)*D20*ROUND(K20*L20*revleg_mid,0)*VLOOKUP(B20,country_opex,3,FALSE))+V20+W20+X20+Y20+Z20)))</f>
         <v/>
       </c>
-      <c r="AV20" s="43">
+      <c r="AW20" s="43">
         <f>IF(((S20*pax_cap*load_full*ROUND(K20*L20*revleg_full,0))-(((battery/range_nm)*D20*ROUND(K20*L20*revleg_full,0)*VLOOKUP(B20,country_opex,3,FALSE))+V20+W20+X20+Y20+Z20))&lt;=0,"",VLOOKUP(B20,country_opex,7,FALSE)/((S20*pax_cap*load_full*ROUND(K20*L20*revleg_full,0))-(((battery/range_nm)*D20*ROUND(K20*L20*revleg_full,0)*VLOOKUP(B20,country_opex,3,FALSE))+V20+W20+X20+Y20+Z20)))</f>
         <v/>
       </c>
-      <c r="AW20" s="44" t="n"/>
       <c r="AX20" s="44" t="n"/>
+      <c r="AY20" s="44" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="29" t="inlineStr">
@@ -5416,11 +5503,11 @@
       </c>
       <c r="C21" s="30" t="inlineStr">
         <is>
-          <t>The Cove Rotana Resort jetty → Anantara Mina Al Arab Ras Al Khaimah Resort jetty</t>
+          <t>Raksa → Ras Al Khaimah Harbour</t>
         </is>
       </c>
       <c r="D21" s="31" t="n">
-        <v>2.2</v>
+        <v>1.9</v>
       </c>
       <c r="E21" s="26" t="n">
         <v>35</v>
@@ -5555,7 +5642,7 @@
         <v/>
       </c>
       <c r="AL21" s="34">
-        <f>IF(OR(AG21="",R21=0),"",MIN(IF(AS21="",9.9E+99,AS21),FLOOR(AK21/R21,1)))</f>
+        <f>IF(OR(AG21="",R21=0),"",MIN(IF(AT21="",9.9E+99,AT21),FLOOR(AK21/R21,1)))</f>
         <v/>
       </c>
       <c r="AM21" s="38">
@@ -5563,7 +5650,7 @@
         <v/>
       </c>
       <c r="AN21" s="36">
-        <f>IF(OR(AG21="",R21=0),"",MIN(IF(AS21="",9.9E+99,AS21),AK21/R21))</f>
+        <f>IF(OR(AG21="",R21=0),"",MIN(IF(AT21="",9.9E+99,AT21),AK21/R21))</f>
         <v/>
       </c>
       <c r="AO21" s="38">
@@ -5571,23 +5658,28 @@
         <v/>
       </c>
       <c r="AP21" s="40" t="n"/>
-      <c r="AQ21" s="41" t="n"/>
+      <c r="AQ21" s="32" t="inlineStr">
+        <is>
+          <t>Grounded</t>
+        </is>
+      </c>
       <c r="AR21" s="41" t="n"/>
-      <c r="AS21" s="42" t="n"/>
-      <c r="AT21" s="43">
+      <c r="AS21" s="41" t="n"/>
+      <c r="AT21" s="42" t="n"/>
+      <c r="AU21" s="43">
         <f>IF(((S21*pax_cap*load_thin*ROUND(K21*L21*revleg_thin,0))-(((battery/range_nm)*D21*ROUND(K21*L21*revleg_thin,0)*VLOOKUP(B21,country_opex,3,FALSE))+V21+W21+X21+Y21+Z21))&lt;=0,"",VLOOKUP(B21,country_opex,7,FALSE)/((S21*pax_cap*load_thin*ROUND(K21*L21*revleg_thin,0))-(((battery/range_nm)*D21*ROUND(K21*L21*revleg_thin,0)*VLOOKUP(B21,country_opex,3,FALSE))+V21+W21+X21+Y21+Z21)))</f>
         <v/>
       </c>
-      <c r="AU21" s="43">
+      <c r="AV21" s="43">
         <f>IF(((S21*pax_cap*load_mid*ROUND(K21*L21*revleg_mid,0))-(((battery/range_nm)*D21*ROUND(K21*L21*revleg_mid,0)*VLOOKUP(B21,country_opex,3,FALSE))+V21+W21+X21+Y21+Z21))&lt;=0,"",VLOOKUP(B21,country_opex,7,FALSE)/((S21*pax_cap*load_mid*ROUND(K21*L21*revleg_mid,0))-(((battery/range_nm)*D21*ROUND(K21*L21*revleg_mid,0)*VLOOKUP(B21,country_opex,3,FALSE))+V21+W21+X21+Y21+Z21)))</f>
         <v/>
       </c>
-      <c r="AV21" s="43">
+      <c r="AW21" s="43">
         <f>IF(((S21*pax_cap*load_full*ROUND(K21*L21*revleg_full,0))-(((battery/range_nm)*D21*ROUND(K21*L21*revleg_full,0)*VLOOKUP(B21,country_opex,3,FALSE))+V21+W21+X21+Y21+Z21))&lt;=0,"",VLOOKUP(B21,country_opex,7,FALSE)/((S21*pax_cap*load_full*ROUND(K21*L21*revleg_full,0))-(((battery/range_nm)*D21*ROUND(K21*L21*revleg_full,0)*VLOOKUP(B21,country_opex,3,FALSE))+V21+W21+X21+Y21+Z21)))</f>
         <v/>
       </c>
-      <c r="AW21" s="44" t="n"/>
       <c r="AX21" s="44" t="n"/>
+      <c r="AY21" s="44" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="29" t="inlineStr">
@@ -5602,11 +5694,11 @@
       </c>
       <c r="C22" s="30" t="inlineStr">
         <is>
-          <t>ميناء صيادين غليلة → Sha'am Fishing Boat Harbour</t>
+          <t>Sha'am Fishing Boat Harbour → Sha'am coastal staging point</t>
         </is>
       </c>
       <c r="D22" s="31" t="n">
-        <v>2.5</v>
+        <v>2.1</v>
       </c>
       <c r="E22" s="26" t="n">
         <v>35</v>
@@ -5741,7 +5833,7 @@
         <v/>
       </c>
       <c r="AL22" s="34">
-        <f>IF(OR(AG22="",R22=0),"",MIN(IF(AS22="",9.9E+99,AS22),FLOOR(AK22/R22,1)))</f>
+        <f>IF(OR(AG22="",R22=0),"",MIN(IF(AT22="",9.9E+99,AT22),FLOOR(AK22/R22,1)))</f>
         <v/>
       </c>
       <c r="AM22" s="38">
@@ -5749,7 +5841,7 @@
         <v/>
       </c>
       <c r="AN22" s="36">
-        <f>IF(OR(AG22="",R22=0),"",MIN(IF(AS22="",9.9E+99,AS22),AK22/R22))</f>
+        <f>IF(OR(AG22="",R22=0),"",MIN(IF(AT22="",9.9E+99,AT22),AK22/R22))</f>
         <v/>
       </c>
       <c r="AO22" s="38">
@@ -5757,23 +5849,28 @@
         <v/>
       </c>
       <c r="AP22" s="40" t="n"/>
-      <c r="AQ22" s="41" t="n"/>
+      <c r="AQ22" s="32" t="inlineStr">
+        <is>
+          <t>Grounded</t>
+        </is>
+      </c>
       <c r="AR22" s="41" t="n"/>
-      <c r="AS22" s="42" t="n"/>
-      <c r="AT22" s="43">
+      <c r="AS22" s="41" t="n"/>
+      <c r="AT22" s="42" t="n"/>
+      <c r="AU22" s="43">
         <f>IF(((S22*pax_cap*load_thin*ROUND(K22*L22*revleg_thin,0))-(((battery/range_nm)*D22*ROUND(K22*L22*revleg_thin,0)*VLOOKUP(B22,country_opex,3,FALSE))+V22+W22+X22+Y22+Z22))&lt;=0,"",VLOOKUP(B22,country_opex,7,FALSE)/((S22*pax_cap*load_thin*ROUND(K22*L22*revleg_thin,0))-(((battery/range_nm)*D22*ROUND(K22*L22*revleg_thin,0)*VLOOKUP(B22,country_opex,3,FALSE))+V22+W22+X22+Y22+Z22)))</f>
         <v/>
       </c>
-      <c r="AU22" s="43">
+      <c r="AV22" s="43">
         <f>IF(((S22*pax_cap*load_mid*ROUND(K22*L22*revleg_mid,0))-(((battery/range_nm)*D22*ROUND(K22*L22*revleg_mid,0)*VLOOKUP(B22,country_opex,3,FALSE))+V22+W22+X22+Y22+Z22))&lt;=0,"",VLOOKUP(B22,country_opex,7,FALSE)/((S22*pax_cap*load_mid*ROUND(K22*L22*revleg_mid,0))-(((battery/range_nm)*D22*ROUND(K22*L22*revleg_mid,0)*VLOOKUP(B22,country_opex,3,FALSE))+V22+W22+X22+Y22+Z22)))</f>
         <v/>
       </c>
-      <c r="AV22" s="43">
+      <c r="AW22" s="43">
         <f>IF(((S22*pax_cap*load_full*ROUND(K22*L22*revleg_full,0))-(((battery/range_nm)*D22*ROUND(K22*L22*revleg_full,0)*VLOOKUP(B22,country_opex,3,FALSE))+V22+W22+X22+Y22+Z22))&lt;=0,"",VLOOKUP(B22,country_opex,7,FALSE)/((S22*pax_cap*load_full*ROUND(K22*L22*revleg_full,0))-(((battery/range_nm)*D22*ROUND(K22*L22*revleg_full,0)*VLOOKUP(B22,country_opex,3,FALSE))+V22+W22+X22+Y22+Z22)))</f>
         <v/>
       </c>
-      <c r="AW22" s="44" t="n"/>
       <c r="AX22" s="44" t="n"/>
+      <c r="AY22" s="44" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="29" t="inlineStr">
@@ -5788,11 +5885,11 @@
       </c>
       <c r="C23" s="30" t="inlineStr">
         <is>
-          <t>Daba Port → Dibba Al-Hisn Marina - Sharjah</t>
+          <t>The Cove Rotana Resort jetty → Anantara Mina Al Arab Ras Al Khaimah Resort jetty</t>
         </is>
       </c>
       <c r="D23" s="31" t="n">
-        <v>2.7</v>
+        <v>2.2</v>
       </c>
       <c r="E23" s="26" t="n">
         <v>35</v>
@@ -5927,7 +6024,7 @@
         <v/>
       </c>
       <c r="AL23" s="34">
-        <f>IF(OR(AG23="",R23=0),"",MIN(IF(AS23="",9.9E+99,AS23),FLOOR(AK23/R23,1)))</f>
+        <f>IF(OR(AG23="",R23=0),"",MIN(IF(AT23="",9.9E+99,AT23),FLOOR(AK23/R23,1)))</f>
         <v/>
       </c>
       <c r="AM23" s="38">
@@ -5935,7 +6032,7 @@
         <v/>
       </c>
       <c r="AN23" s="36">
-        <f>IF(OR(AG23="",R23=0),"",MIN(IF(AS23="",9.9E+99,AS23),AK23/R23))</f>
+        <f>IF(OR(AG23="",R23=0),"",MIN(IF(AT23="",9.9E+99,AT23),AK23/R23))</f>
         <v/>
       </c>
       <c r="AO23" s="38">
@@ -5943,23 +6040,28 @@
         <v/>
       </c>
       <c r="AP23" s="40" t="n"/>
-      <c r="AQ23" s="41" t="n"/>
+      <c r="AQ23" s="32" t="inlineStr">
+        <is>
+          <t>Grounded</t>
+        </is>
+      </c>
       <c r="AR23" s="41" t="n"/>
-      <c r="AS23" s="42" t="n"/>
-      <c r="AT23" s="43">
+      <c r="AS23" s="41" t="n"/>
+      <c r="AT23" s="42" t="n"/>
+      <c r="AU23" s="43">
         <f>IF(((S23*pax_cap*load_thin*ROUND(K23*L23*revleg_thin,0))-(((battery/range_nm)*D23*ROUND(K23*L23*revleg_thin,0)*VLOOKUP(B23,country_opex,3,FALSE))+V23+W23+X23+Y23+Z23))&lt;=0,"",VLOOKUP(B23,country_opex,7,FALSE)/((S23*pax_cap*load_thin*ROUND(K23*L23*revleg_thin,0))-(((battery/range_nm)*D23*ROUND(K23*L23*revleg_thin,0)*VLOOKUP(B23,country_opex,3,FALSE))+V23+W23+X23+Y23+Z23)))</f>
         <v/>
       </c>
-      <c r="AU23" s="43">
+      <c r="AV23" s="43">
         <f>IF(((S23*pax_cap*load_mid*ROUND(K23*L23*revleg_mid,0))-(((battery/range_nm)*D23*ROUND(K23*L23*revleg_mid,0)*VLOOKUP(B23,country_opex,3,FALSE))+V23+W23+X23+Y23+Z23))&lt;=0,"",VLOOKUP(B23,country_opex,7,FALSE)/((S23*pax_cap*load_mid*ROUND(K23*L23*revleg_mid,0))-(((battery/range_nm)*D23*ROUND(K23*L23*revleg_mid,0)*VLOOKUP(B23,country_opex,3,FALSE))+V23+W23+X23+Y23+Z23)))</f>
         <v/>
       </c>
-      <c r="AV23" s="43">
+      <c r="AW23" s="43">
         <f>IF(((S23*pax_cap*load_full*ROUND(K23*L23*revleg_full,0))-(((battery/range_nm)*D23*ROUND(K23*L23*revleg_full,0)*VLOOKUP(B23,country_opex,3,FALSE))+V23+W23+X23+Y23+Z23))&lt;=0,"",VLOOKUP(B23,country_opex,7,FALSE)/((S23*pax_cap*load_full*ROUND(K23*L23*revleg_full,0))-(((battery/range_nm)*D23*ROUND(K23*L23*revleg_full,0)*VLOOKUP(B23,country_opex,3,FALSE))+V23+W23+X23+Y23+Z23)))</f>
         <v/>
       </c>
-      <c r="AW23" s="44" t="n"/>
       <c r="AX23" s="44" t="n"/>
+      <c r="AY23" s="44" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="29" t="inlineStr">
@@ -5974,11 +6076,11 @@
       </c>
       <c r="C24" s="30" t="inlineStr">
         <is>
-          <t>ميناء صيادين غليلة → ميناء صيادين خورخوير</t>
+          <t>ميناء صيادين غليلة → Sha'am Fishing Boat Harbour</t>
         </is>
       </c>
       <c r="D24" s="31" t="n">
-        <v>2.8</v>
+        <v>2.5</v>
       </c>
       <c r="E24" s="26" t="n">
         <v>35</v>
@@ -6113,7 +6215,7 @@
         <v/>
       </c>
       <c r="AL24" s="34">
-        <f>IF(OR(AG24="",R24=0),"",MIN(IF(AS24="",9.9E+99,AS24),FLOOR(AK24/R24,1)))</f>
+        <f>IF(OR(AG24="",R24=0),"",MIN(IF(AT24="",9.9E+99,AT24),FLOOR(AK24/R24,1)))</f>
         <v/>
       </c>
       <c r="AM24" s="38">
@@ -6121,7 +6223,7 @@
         <v/>
       </c>
       <c r="AN24" s="36">
-        <f>IF(OR(AG24="",R24=0),"",MIN(IF(AS24="",9.9E+99,AS24),AK24/R24))</f>
+        <f>IF(OR(AG24="",R24=0),"",MIN(IF(AT24="",9.9E+99,AT24),AK24/R24))</f>
         <v/>
       </c>
       <c r="AO24" s="38">
@@ -6129,23 +6231,28 @@
         <v/>
       </c>
       <c r="AP24" s="40" t="n"/>
-      <c r="AQ24" s="41" t="n"/>
+      <c r="AQ24" s="32" t="inlineStr">
+        <is>
+          <t>Grounded</t>
+        </is>
+      </c>
       <c r="AR24" s="41" t="n"/>
-      <c r="AS24" s="42" t="n"/>
-      <c r="AT24" s="43">
+      <c r="AS24" s="41" t="n"/>
+      <c r="AT24" s="42" t="n"/>
+      <c r="AU24" s="43">
         <f>IF(((S24*pax_cap*load_thin*ROUND(K24*L24*revleg_thin,0))-(((battery/range_nm)*D24*ROUND(K24*L24*revleg_thin,0)*VLOOKUP(B24,country_opex,3,FALSE))+V24+W24+X24+Y24+Z24))&lt;=0,"",VLOOKUP(B24,country_opex,7,FALSE)/((S24*pax_cap*load_thin*ROUND(K24*L24*revleg_thin,0))-(((battery/range_nm)*D24*ROUND(K24*L24*revleg_thin,0)*VLOOKUP(B24,country_opex,3,FALSE))+V24+W24+X24+Y24+Z24)))</f>
         <v/>
       </c>
-      <c r="AU24" s="43">
+      <c r="AV24" s="43">
         <f>IF(((S24*pax_cap*load_mid*ROUND(K24*L24*revleg_mid,0))-(((battery/range_nm)*D24*ROUND(K24*L24*revleg_mid,0)*VLOOKUP(B24,country_opex,3,FALSE))+V24+W24+X24+Y24+Z24))&lt;=0,"",VLOOKUP(B24,country_opex,7,FALSE)/((S24*pax_cap*load_mid*ROUND(K24*L24*revleg_mid,0))-(((battery/range_nm)*D24*ROUND(K24*L24*revleg_mid,0)*VLOOKUP(B24,country_opex,3,FALSE))+V24+W24+X24+Y24+Z24)))</f>
         <v/>
       </c>
-      <c r="AV24" s="43">
+      <c r="AW24" s="43">
         <f>IF(((S24*pax_cap*load_full*ROUND(K24*L24*revleg_full,0))-(((battery/range_nm)*D24*ROUND(K24*L24*revleg_full,0)*VLOOKUP(B24,country_opex,3,FALSE))+V24+W24+X24+Y24+Z24))&lt;=0,"",VLOOKUP(B24,country_opex,7,FALSE)/((S24*pax_cap*load_full*ROUND(K24*L24*revleg_full,0))-(((battery/range_nm)*D24*ROUND(K24*L24*revleg_full,0)*VLOOKUP(B24,country_opex,3,FALSE))+V24+W24+X24+Y24+Z24)))</f>
         <v/>
       </c>
-      <c r="AW24" s="44" t="n"/>
       <c r="AX24" s="44" t="n"/>
+      <c r="AY24" s="44" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="29" t="inlineStr">
@@ -6160,11 +6267,11 @@
       </c>
       <c r="C25" s="30" t="inlineStr">
         <is>
-          <t>Acacia by Bin Majid jetty → The Cove Rotana Resort jetty</t>
+          <t>Daba Port → Dibba Al-Hisn Marina - Sharjah</t>
         </is>
       </c>
       <c r="D25" s="31" t="n">
-        <v>2.9</v>
+        <v>2.7</v>
       </c>
       <c r="E25" s="26" t="n">
         <v>35</v>
@@ -6299,7 +6406,7 @@
         <v/>
       </c>
       <c r="AL25" s="34">
-        <f>IF(OR(AG25="",R25=0),"",MIN(IF(AS25="",9.9E+99,AS25),FLOOR(AK25/R25,1)))</f>
+        <f>IF(OR(AG25="",R25=0),"",MIN(IF(AT25="",9.9E+99,AT25),FLOOR(AK25/R25,1)))</f>
         <v/>
       </c>
       <c r="AM25" s="38">
@@ -6307,7 +6414,7 @@
         <v/>
       </c>
       <c r="AN25" s="36">
-        <f>IF(OR(AG25="",R25=0),"",MIN(IF(AS25="",9.9E+99,AS25),AK25/R25))</f>
+        <f>IF(OR(AG25="",R25=0),"",MIN(IF(AT25="",9.9E+99,AT25),AK25/R25))</f>
         <v/>
       </c>
       <c r="AO25" s="38">
@@ -6315,23 +6422,28 @@
         <v/>
       </c>
       <c r="AP25" s="40" t="n"/>
-      <c r="AQ25" s="41" t="n"/>
+      <c r="AQ25" s="32" t="inlineStr">
+        <is>
+          <t>Grounded</t>
+        </is>
+      </c>
       <c r="AR25" s="41" t="n"/>
-      <c r="AS25" s="42" t="n"/>
-      <c r="AT25" s="43">
+      <c r="AS25" s="41" t="n"/>
+      <c r="AT25" s="42" t="n"/>
+      <c r="AU25" s="43">
         <f>IF(((S25*pax_cap*load_thin*ROUND(K25*L25*revleg_thin,0))-(((battery/range_nm)*D25*ROUND(K25*L25*revleg_thin,0)*VLOOKUP(B25,country_opex,3,FALSE))+V25+W25+X25+Y25+Z25))&lt;=0,"",VLOOKUP(B25,country_opex,7,FALSE)/((S25*pax_cap*load_thin*ROUND(K25*L25*revleg_thin,0))-(((battery/range_nm)*D25*ROUND(K25*L25*revleg_thin,0)*VLOOKUP(B25,country_opex,3,FALSE))+V25+W25+X25+Y25+Z25)))</f>
         <v/>
       </c>
-      <c r="AU25" s="43">
+      <c r="AV25" s="43">
         <f>IF(((S25*pax_cap*load_mid*ROUND(K25*L25*revleg_mid,0))-(((battery/range_nm)*D25*ROUND(K25*L25*revleg_mid,0)*VLOOKUP(B25,country_opex,3,FALSE))+V25+W25+X25+Y25+Z25))&lt;=0,"",VLOOKUP(B25,country_opex,7,FALSE)/((S25*pax_cap*load_mid*ROUND(K25*L25*revleg_mid,0))-(((battery/range_nm)*D25*ROUND(K25*L25*revleg_mid,0)*VLOOKUP(B25,country_opex,3,FALSE))+V25+W25+X25+Y25+Z25)))</f>
         <v/>
       </c>
-      <c r="AV25" s="43">
+      <c r="AW25" s="43">
         <f>IF(((S25*pax_cap*load_full*ROUND(K25*L25*revleg_full,0))-(((battery/range_nm)*D25*ROUND(K25*L25*revleg_full,0)*VLOOKUP(B25,country_opex,3,FALSE))+V25+W25+X25+Y25+Z25))&lt;=0,"",VLOOKUP(B25,country_opex,7,FALSE)/((S25*pax_cap*load_full*ROUND(K25*L25*revleg_full,0))-(((battery/range_nm)*D25*ROUND(K25*L25*revleg_full,0)*VLOOKUP(B25,country_opex,3,FALSE))+V25+W25+X25+Y25+Z25)))</f>
         <v/>
       </c>
-      <c r="AW25" s="44" t="n"/>
       <c r="AX25" s="44" t="n"/>
+      <c r="AY25" s="44" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="29" t="inlineStr">
@@ -6346,11 +6458,11 @@
       </c>
       <c r="C26" s="30" t="inlineStr">
         <is>
-          <t>Raksa → Hilton Garden Inn Ras Al Khaimah (Corniche) jetty</t>
+          <t>ميناء صيادين غليلة → ميناء صيادين خورخوير</t>
         </is>
       </c>
       <c r="D26" s="31" t="n">
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="E26" s="26" t="n">
         <v>35</v>
@@ -6485,7 +6597,7 @@
         <v/>
       </c>
       <c r="AL26" s="34">
-        <f>IF(OR(AG26="",R26=0),"",MIN(IF(AS26="",9.9E+99,AS26),FLOOR(AK26/R26,1)))</f>
+        <f>IF(OR(AG26="",R26=0),"",MIN(IF(AT26="",9.9E+99,AT26),FLOOR(AK26/R26,1)))</f>
         <v/>
       </c>
       <c r="AM26" s="38">
@@ -6493,7 +6605,7 @@
         <v/>
       </c>
       <c r="AN26" s="36">
-        <f>IF(OR(AG26="",R26=0),"",MIN(IF(AS26="",9.9E+99,AS26),AK26/R26))</f>
+        <f>IF(OR(AG26="",R26=0),"",MIN(IF(AT26="",9.9E+99,AT26),AK26/R26))</f>
         <v/>
       </c>
       <c r="AO26" s="38">
@@ -6501,23 +6613,28 @@
         <v/>
       </c>
       <c r="AP26" s="40" t="n"/>
-      <c r="AQ26" s="41" t="n"/>
+      <c r="AQ26" s="32" t="inlineStr">
+        <is>
+          <t>Grounded</t>
+        </is>
+      </c>
       <c r="AR26" s="41" t="n"/>
-      <c r="AS26" s="42" t="n"/>
-      <c r="AT26" s="43">
+      <c r="AS26" s="41" t="n"/>
+      <c r="AT26" s="42" t="n"/>
+      <c r="AU26" s="43">
         <f>IF(((S26*pax_cap*load_thin*ROUND(K26*L26*revleg_thin,0))-(((battery/range_nm)*D26*ROUND(K26*L26*revleg_thin,0)*VLOOKUP(B26,country_opex,3,FALSE))+V26+W26+X26+Y26+Z26))&lt;=0,"",VLOOKUP(B26,country_opex,7,FALSE)/((S26*pax_cap*load_thin*ROUND(K26*L26*revleg_thin,0))-(((battery/range_nm)*D26*ROUND(K26*L26*revleg_thin,0)*VLOOKUP(B26,country_opex,3,FALSE))+V26+W26+X26+Y26+Z26)))</f>
         <v/>
       </c>
-      <c r="AU26" s="43">
+      <c r="AV26" s="43">
         <f>IF(((S26*pax_cap*load_mid*ROUND(K26*L26*revleg_mid,0))-(((battery/range_nm)*D26*ROUND(K26*L26*revleg_mid,0)*VLOOKUP(B26,country_opex,3,FALSE))+V26+W26+X26+Y26+Z26))&lt;=0,"",VLOOKUP(B26,country_opex,7,FALSE)/((S26*pax_cap*load_mid*ROUND(K26*L26*revleg_mid,0))-(((battery/range_nm)*D26*ROUND(K26*L26*revleg_mid,0)*VLOOKUP(B26,country_opex,3,FALSE))+V26+W26+X26+Y26+Z26)))</f>
         <v/>
       </c>
-      <c r="AV26" s="43">
+      <c r="AW26" s="43">
         <f>IF(((S26*pax_cap*load_full*ROUND(K26*L26*revleg_full,0))-(((battery/range_nm)*D26*ROUND(K26*L26*revleg_full,0)*VLOOKUP(B26,country_opex,3,FALSE))+V26+W26+X26+Y26+Z26))&lt;=0,"",VLOOKUP(B26,country_opex,7,FALSE)/((S26*pax_cap*load_full*ROUND(K26*L26*revleg_full,0))-(((battery/range_nm)*D26*ROUND(K26*L26*revleg_full,0)*VLOOKUP(B26,country_opex,3,FALSE))+V26+W26+X26+Y26+Z26)))</f>
         <v/>
       </c>
-      <c r="AW26" s="44" t="n"/>
       <c r="AX26" s="44" t="n"/>
+      <c r="AY26" s="44" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="29" t="inlineStr">
@@ -6532,11 +6649,11 @@
       </c>
       <c r="C27" s="30" t="inlineStr">
         <is>
-          <t>Bin Majid Beach Resort jetty → The Cove Rotana Resort jetty</t>
+          <t>Acacia by Bin Majid jetty → The Cove Rotana Resort jetty</t>
         </is>
       </c>
       <c r="D27" s="31" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="E27" s="26" t="n">
         <v>35</v>
@@ -6671,7 +6788,7 @@
         <v/>
       </c>
       <c r="AL27" s="34">
-        <f>IF(OR(AG27="",R27=0),"",MIN(IF(AS27="",9.9E+99,AS27),FLOOR(AK27/R27,1)))</f>
+        <f>IF(OR(AG27="",R27=0),"",MIN(IF(AT27="",9.9E+99,AT27),FLOOR(AK27/R27,1)))</f>
         <v/>
       </c>
       <c r="AM27" s="38">
@@ -6679,7 +6796,7 @@
         <v/>
       </c>
       <c r="AN27" s="36">
-        <f>IF(OR(AG27="",R27=0),"",MIN(IF(AS27="",9.9E+99,AS27),AK27/R27))</f>
+        <f>IF(OR(AG27="",R27=0),"",MIN(IF(AT27="",9.9E+99,AT27),AK27/R27))</f>
         <v/>
       </c>
       <c r="AO27" s="38">
@@ -6687,23 +6804,28 @@
         <v/>
       </c>
       <c r="AP27" s="40" t="n"/>
-      <c r="AQ27" s="41" t="n"/>
+      <c r="AQ27" s="32" t="inlineStr">
+        <is>
+          <t>Grounded</t>
+        </is>
+      </c>
       <c r="AR27" s="41" t="n"/>
-      <c r="AS27" s="42" t="n"/>
-      <c r="AT27" s="43">
+      <c r="AS27" s="41" t="n"/>
+      <c r="AT27" s="42" t="n"/>
+      <c r="AU27" s="43">
         <f>IF(((S27*pax_cap*load_thin*ROUND(K27*L27*revleg_thin,0))-(((battery/range_nm)*D27*ROUND(K27*L27*revleg_thin,0)*VLOOKUP(B27,country_opex,3,FALSE))+V27+W27+X27+Y27+Z27))&lt;=0,"",VLOOKUP(B27,country_opex,7,FALSE)/((S27*pax_cap*load_thin*ROUND(K27*L27*revleg_thin,0))-(((battery/range_nm)*D27*ROUND(K27*L27*revleg_thin,0)*VLOOKUP(B27,country_opex,3,FALSE))+V27+W27+X27+Y27+Z27)))</f>
         <v/>
       </c>
-      <c r="AU27" s="43">
+      <c r="AV27" s="43">
         <f>IF(((S27*pax_cap*load_mid*ROUND(K27*L27*revleg_mid,0))-(((battery/range_nm)*D27*ROUND(K27*L27*revleg_mid,0)*VLOOKUP(B27,country_opex,3,FALSE))+V27+W27+X27+Y27+Z27))&lt;=0,"",VLOOKUP(B27,country_opex,7,FALSE)/((S27*pax_cap*load_mid*ROUND(K27*L27*revleg_mid,0))-(((battery/range_nm)*D27*ROUND(K27*L27*revleg_mid,0)*VLOOKUP(B27,country_opex,3,FALSE))+V27+W27+X27+Y27+Z27)))</f>
         <v/>
       </c>
-      <c r="AV27" s="43">
+      <c r="AW27" s="43">
         <f>IF(((S27*pax_cap*load_full*ROUND(K27*L27*revleg_full,0))-(((battery/range_nm)*D27*ROUND(K27*L27*revleg_full,0)*VLOOKUP(B27,country_opex,3,FALSE))+V27+W27+X27+Y27+Z27))&lt;=0,"",VLOOKUP(B27,country_opex,7,FALSE)/((S27*pax_cap*load_full*ROUND(K27*L27*revleg_full,0))-(((battery/range_nm)*D27*ROUND(K27*L27*revleg_full,0)*VLOOKUP(B27,country_opex,3,FALSE))+V27+W27+X27+Y27+Z27)))</f>
         <v/>
       </c>
-      <c r="AW27" s="44" t="n"/>
       <c r="AX27" s="44" t="n"/>
+      <c r="AY27" s="44" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="29" t="inlineStr">
@@ -6718,11 +6840,11 @@
       </c>
       <c r="C28" s="30" t="inlineStr">
         <is>
-          <t>Al Zorah Marina 1 → Hamriyah Port Main Harbour</t>
+          <t>Bin Majid Beach Resort jetty → The Cove Rotana Resort jetty</t>
         </is>
       </c>
       <c r="D28" s="31" t="n">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="E28" s="26" t="n">
         <v>35</v>
@@ -6857,7 +6979,7 @@
         <v/>
       </c>
       <c r="AL28" s="34">
-        <f>IF(OR(AG28="",R28=0),"",MIN(IF(AS28="",9.9E+99,AS28),FLOOR(AK28/R28,1)))</f>
+        <f>IF(OR(AG28="",R28=0),"",MIN(IF(AT28="",9.9E+99,AT28),FLOOR(AK28/R28,1)))</f>
         <v/>
       </c>
       <c r="AM28" s="38">
@@ -6865,7 +6987,7 @@
         <v/>
       </c>
       <c r="AN28" s="36">
-        <f>IF(OR(AG28="",R28=0),"",MIN(IF(AS28="",9.9E+99,AS28),AK28/R28))</f>
+        <f>IF(OR(AG28="",R28=0),"",MIN(IF(AT28="",9.9E+99,AT28),AK28/R28))</f>
         <v/>
       </c>
       <c r="AO28" s="38">
@@ -6873,23 +6995,28 @@
         <v/>
       </c>
       <c r="AP28" s="40" t="n"/>
-      <c r="AQ28" s="41" t="n"/>
+      <c r="AQ28" s="32" t="inlineStr">
+        <is>
+          <t>Grounded</t>
+        </is>
+      </c>
       <c r="AR28" s="41" t="n"/>
-      <c r="AS28" s="42" t="n"/>
-      <c r="AT28" s="43">
+      <c r="AS28" s="41" t="n"/>
+      <c r="AT28" s="42" t="n"/>
+      <c r="AU28" s="43">
         <f>IF(((S28*pax_cap*load_thin*ROUND(K28*L28*revleg_thin,0))-(((battery/range_nm)*D28*ROUND(K28*L28*revleg_thin,0)*VLOOKUP(B28,country_opex,3,FALSE))+V28+W28+X28+Y28+Z28))&lt;=0,"",VLOOKUP(B28,country_opex,7,FALSE)/((S28*pax_cap*load_thin*ROUND(K28*L28*revleg_thin,0))-(((battery/range_nm)*D28*ROUND(K28*L28*revleg_thin,0)*VLOOKUP(B28,country_opex,3,FALSE))+V28+W28+X28+Y28+Z28)))</f>
         <v/>
       </c>
-      <c r="AU28" s="43">
+      <c r="AV28" s="43">
         <f>IF(((S28*pax_cap*load_mid*ROUND(K28*L28*revleg_mid,0))-(((battery/range_nm)*D28*ROUND(K28*L28*revleg_mid,0)*VLOOKUP(B28,country_opex,3,FALSE))+V28+W28+X28+Y28+Z28))&lt;=0,"",VLOOKUP(B28,country_opex,7,FALSE)/((S28*pax_cap*load_mid*ROUND(K28*L28*revleg_mid,0))-(((battery/range_nm)*D28*ROUND(K28*L28*revleg_mid,0)*VLOOKUP(B28,country_opex,3,FALSE))+V28+W28+X28+Y28+Z28)))</f>
         <v/>
       </c>
-      <c r="AV28" s="43">
+      <c r="AW28" s="43">
         <f>IF(((S28*pax_cap*load_full*ROUND(K28*L28*revleg_full,0))-(((battery/range_nm)*D28*ROUND(K28*L28*revleg_full,0)*VLOOKUP(B28,country_opex,3,FALSE))+V28+W28+X28+Y28+Z28))&lt;=0,"",VLOOKUP(B28,country_opex,7,FALSE)/((S28*pax_cap*load_full*ROUND(K28*L28*revleg_full,0))-(((battery/range_nm)*D28*ROUND(K28*L28*revleg_full,0)*VLOOKUP(B28,country_opex,3,FALSE))+V28+W28+X28+Y28+Z28)))</f>
         <v/>
       </c>
-      <c r="AW28" s="44" t="n"/>
       <c r="AX28" s="44" t="n"/>
+      <c r="AY28" s="44" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="29" t="inlineStr">
@@ -6904,11 +7031,11 @@
       </c>
       <c r="C29" s="30" t="inlineStr">
         <is>
-          <t>Sha'am coastal staging point → ميناء صيادين غليلة</t>
+          <t>Raksa → Hilton Garden Inn Ras Al Khaimah (Corniche) jetty</t>
         </is>
       </c>
       <c r="D29" s="31" t="n">
-        <v>3.9</v>
+        <v>3</v>
       </c>
       <c r="E29" s="26" t="n">
         <v>35</v>
@@ -7043,7 +7170,7 @@
         <v/>
       </c>
       <c r="AL29" s="34">
-        <f>IF(OR(AG29="",R29=0),"",MIN(IF(AS29="",9.9E+99,AS29),FLOOR(AK29/R29,1)))</f>
+        <f>IF(OR(AG29="",R29=0),"",MIN(IF(AT29="",9.9E+99,AT29),FLOOR(AK29/R29,1)))</f>
         <v/>
       </c>
       <c r="AM29" s="38">
@@ -7051,7 +7178,7 @@
         <v/>
       </c>
       <c r="AN29" s="36">
-        <f>IF(OR(AG29="",R29=0),"",MIN(IF(AS29="",9.9E+99,AS29),AK29/R29))</f>
+        <f>IF(OR(AG29="",R29=0),"",MIN(IF(AT29="",9.9E+99,AT29),AK29/R29))</f>
         <v/>
       </c>
       <c r="AO29" s="38">
@@ -7059,23 +7186,28 @@
         <v/>
       </c>
       <c r="AP29" s="40" t="n"/>
-      <c r="AQ29" s="41" t="n"/>
+      <c r="AQ29" s="32" t="inlineStr">
+        <is>
+          <t>Grounded</t>
+        </is>
+      </c>
       <c r="AR29" s="41" t="n"/>
-      <c r="AS29" s="42" t="n"/>
-      <c r="AT29" s="43">
+      <c r="AS29" s="41" t="n"/>
+      <c r="AT29" s="42" t="n"/>
+      <c r="AU29" s="43">
         <f>IF(((S29*pax_cap*load_thin*ROUND(K29*L29*revleg_thin,0))-(((battery/range_nm)*D29*ROUND(K29*L29*revleg_thin,0)*VLOOKUP(B29,country_opex,3,FALSE))+V29+W29+X29+Y29+Z29))&lt;=0,"",VLOOKUP(B29,country_opex,7,FALSE)/((S29*pax_cap*load_thin*ROUND(K29*L29*revleg_thin,0))-(((battery/range_nm)*D29*ROUND(K29*L29*revleg_thin,0)*VLOOKUP(B29,country_opex,3,FALSE))+V29+W29+X29+Y29+Z29)))</f>
         <v/>
       </c>
-      <c r="AU29" s="43">
+      <c r="AV29" s="43">
         <f>IF(((S29*pax_cap*load_mid*ROUND(K29*L29*revleg_mid,0))-(((battery/range_nm)*D29*ROUND(K29*L29*revleg_mid,0)*VLOOKUP(B29,country_opex,3,FALSE))+V29+W29+X29+Y29+Z29))&lt;=0,"",VLOOKUP(B29,country_opex,7,FALSE)/((S29*pax_cap*load_mid*ROUND(K29*L29*revleg_mid,0))-(((battery/range_nm)*D29*ROUND(K29*L29*revleg_mid,0)*VLOOKUP(B29,country_opex,3,FALSE))+V29+W29+X29+Y29+Z29)))</f>
         <v/>
       </c>
-      <c r="AV29" s="43">
+      <c r="AW29" s="43">
         <f>IF(((S29*pax_cap*load_full*ROUND(K29*L29*revleg_full,0))-(((battery/range_nm)*D29*ROUND(K29*L29*revleg_full,0)*VLOOKUP(B29,country_opex,3,FALSE))+V29+W29+X29+Y29+Z29))&lt;=0,"",VLOOKUP(B29,country_opex,7,FALSE)/((S29*pax_cap*load_full*ROUND(K29*L29*revleg_full,0))-(((battery/range_nm)*D29*ROUND(K29*L29*revleg_full,0)*VLOOKUP(B29,country_opex,3,FALSE))+V29+W29+X29+Y29+Z29)))</f>
         <v/>
       </c>
-      <c r="AW29" s="44" t="n"/>
       <c r="AX29" s="44" t="n"/>
+      <c r="AY29" s="44" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="29" t="inlineStr">
@@ -7090,11 +7222,11 @@
       </c>
       <c r="C30" s="30" t="inlineStr">
         <is>
-          <t>Ajman Marina → Hamriyah Port Main Harbour</t>
+          <t>Al Zorah Marina 1 → Hamriyah Port Main Harbour</t>
         </is>
       </c>
       <c r="D30" s="31" t="n">
-        <v>3.9</v>
+        <v>3.2</v>
       </c>
       <c r="E30" s="26" t="n">
         <v>35</v>
@@ -7229,7 +7361,7 @@
         <v/>
       </c>
       <c r="AL30" s="34">
-        <f>IF(OR(AG30="",R30=0),"",MIN(IF(AS30="",9.9E+99,AS30),FLOOR(AK30/R30,1)))</f>
+        <f>IF(OR(AG30="",R30=0),"",MIN(IF(AT30="",9.9E+99,AT30),FLOOR(AK30/R30,1)))</f>
         <v/>
       </c>
       <c r="AM30" s="38">
@@ -7237,7 +7369,7 @@
         <v/>
       </c>
       <c r="AN30" s="36">
-        <f>IF(OR(AG30="",R30=0),"",MIN(IF(AS30="",9.9E+99,AS30),AK30/R30))</f>
+        <f>IF(OR(AG30="",R30=0),"",MIN(IF(AT30="",9.9E+99,AT30),AK30/R30))</f>
         <v/>
       </c>
       <c r="AO30" s="38">
@@ -7245,23 +7377,28 @@
         <v/>
       </c>
       <c r="AP30" s="40" t="n"/>
-      <c r="AQ30" s="41" t="n"/>
+      <c r="AQ30" s="32" t="inlineStr">
+        <is>
+          <t>Grounded</t>
+        </is>
+      </c>
       <c r="AR30" s="41" t="n"/>
-      <c r="AS30" s="42" t="n"/>
-      <c r="AT30" s="43">
+      <c r="AS30" s="41" t="n"/>
+      <c r="AT30" s="42" t="n"/>
+      <c r="AU30" s="43">
         <f>IF(((S30*pax_cap*load_thin*ROUND(K30*L30*revleg_thin,0))-(((battery/range_nm)*D30*ROUND(K30*L30*revleg_thin,0)*VLOOKUP(B30,country_opex,3,FALSE))+V30+W30+X30+Y30+Z30))&lt;=0,"",VLOOKUP(B30,country_opex,7,FALSE)/((S30*pax_cap*load_thin*ROUND(K30*L30*revleg_thin,0))-(((battery/range_nm)*D30*ROUND(K30*L30*revleg_thin,0)*VLOOKUP(B30,country_opex,3,FALSE))+V30+W30+X30+Y30+Z30)))</f>
         <v/>
       </c>
-      <c r="AU30" s="43">
+      <c r="AV30" s="43">
         <f>IF(((S30*pax_cap*load_mid*ROUND(K30*L30*revleg_mid,0))-(((battery/range_nm)*D30*ROUND(K30*L30*revleg_mid,0)*VLOOKUP(B30,country_opex,3,FALSE))+V30+W30+X30+Y30+Z30))&lt;=0,"",VLOOKUP(B30,country_opex,7,FALSE)/((S30*pax_cap*load_mid*ROUND(K30*L30*revleg_mid,0))-(((battery/range_nm)*D30*ROUND(K30*L30*revleg_mid,0)*VLOOKUP(B30,country_opex,3,FALSE))+V30+W30+X30+Y30+Z30)))</f>
         <v/>
       </c>
-      <c r="AV30" s="43">
+      <c r="AW30" s="43">
         <f>IF(((S30*pax_cap*load_full*ROUND(K30*L30*revleg_full,0))-(((battery/range_nm)*D30*ROUND(K30*L30*revleg_full,0)*VLOOKUP(B30,country_opex,3,FALSE))+V30+W30+X30+Y30+Z30))&lt;=0,"",VLOOKUP(B30,country_opex,7,FALSE)/((S30*pax_cap*load_full*ROUND(K30*L30*revleg_full,0))-(((battery/range_nm)*D30*ROUND(K30*L30*revleg_full,0)*VLOOKUP(B30,country_opex,3,FALSE))+V30+W30+X30+Y30+Z30)))</f>
         <v/>
       </c>
-      <c r="AW30" s="44" t="n"/>
       <c r="AX30" s="44" t="n"/>
+      <c r="AY30" s="44" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="29" t="inlineStr">
@@ -7276,11 +7413,11 @@
       </c>
       <c r="C31" s="30" t="inlineStr">
         <is>
-          <t>ميناء صيادين خورخوير → Sha'am Fishing Boat Harbour</t>
+          <t>Ajman Marina → Hamriyah Port Main Harbour</t>
         </is>
       </c>
       <c r="D31" s="31" t="n">
-        <v>4.3</v>
+        <v>3.9</v>
       </c>
       <c r="E31" s="26" t="n">
         <v>35</v>
@@ -7415,7 +7552,7 @@
         <v/>
       </c>
       <c r="AL31" s="34">
-        <f>IF(OR(AG31="",R31=0),"",MIN(IF(AS31="",9.9E+99,AS31),FLOOR(AK31/R31,1)))</f>
+        <f>IF(OR(AG31="",R31=0),"",MIN(IF(AT31="",9.9E+99,AT31),FLOOR(AK31/R31,1)))</f>
         <v/>
       </c>
       <c r="AM31" s="38">
@@ -7423,7 +7560,7 @@
         <v/>
       </c>
       <c r="AN31" s="36">
-        <f>IF(OR(AG31="",R31=0),"",MIN(IF(AS31="",9.9E+99,AS31),AK31/R31))</f>
+        <f>IF(OR(AG31="",R31=0),"",MIN(IF(AT31="",9.9E+99,AT31),AK31/R31))</f>
         <v/>
       </c>
       <c r="AO31" s="38">
@@ -7431,23 +7568,28 @@
         <v/>
       </c>
       <c r="AP31" s="40" t="n"/>
-      <c r="AQ31" s="41" t="n"/>
+      <c r="AQ31" s="32" t="inlineStr">
+        <is>
+          <t>Grounded</t>
+        </is>
+      </c>
       <c r="AR31" s="41" t="n"/>
-      <c r="AS31" s="42" t="n"/>
-      <c r="AT31" s="43">
+      <c r="AS31" s="41" t="n"/>
+      <c r="AT31" s="42" t="n"/>
+      <c r="AU31" s="43">
         <f>IF(((S31*pax_cap*load_thin*ROUND(K31*L31*revleg_thin,0))-(((battery/range_nm)*D31*ROUND(K31*L31*revleg_thin,0)*VLOOKUP(B31,country_opex,3,FALSE))+V31+W31+X31+Y31+Z31))&lt;=0,"",VLOOKUP(B31,country_opex,7,FALSE)/((S31*pax_cap*load_thin*ROUND(K31*L31*revleg_thin,0))-(((battery/range_nm)*D31*ROUND(K31*L31*revleg_thin,0)*VLOOKUP(B31,country_opex,3,FALSE))+V31+W31+X31+Y31+Z31)))</f>
         <v/>
       </c>
-      <c r="AU31" s="43">
+      <c r="AV31" s="43">
         <f>IF(((S31*pax_cap*load_mid*ROUND(K31*L31*revleg_mid,0))-(((battery/range_nm)*D31*ROUND(K31*L31*revleg_mid,0)*VLOOKUP(B31,country_opex,3,FALSE))+V31+W31+X31+Y31+Z31))&lt;=0,"",VLOOKUP(B31,country_opex,7,FALSE)/((S31*pax_cap*load_mid*ROUND(K31*L31*revleg_mid,0))-(((battery/range_nm)*D31*ROUND(K31*L31*revleg_mid,0)*VLOOKUP(B31,country_opex,3,FALSE))+V31+W31+X31+Y31+Z31)))</f>
         <v/>
       </c>
-      <c r="AV31" s="43">
+      <c r="AW31" s="43">
         <f>IF(((S31*pax_cap*load_full*ROUND(K31*L31*revleg_full,0))-(((battery/range_nm)*D31*ROUND(K31*L31*revleg_full,0)*VLOOKUP(B31,country_opex,3,FALSE))+V31+W31+X31+Y31+Z31))&lt;=0,"",VLOOKUP(B31,country_opex,7,FALSE)/((S31*pax_cap*load_full*ROUND(K31*L31*revleg_full,0))-(((battery/range_nm)*D31*ROUND(K31*L31*revleg_full,0)*VLOOKUP(B31,country_opex,3,FALSE))+V31+W31+X31+Y31+Z31)))</f>
         <v/>
       </c>
-      <c r="AW31" s="44" t="n"/>
       <c r="AX31" s="44" t="n"/>
+      <c r="AY31" s="44" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="29" t="inlineStr">
@@ -7462,11 +7604,11 @@
       </c>
       <c r="C32" s="30" t="inlineStr">
         <is>
-          <t>Zighy Marina → Dibba Al-Hisn Marina - Sharjah</t>
+          <t>Sha'am coastal staging point → ميناء صيادين غليلة</t>
         </is>
       </c>
       <c r="D32" s="31" t="n">
-        <v>5.3</v>
+        <v>3.9</v>
       </c>
       <c r="E32" s="26" t="n">
         <v>35</v>
@@ -7601,7 +7743,7 @@
         <v/>
       </c>
       <c r="AL32" s="34">
-        <f>IF(OR(AG32="",R32=0),"",MIN(IF(AS32="",9.9E+99,AS32),FLOOR(AK32/R32,1)))</f>
+        <f>IF(OR(AG32="",R32=0),"",MIN(IF(AT32="",9.9E+99,AT32),FLOOR(AK32/R32,1)))</f>
         <v/>
       </c>
       <c r="AM32" s="38">
@@ -7609,7 +7751,7 @@
         <v/>
       </c>
       <c r="AN32" s="36">
-        <f>IF(OR(AG32="",R32=0),"",MIN(IF(AS32="",9.9E+99,AS32),AK32/R32))</f>
+        <f>IF(OR(AG32="",R32=0),"",MIN(IF(AT32="",9.9E+99,AT32),AK32/R32))</f>
         <v/>
       </c>
       <c r="AO32" s="38">
@@ -7617,23 +7759,28 @@
         <v/>
       </c>
       <c r="AP32" s="40" t="n"/>
-      <c r="AQ32" s="41" t="n"/>
+      <c r="AQ32" s="32" t="inlineStr">
+        <is>
+          <t>Grounded</t>
+        </is>
+      </c>
       <c r="AR32" s="41" t="n"/>
-      <c r="AS32" s="42" t="n"/>
-      <c r="AT32" s="43">
+      <c r="AS32" s="41" t="n"/>
+      <c r="AT32" s="42" t="n"/>
+      <c r="AU32" s="43">
         <f>IF(((S32*pax_cap*load_thin*ROUND(K32*L32*revleg_thin,0))-(((battery/range_nm)*D32*ROUND(K32*L32*revleg_thin,0)*VLOOKUP(B32,country_opex,3,FALSE))+V32+W32+X32+Y32+Z32))&lt;=0,"",VLOOKUP(B32,country_opex,7,FALSE)/((S32*pax_cap*load_thin*ROUND(K32*L32*revleg_thin,0))-(((battery/range_nm)*D32*ROUND(K32*L32*revleg_thin,0)*VLOOKUP(B32,country_opex,3,FALSE))+V32+W32+X32+Y32+Z32)))</f>
         <v/>
       </c>
-      <c r="AU32" s="43">
+      <c r="AV32" s="43">
         <f>IF(((S32*pax_cap*load_mid*ROUND(K32*L32*revleg_mid,0))-(((battery/range_nm)*D32*ROUND(K32*L32*revleg_mid,0)*VLOOKUP(B32,country_opex,3,FALSE))+V32+W32+X32+Y32+Z32))&lt;=0,"",VLOOKUP(B32,country_opex,7,FALSE)/((S32*pax_cap*load_mid*ROUND(K32*L32*revleg_mid,0))-(((battery/range_nm)*D32*ROUND(K32*L32*revleg_mid,0)*VLOOKUP(B32,country_opex,3,FALSE))+V32+W32+X32+Y32+Z32)))</f>
         <v/>
       </c>
-      <c r="AV32" s="43">
+      <c r="AW32" s="43">
         <f>IF(((S32*pax_cap*load_full*ROUND(K32*L32*revleg_full,0))-(((battery/range_nm)*D32*ROUND(K32*L32*revleg_full,0)*VLOOKUP(B32,country_opex,3,FALSE))+V32+W32+X32+Y32+Z32))&lt;=0,"",VLOOKUP(B32,country_opex,7,FALSE)/((S32*pax_cap*load_full*ROUND(K32*L32*revleg_full,0))-(((battery/range_nm)*D32*ROUND(K32*L32*revleg_full,0)*VLOOKUP(B32,country_opex,3,FALSE))+V32+W32+X32+Y32+Z32)))</f>
         <v/>
       </c>
-      <c r="AW32" s="44" t="n"/>
       <c r="AX32" s="44" t="n"/>
+      <c r="AY32" s="44" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="29" t="inlineStr">
@@ -7648,11 +7795,11 @@
       </c>
       <c r="C33" s="30" t="inlineStr">
         <is>
-          <t>Gumda Fishing Harbour → Sha'am coastal staging point</t>
+          <t>ميناء صيادين خورخوير → Sha'am Fishing Boat Harbour</t>
         </is>
       </c>
       <c r="D33" s="31" t="n">
-        <v>5.3</v>
+        <v>4.3</v>
       </c>
       <c r="E33" s="26" t="n">
         <v>35</v>
@@ -7787,7 +7934,7 @@
         <v/>
       </c>
       <c r="AL33" s="34">
-        <f>IF(OR(AG33="",R33=0),"",MIN(IF(AS33="",9.9E+99,AS33),FLOOR(AK33/R33,1)))</f>
+        <f>IF(OR(AG33="",R33=0),"",MIN(IF(AT33="",9.9E+99,AT33),FLOOR(AK33/R33,1)))</f>
         <v/>
       </c>
       <c r="AM33" s="38">
@@ -7795,7 +7942,7 @@
         <v/>
       </c>
       <c r="AN33" s="36">
-        <f>IF(OR(AG33="",R33=0),"",MIN(IF(AS33="",9.9E+99,AS33),AK33/R33))</f>
+        <f>IF(OR(AG33="",R33=0),"",MIN(IF(AT33="",9.9E+99,AT33),AK33/R33))</f>
         <v/>
       </c>
       <c r="AO33" s="38">
@@ -7803,23 +7950,28 @@
         <v/>
       </c>
       <c r="AP33" s="40" t="n"/>
-      <c r="AQ33" s="41" t="n"/>
+      <c r="AQ33" s="32" t="inlineStr">
+        <is>
+          <t>Grounded</t>
+        </is>
+      </c>
       <c r="AR33" s="41" t="n"/>
-      <c r="AS33" s="42" t="n"/>
-      <c r="AT33" s="43">
+      <c r="AS33" s="41" t="n"/>
+      <c r="AT33" s="42" t="n"/>
+      <c r="AU33" s="43">
         <f>IF(((S33*pax_cap*load_thin*ROUND(K33*L33*revleg_thin,0))-(((battery/range_nm)*D33*ROUND(K33*L33*revleg_thin,0)*VLOOKUP(B33,country_opex,3,FALSE))+V33+W33+X33+Y33+Z33))&lt;=0,"",VLOOKUP(B33,country_opex,7,FALSE)/((S33*pax_cap*load_thin*ROUND(K33*L33*revleg_thin,0))-(((battery/range_nm)*D33*ROUND(K33*L33*revleg_thin,0)*VLOOKUP(B33,country_opex,3,FALSE))+V33+W33+X33+Y33+Z33)))</f>
         <v/>
       </c>
-      <c r="AU33" s="43">
+      <c r="AV33" s="43">
         <f>IF(((S33*pax_cap*load_mid*ROUND(K33*L33*revleg_mid,0))-(((battery/range_nm)*D33*ROUND(K33*L33*revleg_mid,0)*VLOOKUP(B33,country_opex,3,FALSE))+V33+W33+X33+Y33+Z33))&lt;=0,"",VLOOKUP(B33,country_opex,7,FALSE)/((S33*pax_cap*load_mid*ROUND(K33*L33*revleg_mid,0))-(((battery/range_nm)*D33*ROUND(K33*L33*revleg_mid,0)*VLOOKUP(B33,country_opex,3,FALSE))+V33+W33+X33+Y33+Z33)))</f>
         <v/>
       </c>
-      <c r="AV33" s="43">
+      <c r="AW33" s="43">
         <f>IF(((S33*pax_cap*load_full*ROUND(K33*L33*revleg_full,0))-(((battery/range_nm)*D33*ROUND(K33*L33*revleg_full,0)*VLOOKUP(B33,country_opex,3,FALSE))+V33+W33+X33+Y33+Z33))&lt;=0,"",VLOOKUP(B33,country_opex,7,FALSE)/((S33*pax_cap*load_full*ROUND(K33*L33*revleg_full,0))-(((battery/range_nm)*D33*ROUND(K33*L33*revleg_full,0)*VLOOKUP(B33,country_opex,3,FALSE))+V33+W33+X33+Y33+Z33)))</f>
         <v/>
       </c>
-      <c r="AW33" s="44" t="n"/>
       <c r="AX33" s="44" t="n"/>
+      <c r="AY33" s="44" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="29" t="inlineStr">
@@ -7834,11 +7986,11 @@
       </c>
       <c r="C34" s="30" t="inlineStr">
         <is>
-          <t>Gumda Fishing Harbour → Sha'am Fishing Boat Harbour</t>
+          <t>Gumda Fishing Harbour → Sha'am coastal staging point</t>
         </is>
       </c>
       <c r="D34" s="31" t="n">
-        <v>7.2</v>
+        <v>5.3</v>
       </c>
       <c r="E34" s="26" t="n">
         <v>35</v>
@@ -7973,7 +8125,7 @@
         <v/>
       </c>
       <c r="AL34" s="34">
-        <f>IF(OR(AG34="",R34=0),"",MIN(IF(AS34="",9.9E+99,AS34),FLOOR(AK34/R34,1)))</f>
+        <f>IF(OR(AG34="",R34=0),"",MIN(IF(AT34="",9.9E+99,AT34),FLOOR(AK34/R34,1)))</f>
         <v/>
       </c>
       <c r="AM34" s="38">
@@ -7981,7 +8133,7 @@
         <v/>
       </c>
       <c r="AN34" s="36">
-        <f>IF(OR(AG34="",R34=0),"",MIN(IF(AS34="",9.9E+99,AS34),AK34/R34))</f>
+        <f>IF(OR(AG34="",R34=0),"",MIN(IF(AT34="",9.9E+99,AT34),AK34/R34))</f>
         <v/>
       </c>
       <c r="AO34" s="38">
@@ -7989,23 +8141,28 @@
         <v/>
       </c>
       <c r="AP34" s="40" t="n"/>
-      <c r="AQ34" s="41" t="n"/>
+      <c r="AQ34" s="32" t="inlineStr">
+        <is>
+          <t>Grounded</t>
+        </is>
+      </c>
       <c r="AR34" s="41" t="n"/>
-      <c r="AS34" s="42" t="n"/>
-      <c r="AT34" s="43">
+      <c r="AS34" s="41" t="n"/>
+      <c r="AT34" s="42" t="n"/>
+      <c r="AU34" s="43">
         <f>IF(((S34*pax_cap*load_thin*ROUND(K34*L34*revleg_thin,0))-(((battery/range_nm)*D34*ROUND(K34*L34*revleg_thin,0)*VLOOKUP(B34,country_opex,3,FALSE))+V34+W34+X34+Y34+Z34))&lt;=0,"",VLOOKUP(B34,country_opex,7,FALSE)/((S34*pax_cap*load_thin*ROUND(K34*L34*revleg_thin,0))-(((battery/range_nm)*D34*ROUND(K34*L34*revleg_thin,0)*VLOOKUP(B34,country_opex,3,FALSE))+V34+W34+X34+Y34+Z34)))</f>
         <v/>
       </c>
-      <c r="AU34" s="43">
+      <c r="AV34" s="43">
         <f>IF(((S34*pax_cap*load_mid*ROUND(K34*L34*revleg_mid,0))-(((battery/range_nm)*D34*ROUND(K34*L34*revleg_mid,0)*VLOOKUP(B34,country_opex,3,FALSE))+V34+W34+X34+Y34+Z34))&lt;=0,"",VLOOKUP(B34,country_opex,7,FALSE)/((S34*pax_cap*load_mid*ROUND(K34*L34*revleg_mid,0))-(((battery/range_nm)*D34*ROUND(K34*L34*revleg_mid,0)*VLOOKUP(B34,country_opex,3,FALSE))+V34+W34+X34+Y34+Z34)))</f>
         <v/>
       </c>
-      <c r="AV34" s="43">
+      <c r="AW34" s="43">
         <f>IF(((S34*pax_cap*load_full*ROUND(K34*L34*revleg_full,0))-(((battery/range_nm)*D34*ROUND(K34*L34*revleg_full,0)*VLOOKUP(B34,country_opex,3,FALSE))+V34+W34+X34+Y34+Z34))&lt;=0,"",VLOOKUP(B34,country_opex,7,FALSE)/((S34*pax_cap*load_full*ROUND(K34*L34*revleg_full,0))-(((battery/range_nm)*D34*ROUND(K34*L34*revleg_full,0)*VLOOKUP(B34,country_opex,3,FALSE))+V34+W34+X34+Y34+Z34)))</f>
         <v/>
       </c>
-      <c r="AW34" s="44" t="n"/>
       <c r="AX34" s="44" t="n"/>
+      <c r="AY34" s="44" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="29" t="inlineStr">
@@ -8020,11 +8177,11 @@
       </c>
       <c r="C35" s="30" t="inlineStr">
         <is>
-          <t>UAQ Marine Club → Hamriyah Port Main Harbour</t>
+          <t>Zighy Marina → Dibba Al-Hisn Marina - Sharjah</t>
         </is>
       </c>
       <c r="D35" s="31" t="n">
-        <v>10.5</v>
+        <v>5.3</v>
       </c>
       <c r="E35" s="26" t="n">
         <v>35</v>
@@ -8159,7 +8316,7 @@
         <v/>
       </c>
       <c r="AL35" s="34">
-        <f>IF(OR(AG35="",R35=0),"",MIN(IF(AS35="",9.9E+99,AS35),FLOOR(AK35/R35,1)))</f>
+        <f>IF(OR(AG35="",R35=0),"",MIN(IF(AT35="",9.9E+99,AT35),FLOOR(AK35/R35,1)))</f>
         <v/>
       </c>
       <c r="AM35" s="38">
@@ -8167,7 +8324,7 @@
         <v/>
       </c>
       <c r="AN35" s="36">
-        <f>IF(OR(AG35="",R35=0),"",MIN(IF(AS35="",9.9E+99,AS35),AK35/R35))</f>
+        <f>IF(OR(AG35="",R35=0),"",MIN(IF(AT35="",9.9E+99,AT35),AK35/R35))</f>
         <v/>
       </c>
       <c r="AO35" s="38">
@@ -8175,23 +8332,28 @@
         <v/>
       </c>
       <c r="AP35" s="40" t="n"/>
-      <c r="AQ35" s="41" t="n"/>
+      <c r="AQ35" s="32" t="inlineStr">
+        <is>
+          <t>Grounded</t>
+        </is>
+      </c>
       <c r="AR35" s="41" t="n"/>
-      <c r="AS35" s="42" t="n"/>
-      <c r="AT35" s="43">
+      <c r="AS35" s="41" t="n"/>
+      <c r="AT35" s="42" t="n"/>
+      <c r="AU35" s="43">
         <f>IF(((S35*pax_cap*load_thin*ROUND(K35*L35*revleg_thin,0))-(((battery/range_nm)*D35*ROUND(K35*L35*revleg_thin,0)*VLOOKUP(B35,country_opex,3,FALSE))+V35+W35+X35+Y35+Z35))&lt;=0,"",VLOOKUP(B35,country_opex,7,FALSE)/((S35*pax_cap*load_thin*ROUND(K35*L35*revleg_thin,0))-(((battery/range_nm)*D35*ROUND(K35*L35*revleg_thin,0)*VLOOKUP(B35,country_opex,3,FALSE))+V35+W35+X35+Y35+Z35)))</f>
         <v/>
       </c>
-      <c r="AU35" s="43">
+      <c r="AV35" s="43">
         <f>IF(((S35*pax_cap*load_mid*ROUND(K35*L35*revleg_mid,0))-(((battery/range_nm)*D35*ROUND(K35*L35*revleg_mid,0)*VLOOKUP(B35,country_opex,3,FALSE))+V35+W35+X35+Y35+Z35))&lt;=0,"",VLOOKUP(B35,country_opex,7,FALSE)/((S35*pax_cap*load_mid*ROUND(K35*L35*revleg_mid,0))-(((battery/range_nm)*D35*ROUND(K35*L35*revleg_mid,0)*VLOOKUP(B35,country_opex,3,FALSE))+V35+W35+X35+Y35+Z35)))</f>
         <v/>
       </c>
-      <c r="AV35" s="43">
+      <c r="AW35" s="43">
         <f>IF(((S35*pax_cap*load_full*ROUND(K35*L35*revleg_full,0))-(((battery/range_nm)*D35*ROUND(K35*L35*revleg_full,0)*VLOOKUP(B35,country_opex,3,FALSE))+V35+W35+X35+Y35+Z35))&lt;=0,"",VLOOKUP(B35,country_opex,7,FALSE)/((S35*pax_cap*load_full*ROUND(K35*L35*revleg_full,0))-(((battery/range_nm)*D35*ROUND(K35*L35*revleg_full,0)*VLOOKUP(B35,country_opex,3,FALSE))+V35+W35+X35+Y35+Z35)))</f>
         <v/>
       </c>
-      <c r="AW35" s="44" t="n"/>
       <c r="AX35" s="44" t="n"/>
+      <c r="AY35" s="44" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="29" t="inlineStr">
@@ -8206,11 +8368,11 @@
       </c>
       <c r="C36" s="30" t="inlineStr">
         <is>
-          <t>UAQ Marine Club → Rixos Bab Al Bahr beach jetty</t>
+          <t>Gumda Fishing Harbour → Sha'am Fishing Boat Harbour</t>
         </is>
       </c>
       <c r="D36" s="31" t="n">
-        <v>11.8</v>
+        <v>7.2</v>
       </c>
       <c r="E36" s="26" t="n">
         <v>35</v>
@@ -8345,7 +8507,7 @@
         <v/>
       </c>
       <c r="AL36" s="34">
-        <f>IF(OR(AG36="",R36=0),"",MIN(IF(AS36="",9.9E+99,AS36),FLOOR(AK36/R36,1)))</f>
+        <f>IF(OR(AG36="",R36=0),"",MIN(IF(AT36="",9.9E+99,AT36),FLOOR(AK36/R36,1)))</f>
         <v/>
       </c>
       <c r="AM36" s="38">
@@ -8353,7 +8515,7 @@
         <v/>
       </c>
       <c r="AN36" s="36">
-        <f>IF(OR(AG36="",R36=0),"",MIN(IF(AS36="",9.9E+99,AS36),AK36/R36))</f>
+        <f>IF(OR(AG36="",R36=0),"",MIN(IF(AT36="",9.9E+99,AT36),AK36/R36))</f>
         <v/>
       </c>
       <c r="AO36" s="38">
@@ -8361,23 +8523,28 @@
         <v/>
       </c>
       <c r="AP36" s="40" t="n"/>
-      <c r="AQ36" s="41" t="n"/>
+      <c r="AQ36" s="32" t="inlineStr">
+        <is>
+          <t>Grounded</t>
+        </is>
+      </c>
       <c r="AR36" s="41" t="n"/>
-      <c r="AS36" s="42" t="n"/>
-      <c r="AT36" s="43">
+      <c r="AS36" s="41" t="n"/>
+      <c r="AT36" s="42" t="n"/>
+      <c r="AU36" s="43">
         <f>IF(((S36*pax_cap*load_thin*ROUND(K36*L36*revleg_thin,0))-(((battery/range_nm)*D36*ROUND(K36*L36*revleg_thin,0)*VLOOKUP(B36,country_opex,3,FALSE))+V36+W36+X36+Y36+Z36))&lt;=0,"",VLOOKUP(B36,country_opex,7,FALSE)/((S36*pax_cap*load_thin*ROUND(K36*L36*revleg_thin,0))-(((battery/range_nm)*D36*ROUND(K36*L36*revleg_thin,0)*VLOOKUP(B36,country_opex,3,FALSE))+V36+W36+X36+Y36+Z36)))</f>
         <v/>
       </c>
-      <c r="AU36" s="43">
+      <c r="AV36" s="43">
         <f>IF(((S36*pax_cap*load_mid*ROUND(K36*L36*revleg_mid,0))-(((battery/range_nm)*D36*ROUND(K36*L36*revleg_mid,0)*VLOOKUP(B36,country_opex,3,FALSE))+V36+W36+X36+Y36+Z36))&lt;=0,"",VLOOKUP(B36,country_opex,7,FALSE)/((S36*pax_cap*load_mid*ROUND(K36*L36*revleg_mid,0))-(((battery/range_nm)*D36*ROUND(K36*L36*revleg_mid,0)*VLOOKUP(B36,country_opex,3,FALSE))+V36+W36+X36+Y36+Z36)))</f>
         <v/>
       </c>
-      <c r="AV36" s="43">
+      <c r="AW36" s="43">
         <f>IF(((S36*pax_cap*load_full*ROUND(K36*L36*revleg_full,0))-(((battery/range_nm)*D36*ROUND(K36*L36*revleg_full,0)*VLOOKUP(B36,country_opex,3,FALSE))+V36+W36+X36+Y36+Z36))&lt;=0,"",VLOOKUP(B36,country_opex,7,FALSE)/((S36*pax_cap*load_full*ROUND(K36*L36*revleg_full,0))-(((battery/range_nm)*D36*ROUND(K36*L36*revleg_full,0)*VLOOKUP(B36,country_opex,3,FALSE))+V36+W36+X36+Y36+Z36)))</f>
         <v/>
       </c>
-      <c r="AW36" s="44" t="n"/>
       <c r="AX36" s="44" t="n"/>
+      <c r="AY36" s="44" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="29" t="inlineStr">
@@ -8392,11 +8559,11 @@
       </c>
       <c r="C37" s="30" t="inlineStr">
         <is>
-          <t>Ras Al Khaimah → ميناء صيادين غليلة</t>
+          <t>UAQ Marine Club → Hamriyah Port Main Harbour</t>
         </is>
       </c>
       <c r="D37" s="31" t="n">
-        <v>11.9</v>
+        <v>10.5</v>
       </c>
       <c r="E37" s="26" t="n">
         <v>35</v>
@@ -8531,7 +8698,7 @@
         <v/>
       </c>
       <c r="AL37" s="34">
-        <f>IF(OR(AG37="",R37=0),"",MIN(IF(AS37="",9.9E+99,AS37),FLOOR(AK37/R37,1)))</f>
+        <f>IF(OR(AG37="",R37=0),"",MIN(IF(AT37="",9.9E+99,AT37),FLOOR(AK37/R37,1)))</f>
         <v/>
       </c>
       <c r="AM37" s="38">
@@ -8539,7 +8706,7 @@
         <v/>
       </c>
       <c r="AN37" s="36">
-        <f>IF(OR(AG37="",R37=0),"",MIN(IF(AS37="",9.9E+99,AS37),AK37/R37))</f>
+        <f>IF(OR(AG37="",R37=0),"",MIN(IF(AT37="",9.9E+99,AT37),AK37/R37))</f>
         <v/>
       </c>
       <c r="AO37" s="38">
@@ -8547,23 +8714,28 @@
         <v/>
       </c>
       <c r="AP37" s="40" t="n"/>
-      <c r="AQ37" s="41" t="n"/>
+      <c r="AQ37" s="32" t="inlineStr">
+        <is>
+          <t>Grounded</t>
+        </is>
+      </c>
       <c r="AR37" s="41" t="n"/>
-      <c r="AS37" s="42" t="n"/>
-      <c r="AT37" s="43">
+      <c r="AS37" s="41" t="n"/>
+      <c r="AT37" s="42" t="n"/>
+      <c r="AU37" s="43">
         <f>IF(((S37*pax_cap*load_thin*ROUND(K37*L37*revleg_thin,0))-(((battery/range_nm)*D37*ROUND(K37*L37*revleg_thin,0)*VLOOKUP(B37,country_opex,3,FALSE))+V37+W37+X37+Y37+Z37))&lt;=0,"",VLOOKUP(B37,country_opex,7,FALSE)/((S37*pax_cap*load_thin*ROUND(K37*L37*revleg_thin,0))-(((battery/range_nm)*D37*ROUND(K37*L37*revleg_thin,0)*VLOOKUP(B37,country_opex,3,FALSE))+V37+W37+X37+Y37+Z37)))</f>
         <v/>
       </c>
-      <c r="AU37" s="43">
+      <c r="AV37" s="43">
         <f>IF(((S37*pax_cap*load_mid*ROUND(K37*L37*revleg_mid,0))-(((battery/range_nm)*D37*ROUND(K37*L37*revleg_mid,0)*VLOOKUP(B37,country_opex,3,FALSE))+V37+W37+X37+Y37+Z37))&lt;=0,"",VLOOKUP(B37,country_opex,7,FALSE)/((S37*pax_cap*load_mid*ROUND(K37*L37*revleg_mid,0))-(((battery/range_nm)*D37*ROUND(K37*L37*revleg_mid,0)*VLOOKUP(B37,country_opex,3,FALSE))+V37+W37+X37+Y37+Z37)))</f>
         <v/>
       </c>
-      <c r="AV37" s="43">
+      <c r="AW37" s="43">
         <f>IF(((S37*pax_cap*load_full*ROUND(K37*L37*revleg_full,0))-(((battery/range_nm)*D37*ROUND(K37*L37*revleg_full,0)*VLOOKUP(B37,country_opex,3,FALSE))+V37+W37+X37+Y37+Z37))&lt;=0,"",VLOOKUP(B37,country_opex,7,FALSE)/((S37*pax_cap*load_full*ROUND(K37*L37*revleg_full,0))-(((battery/range_nm)*D37*ROUND(K37*L37*revleg_full,0)*VLOOKUP(B37,country_opex,3,FALSE))+V37+W37+X37+Y37+Z37)))</f>
         <v/>
       </c>
-      <c r="AW37" s="44" t="n"/>
       <c r="AX37" s="44" t="n"/>
+      <c r="AY37" s="44" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="29" t="inlineStr">
@@ -8578,11 +8750,11 @@
       </c>
       <c r="C38" s="30" t="inlineStr">
         <is>
-          <t>Ras Al Khaimah → Al Hamra Marina &amp; Royal Yacht Club RAK</t>
+          <t>UAQ Marine Club → Rixos Bab Al Bahr beach jetty</t>
         </is>
       </c>
       <c r="D38" s="31" t="n">
-        <v>13.6</v>
+        <v>11.8</v>
       </c>
       <c r="E38" s="26" t="n">
         <v>35</v>
@@ -8717,7 +8889,7 @@
         <v/>
       </c>
       <c r="AL38" s="34">
-        <f>IF(OR(AG38="",R38=0),"",MIN(IF(AS38="",9.9E+99,AS38),FLOOR(AK38/R38,1)))</f>
+        <f>IF(OR(AG38="",R38=0),"",MIN(IF(AT38="",9.9E+99,AT38),FLOOR(AK38/R38,1)))</f>
         <v/>
       </c>
       <c r="AM38" s="38">
@@ -8725,7 +8897,7 @@
         <v/>
       </c>
       <c r="AN38" s="36">
-        <f>IF(OR(AG38="",R38=0),"",MIN(IF(AS38="",9.9E+99,AS38),AK38/R38))</f>
+        <f>IF(OR(AG38="",R38=0),"",MIN(IF(AT38="",9.9E+99,AT38),AK38/R38))</f>
         <v/>
       </c>
       <c r="AO38" s="38">
@@ -8733,23 +8905,28 @@
         <v/>
       </c>
       <c r="AP38" s="40" t="n"/>
-      <c r="AQ38" s="41" t="n"/>
+      <c r="AQ38" s="32" t="inlineStr">
+        <is>
+          <t>Grounded</t>
+        </is>
+      </c>
       <c r="AR38" s="41" t="n"/>
-      <c r="AS38" s="42" t="n"/>
-      <c r="AT38" s="43">
+      <c r="AS38" s="41" t="n"/>
+      <c r="AT38" s="42" t="n"/>
+      <c r="AU38" s="43">
         <f>IF(((S38*pax_cap*load_thin*ROUND(K38*L38*revleg_thin,0))-(((battery/range_nm)*D38*ROUND(K38*L38*revleg_thin,0)*VLOOKUP(B38,country_opex,3,FALSE))+V38+W38+X38+Y38+Z38))&lt;=0,"",VLOOKUP(B38,country_opex,7,FALSE)/((S38*pax_cap*load_thin*ROUND(K38*L38*revleg_thin,0))-(((battery/range_nm)*D38*ROUND(K38*L38*revleg_thin,0)*VLOOKUP(B38,country_opex,3,FALSE))+V38+W38+X38+Y38+Z38)))</f>
         <v/>
       </c>
-      <c r="AU38" s="43">
+      <c r="AV38" s="43">
         <f>IF(((S38*pax_cap*load_mid*ROUND(K38*L38*revleg_mid,0))-(((battery/range_nm)*D38*ROUND(K38*L38*revleg_mid,0)*VLOOKUP(B38,country_opex,3,FALSE))+V38+W38+X38+Y38+Z38))&lt;=0,"",VLOOKUP(B38,country_opex,7,FALSE)/((S38*pax_cap*load_mid*ROUND(K38*L38*revleg_mid,0))-(((battery/range_nm)*D38*ROUND(K38*L38*revleg_mid,0)*VLOOKUP(B38,country_opex,3,FALSE))+V38+W38+X38+Y38+Z38)))</f>
         <v/>
       </c>
-      <c r="AV38" s="43">
+      <c r="AW38" s="43">
         <f>IF(((S38*pax_cap*load_full*ROUND(K38*L38*revleg_full,0))-(((battery/range_nm)*D38*ROUND(K38*L38*revleg_full,0)*VLOOKUP(B38,country_opex,3,FALSE))+V38+W38+X38+Y38+Z38))&lt;=0,"",VLOOKUP(B38,country_opex,7,FALSE)/((S38*pax_cap*load_full*ROUND(K38*L38*revleg_full,0))-(((battery/range_nm)*D38*ROUND(K38*L38*revleg_full,0)*VLOOKUP(B38,country_opex,3,FALSE))+V38+W38+X38+Y38+Z38)))</f>
         <v/>
       </c>
-      <c r="AW38" s="44" t="n"/>
       <c r="AX38" s="44" t="n"/>
+      <c r="AY38" s="44" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="29" t="inlineStr">
@@ -8764,11 +8941,11 @@
       </c>
       <c r="C39" s="30" t="inlineStr">
         <is>
-          <t>Ras Al Khaimah → Al Marjan Island public arrival marina</t>
+          <t>Ras Al Khaimah → ميناء صيادين غليلة</t>
         </is>
       </c>
       <c r="D39" s="31" t="n">
-        <v>16</v>
+        <v>11.9</v>
       </c>
       <c r="E39" s="26" t="n">
         <v>35</v>
@@ -8903,7 +9080,7 @@
         <v/>
       </c>
       <c r="AL39" s="34">
-        <f>IF(OR(AG39="",R39=0),"",MIN(IF(AS39="",9.9E+99,AS39),FLOOR(AK39/R39,1)))</f>
+        <f>IF(OR(AG39="",R39=0),"",MIN(IF(AT39="",9.9E+99,AT39),FLOOR(AK39/R39,1)))</f>
         <v/>
       </c>
       <c r="AM39" s="38">
@@ -8911,7 +9088,7 @@
         <v/>
       </c>
       <c r="AN39" s="36">
-        <f>IF(OR(AG39="",R39=0),"",MIN(IF(AS39="",9.9E+99,AS39),AK39/R39))</f>
+        <f>IF(OR(AG39="",R39=0),"",MIN(IF(AT39="",9.9E+99,AT39),AK39/R39))</f>
         <v/>
       </c>
       <c r="AO39" s="38">
@@ -8919,23 +9096,28 @@
         <v/>
       </c>
       <c r="AP39" s="40" t="n"/>
-      <c r="AQ39" s="41" t="n"/>
+      <c r="AQ39" s="32" t="inlineStr">
+        <is>
+          <t>Grounded</t>
+        </is>
+      </c>
       <c r="AR39" s="41" t="n"/>
-      <c r="AS39" s="42" t="n"/>
-      <c r="AT39" s="43">
+      <c r="AS39" s="41" t="n"/>
+      <c r="AT39" s="42" t="n"/>
+      <c r="AU39" s="43">
         <f>IF(((S39*pax_cap*load_thin*ROUND(K39*L39*revleg_thin,0))-(((battery/range_nm)*D39*ROUND(K39*L39*revleg_thin,0)*VLOOKUP(B39,country_opex,3,FALSE))+V39+W39+X39+Y39+Z39))&lt;=0,"",VLOOKUP(B39,country_opex,7,FALSE)/((S39*pax_cap*load_thin*ROUND(K39*L39*revleg_thin,0))-(((battery/range_nm)*D39*ROUND(K39*L39*revleg_thin,0)*VLOOKUP(B39,country_opex,3,FALSE))+V39+W39+X39+Y39+Z39)))</f>
         <v/>
       </c>
-      <c r="AU39" s="43">
+      <c r="AV39" s="43">
         <f>IF(((S39*pax_cap*load_mid*ROUND(K39*L39*revleg_mid,0))-(((battery/range_nm)*D39*ROUND(K39*L39*revleg_mid,0)*VLOOKUP(B39,country_opex,3,FALSE))+V39+W39+X39+Y39+Z39))&lt;=0,"",VLOOKUP(B39,country_opex,7,FALSE)/((S39*pax_cap*load_mid*ROUND(K39*L39*revleg_mid,0))-(((battery/range_nm)*D39*ROUND(K39*L39*revleg_mid,0)*VLOOKUP(B39,country_opex,3,FALSE))+V39+W39+X39+Y39+Z39)))</f>
         <v/>
       </c>
-      <c r="AV39" s="43">
+      <c r="AW39" s="43">
         <f>IF(((S39*pax_cap*load_full*ROUND(K39*L39*revleg_full,0))-(((battery/range_nm)*D39*ROUND(K39*L39*revleg_full,0)*VLOOKUP(B39,country_opex,3,FALSE))+V39+W39+X39+Y39+Z39))&lt;=0,"",VLOOKUP(B39,country_opex,7,FALSE)/((S39*pax_cap*load_full*ROUND(K39*L39*revleg_full,0))-(((battery/range_nm)*D39*ROUND(K39*L39*revleg_full,0)*VLOOKUP(B39,country_opex,3,FALSE))+V39+W39+X39+Y39+Z39)))</f>
         <v/>
       </c>
-      <c r="AW39" s="44" t="n"/>
       <c r="AX39" s="44" t="n"/>
+      <c r="AY39" s="44" t="n"/>
     </row>
     <row r="40">
       <c r="A40" s="29" t="inlineStr">
@@ -8950,11 +9132,11 @@
       </c>
       <c r="C40" s="30" t="inlineStr">
         <is>
-          <t>Ras Al Khaimah → UAQ Marine Club</t>
+          <t>Ras Al Khaimah → Al Hamra Marina &amp; Royal Yacht Club RAK</t>
         </is>
       </c>
       <c r="D40" s="31" t="n">
-        <v>26.6</v>
+        <v>13.6</v>
       </c>
       <c r="E40" s="26" t="n">
         <v>35</v>
@@ -9089,7 +9271,7 @@
         <v/>
       </c>
       <c r="AL40" s="34">
-        <f>IF(OR(AG40="",R40=0),"",MIN(IF(AS40="",9.9E+99,AS40),FLOOR(AK40/R40,1)))</f>
+        <f>IF(OR(AG40="",R40=0),"",MIN(IF(AT40="",9.9E+99,AT40),FLOOR(AK40/R40,1)))</f>
         <v/>
       </c>
       <c r="AM40" s="38">
@@ -9097,7 +9279,7 @@
         <v/>
       </c>
       <c r="AN40" s="36">
-        <f>IF(OR(AG40="",R40=0),"",MIN(IF(AS40="",9.9E+99,AS40),AK40/R40))</f>
+        <f>IF(OR(AG40="",R40=0),"",MIN(IF(AT40="",9.9E+99,AT40),AK40/R40))</f>
         <v/>
       </c>
       <c r="AO40" s="38">
@@ -9105,23 +9287,28 @@
         <v/>
       </c>
       <c r="AP40" s="40" t="n"/>
-      <c r="AQ40" s="41" t="n"/>
+      <c r="AQ40" s="32" t="inlineStr">
+        <is>
+          <t>Grounded</t>
+        </is>
+      </c>
       <c r="AR40" s="41" t="n"/>
-      <c r="AS40" s="42" t="n"/>
-      <c r="AT40" s="43">
+      <c r="AS40" s="41" t="n"/>
+      <c r="AT40" s="42" t="n"/>
+      <c r="AU40" s="43">
         <f>IF(((S40*pax_cap*load_thin*ROUND(K40*L40*revleg_thin,0))-(((battery/range_nm)*D40*ROUND(K40*L40*revleg_thin,0)*VLOOKUP(B40,country_opex,3,FALSE))+V40+W40+X40+Y40+Z40))&lt;=0,"",VLOOKUP(B40,country_opex,7,FALSE)/((S40*pax_cap*load_thin*ROUND(K40*L40*revleg_thin,0))-(((battery/range_nm)*D40*ROUND(K40*L40*revleg_thin,0)*VLOOKUP(B40,country_opex,3,FALSE))+V40+W40+X40+Y40+Z40)))</f>
         <v/>
       </c>
-      <c r="AU40" s="43">
+      <c r="AV40" s="43">
         <f>IF(((S40*pax_cap*load_mid*ROUND(K40*L40*revleg_mid,0))-(((battery/range_nm)*D40*ROUND(K40*L40*revleg_mid,0)*VLOOKUP(B40,country_opex,3,FALSE))+V40+W40+X40+Y40+Z40))&lt;=0,"",VLOOKUP(B40,country_opex,7,FALSE)/((S40*pax_cap*load_mid*ROUND(K40*L40*revleg_mid,0))-(((battery/range_nm)*D40*ROUND(K40*L40*revleg_mid,0)*VLOOKUP(B40,country_opex,3,FALSE))+V40+W40+X40+Y40+Z40)))</f>
         <v/>
       </c>
-      <c r="AV40" s="43">
+      <c r="AW40" s="43">
         <f>IF(((S40*pax_cap*load_full*ROUND(K40*L40*revleg_full,0))-(((battery/range_nm)*D40*ROUND(K40*L40*revleg_full,0)*VLOOKUP(B40,country_opex,3,FALSE))+V40+W40+X40+Y40+Z40))&lt;=0,"",VLOOKUP(B40,country_opex,7,FALSE)/((S40*pax_cap*load_full*ROUND(K40*L40*revleg_full,0))-(((battery/range_nm)*D40*ROUND(K40*L40*revleg_full,0)*VLOOKUP(B40,country_opex,3,FALSE))+V40+W40+X40+Y40+Z40)))</f>
         <v/>
       </c>
-      <c r="AW40" s="44" t="n"/>
       <c r="AX40" s="44" t="n"/>
+      <c r="AY40" s="44" t="n"/>
     </row>
     <row r="41">
       <c r="A41" s="29" t="inlineStr">
@@ -9136,11 +9323,11 @@
       </c>
       <c r="C41" s="30" t="inlineStr">
         <is>
-          <t>Ras Al Khaimah → Ajman Marina</t>
+          <t>Ras Al Khaimah → Al Marjan Island public arrival marina</t>
         </is>
       </c>
       <c r="D41" s="31" t="n">
-        <v>39</v>
+        <v>16</v>
       </c>
       <c r="E41" s="26" t="n">
         <v>35</v>
@@ -9275,7 +9462,7 @@
         <v/>
       </c>
       <c r="AL41" s="34">
-        <f>IF(OR(AG41="",R41=0),"",MIN(IF(AS41="",9.9E+99,AS41),FLOOR(AK41/R41,1)))</f>
+        <f>IF(OR(AG41="",R41=0),"",MIN(IF(AT41="",9.9E+99,AT41),FLOOR(AK41/R41,1)))</f>
         <v/>
       </c>
       <c r="AM41" s="38">
@@ -9283,7 +9470,7 @@
         <v/>
       </c>
       <c r="AN41" s="36">
-        <f>IF(OR(AG41="",R41=0),"",MIN(IF(AS41="",9.9E+99,AS41),AK41/R41))</f>
+        <f>IF(OR(AG41="",R41=0),"",MIN(IF(AT41="",9.9E+99,AT41),AK41/R41))</f>
         <v/>
       </c>
       <c r="AO41" s="38">
@@ -9291,23 +9478,28 @@
         <v/>
       </c>
       <c r="AP41" s="40" t="n"/>
-      <c r="AQ41" s="41" t="n"/>
+      <c r="AQ41" s="32" t="inlineStr">
+        <is>
+          <t>Grounded</t>
+        </is>
+      </c>
       <c r="AR41" s="41" t="n"/>
-      <c r="AS41" s="42" t="n"/>
-      <c r="AT41" s="43">
+      <c r="AS41" s="41" t="n"/>
+      <c r="AT41" s="42" t="n"/>
+      <c r="AU41" s="43">
         <f>IF(((S41*pax_cap*load_thin*ROUND(K41*L41*revleg_thin,0))-(((battery/range_nm)*D41*ROUND(K41*L41*revleg_thin,0)*VLOOKUP(B41,country_opex,3,FALSE))+V41+W41+X41+Y41+Z41))&lt;=0,"",VLOOKUP(B41,country_opex,7,FALSE)/((S41*pax_cap*load_thin*ROUND(K41*L41*revleg_thin,0))-(((battery/range_nm)*D41*ROUND(K41*L41*revleg_thin,0)*VLOOKUP(B41,country_opex,3,FALSE))+V41+W41+X41+Y41+Z41)))</f>
         <v/>
       </c>
-      <c r="AU41" s="43">
+      <c r="AV41" s="43">
         <f>IF(((S41*pax_cap*load_mid*ROUND(K41*L41*revleg_mid,0))-(((battery/range_nm)*D41*ROUND(K41*L41*revleg_mid,0)*VLOOKUP(B41,country_opex,3,FALSE))+V41+W41+X41+Y41+Z41))&lt;=0,"",VLOOKUP(B41,country_opex,7,FALSE)/((S41*pax_cap*load_mid*ROUND(K41*L41*revleg_mid,0))-(((battery/range_nm)*D41*ROUND(K41*L41*revleg_mid,0)*VLOOKUP(B41,country_opex,3,FALSE))+V41+W41+X41+Y41+Z41)))</f>
         <v/>
       </c>
-      <c r="AV41" s="43">
+      <c r="AW41" s="43">
         <f>IF(((S41*pax_cap*load_full*ROUND(K41*L41*revleg_full,0))-(((battery/range_nm)*D41*ROUND(K41*L41*revleg_full,0)*VLOOKUP(B41,country_opex,3,FALSE))+V41+W41+X41+Y41+Z41))&lt;=0,"",VLOOKUP(B41,country_opex,7,FALSE)/((S41*pax_cap*load_full*ROUND(K41*L41*revleg_full,0))-(((battery/range_nm)*D41*ROUND(K41*L41*revleg_full,0)*VLOOKUP(B41,country_opex,3,FALSE))+V41+W41+X41+Y41+Z41)))</f>
         <v/>
       </c>
-      <c r="AW41" s="44" t="n"/>
       <c r="AX41" s="44" t="n"/>
+      <c r="AY41" s="44" t="n"/>
     </row>
     <row r="42">
       <c r="A42" s="29" t="inlineStr">
@@ -9322,11 +9514,11 @@
       </c>
       <c r="C42" s="30" t="inlineStr">
         <is>
-          <t>Ras Al Khaimah → Sharjah</t>
+          <t>Ras Al Khaimah → UAQ Marine Club</t>
         </is>
       </c>
       <c r="D42" s="31" t="n">
-        <v>42</v>
+        <v>26.6</v>
       </c>
       <c r="E42" s="26" t="n">
         <v>35</v>
@@ -9461,7 +9653,7 @@
         <v/>
       </c>
       <c r="AL42" s="34">
-        <f>IF(OR(AG42="",R42=0),"",MIN(IF(AS42="",9.9E+99,AS42),FLOOR(AK42/R42,1)))</f>
+        <f>IF(OR(AG42="",R42=0),"",MIN(IF(AT42="",9.9E+99,AT42),FLOOR(AK42/R42,1)))</f>
         <v/>
       </c>
       <c r="AM42" s="38">
@@ -9469,7 +9661,7 @@
         <v/>
       </c>
       <c r="AN42" s="36">
-        <f>IF(OR(AG42="",R42=0),"",MIN(IF(AS42="",9.9E+99,AS42),AK42/R42))</f>
+        <f>IF(OR(AG42="",R42=0),"",MIN(IF(AT42="",9.9E+99,AT42),AK42/R42))</f>
         <v/>
       </c>
       <c r="AO42" s="38">
@@ -9477,23 +9669,28 @@
         <v/>
       </c>
       <c r="AP42" s="40" t="n"/>
-      <c r="AQ42" s="41" t="n"/>
+      <c r="AQ42" s="32" t="inlineStr">
+        <is>
+          <t>Grounded</t>
+        </is>
+      </c>
       <c r="AR42" s="41" t="n"/>
-      <c r="AS42" s="42" t="n"/>
-      <c r="AT42" s="43">
+      <c r="AS42" s="41" t="n"/>
+      <c r="AT42" s="42" t="n"/>
+      <c r="AU42" s="43">
         <f>IF(((S42*pax_cap*load_thin*ROUND(K42*L42*revleg_thin,0))-(((battery/range_nm)*D42*ROUND(K42*L42*revleg_thin,0)*VLOOKUP(B42,country_opex,3,FALSE))+V42+W42+X42+Y42+Z42))&lt;=0,"",VLOOKUP(B42,country_opex,7,FALSE)/((S42*pax_cap*load_thin*ROUND(K42*L42*revleg_thin,0))-(((battery/range_nm)*D42*ROUND(K42*L42*revleg_thin,0)*VLOOKUP(B42,country_opex,3,FALSE))+V42+W42+X42+Y42+Z42)))</f>
         <v/>
       </c>
-      <c r="AU42" s="43">
+      <c r="AV42" s="43">
         <f>IF(((S42*pax_cap*load_mid*ROUND(K42*L42*revleg_mid,0))-(((battery/range_nm)*D42*ROUND(K42*L42*revleg_mid,0)*VLOOKUP(B42,country_opex,3,FALSE))+V42+W42+X42+Y42+Z42))&lt;=0,"",VLOOKUP(B42,country_opex,7,FALSE)/((S42*pax_cap*load_mid*ROUND(K42*L42*revleg_mid,0))-(((battery/range_nm)*D42*ROUND(K42*L42*revleg_mid,0)*VLOOKUP(B42,country_opex,3,FALSE))+V42+W42+X42+Y42+Z42)))</f>
         <v/>
       </c>
-      <c r="AV42" s="43">
+      <c r="AW42" s="43">
         <f>IF(((S42*pax_cap*load_full*ROUND(K42*L42*revleg_full,0))-(((battery/range_nm)*D42*ROUND(K42*L42*revleg_full,0)*VLOOKUP(B42,country_opex,3,FALSE))+V42+W42+X42+Y42+Z42))&lt;=0,"",VLOOKUP(B42,country_opex,7,FALSE)/((S42*pax_cap*load_full*ROUND(K42*L42*revleg_full,0))-(((battery/range_nm)*D42*ROUND(K42*L42*revleg_full,0)*VLOOKUP(B42,country_opex,3,FALSE))+V42+W42+X42+Y42+Z42)))</f>
         <v/>
       </c>
-      <c r="AW42" s="44" t="n"/>
       <c r="AX42" s="44" t="n"/>
+      <c r="AY42" s="44" t="n"/>
     </row>
     <row r="43">
       <c r="A43" s="29" t="inlineStr">
@@ -9508,11 +9705,11 @@
       </c>
       <c r="C43" s="30" t="inlineStr">
         <is>
-          <t>Dubai Harbour Marina → Wynn Al Marjan Island arrival lagoon</t>
+          <t>Ras Al Khaimah → Ajman Marina</t>
         </is>
       </c>
       <c r="D43" s="31" t="n">
-        <v>49.8</v>
+        <v>39</v>
       </c>
       <c r="E43" s="26" t="n">
         <v>35</v>
@@ -9647,7 +9844,7 @@
         <v/>
       </c>
       <c r="AL43" s="34">
-        <f>IF(OR(AG43="",R43=0),"",MIN(IF(AS43="",9.9E+99,AS43),FLOOR(AK43/R43,1)))</f>
+        <f>IF(OR(AG43="",R43=0),"",MIN(IF(AT43="",9.9E+99,AT43),FLOOR(AK43/R43,1)))</f>
         <v/>
       </c>
       <c r="AM43" s="38">
@@ -9655,7 +9852,7 @@
         <v/>
       </c>
       <c r="AN43" s="36">
-        <f>IF(OR(AG43="",R43=0),"",MIN(IF(AS43="",9.9E+99,AS43),AK43/R43))</f>
+        <f>IF(OR(AG43="",R43=0),"",MIN(IF(AT43="",9.9E+99,AT43),AK43/R43))</f>
         <v/>
       </c>
       <c r="AO43" s="38">
@@ -9663,23 +9860,28 @@
         <v/>
       </c>
       <c r="AP43" s="40" t="n"/>
-      <c r="AQ43" s="41" t="n"/>
+      <c r="AQ43" s="32" t="inlineStr">
+        <is>
+          <t>Grounded</t>
+        </is>
+      </c>
       <c r="AR43" s="41" t="n"/>
-      <c r="AS43" s="42" t="n"/>
-      <c r="AT43" s="43">
+      <c r="AS43" s="41" t="n"/>
+      <c r="AT43" s="42" t="n"/>
+      <c r="AU43" s="43">
         <f>IF(((S43*pax_cap*load_thin*ROUND(K43*L43*revleg_thin,0))-(((battery/range_nm)*D43*ROUND(K43*L43*revleg_thin,0)*VLOOKUP(B43,country_opex,3,FALSE))+V43+W43+X43+Y43+Z43))&lt;=0,"",VLOOKUP(B43,country_opex,7,FALSE)/((S43*pax_cap*load_thin*ROUND(K43*L43*revleg_thin,0))-(((battery/range_nm)*D43*ROUND(K43*L43*revleg_thin,0)*VLOOKUP(B43,country_opex,3,FALSE))+V43+W43+X43+Y43+Z43)))</f>
         <v/>
       </c>
-      <c r="AU43" s="43">
+      <c r="AV43" s="43">
         <f>IF(((S43*pax_cap*load_mid*ROUND(K43*L43*revleg_mid,0))-(((battery/range_nm)*D43*ROUND(K43*L43*revleg_mid,0)*VLOOKUP(B43,country_opex,3,FALSE))+V43+W43+X43+Y43+Z43))&lt;=0,"",VLOOKUP(B43,country_opex,7,FALSE)/((S43*pax_cap*load_mid*ROUND(K43*L43*revleg_mid,0))-(((battery/range_nm)*D43*ROUND(K43*L43*revleg_mid,0)*VLOOKUP(B43,country_opex,3,FALSE))+V43+W43+X43+Y43+Z43)))</f>
         <v/>
       </c>
-      <c r="AV43" s="43">
+      <c r="AW43" s="43">
         <f>IF(((S43*pax_cap*load_full*ROUND(K43*L43*revleg_full,0))-(((battery/range_nm)*D43*ROUND(K43*L43*revleg_full,0)*VLOOKUP(B43,country_opex,3,FALSE))+V43+W43+X43+Y43+Z43))&lt;=0,"",VLOOKUP(B43,country_opex,7,FALSE)/((S43*pax_cap*load_full*ROUND(K43*L43*revleg_full,0))-(((battery/range_nm)*D43*ROUND(K43*L43*revleg_full,0)*VLOOKUP(B43,country_opex,3,FALSE))+V43+W43+X43+Y43+Z43)))</f>
         <v/>
       </c>
-      <c r="AW43" s="44" t="n"/>
       <c r="AX43" s="44" t="n"/>
+      <c r="AY43" s="44" t="n"/>
     </row>
     <row r="44">
       <c r="A44" s="29" t="inlineStr">
@@ -9694,11 +9896,11 @@
       </c>
       <c r="C44" s="30" t="inlineStr">
         <is>
-          <t>Ras Al Khaimah → Dubai Islands Marina</t>
+          <t>Ras Al Khaimah → Sharjah</t>
         </is>
       </c>
       <c r="D44" s="31" t="n">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="E44" s="26" t="n">
         <v>35</v>
@@ -9833,7 +10035,7 @@
         <v/>
       </c>
       <c r="AL44" s="34">
-        <f>IF(OR(AG44="",R44=0),"",MIN(IF(AS44="",9.9E+99,AS44),FLOOR(AK44/R44,1)))</f>
+        <f>IF(OR(AG44="",R44=0),"",MIN(IF(AT44="",9.9E+99,AT44),FLOOR(AK44/R44,1)))</f>
         <v/>
       </c>
       <c r="AM44" s="38">
@@ -9841,7 +10043,7 @@
         <v/>
       </c>
       <c r="AN44" s="36">
-        <f>IF(OR(AG44="",R44=0),"",MIN(IF(AS44="",9.9E+99,AS44),AK44/R44))</f>
+        <f>IF(OR(AG44="",R44=0),"",MIN(IF(AT44="",9.9E+99,AT44),AK44/R44))</f>
         <v/>
       </c>
       <c r="AO44" s="38">
@@ -9849,23 +10051,28 @@
         <v/>
       </c>
       <c r="AP44" s="40" t="n"/>
-      <c r="AQ44" s="41" t="n"/>
+      <c r="AQ44" s="32" t="inlineStr">
+        <is>
+          <t>Grounded</t>
+        </is>
+      </c>
       <c r="AR44" s="41" t="n"/>
-      <c r="AS44" s="42" t="n"/>
-      <c r="AT44" s="43">
+      <c r="AS44" s="41" t="n"/>
+      <c r="AT44" s="42" t="n"/>
+      <c r="AU44" s="43">
         <f>IF(((S44*pax_cap*load_thin*ROUND(K44*L44*revleg_thin,0))-(((battery/range_nm)*D44*ROUND(K44*L44*revleg_thin,0)*VLOOKUP(B44,country_opex,3,FALSE))+V44+W44+X44+Y44+Z44))&lt;=0,"",VLOOKUP(B44,country_opex,7,FALSE)/((S44*pax_cap*load_thin*ROUND(K44*L44*revleg_thin,0))-(((battery/range_nm)*D44*ROUND(K44*L44*revleg_thin,0)*VLOOKUP(B44,country_opex,3,FALSE))+V44+W44+X44+Y44+Z44)))</f>
         <v/>
       </c>
-      <c r="AU44" s="43">
+      <c r="AV44" s="43">
         <f>IF(((S44*pax_cap*load_mid*ROUND(K44*L44*revleg_mid,0))-(((battery/range_nm)*D44*ROUND(K44*L44*revleg_mid,0)*VLOOKUP(B44,country_opex,3,FALSE))+V44+W44+X44+Y44+Z44))&lt;=0,"",VLOOKUP(B44,country_opex,7,FALSE)/((S44*pax_cap*load_mid*ROUND(K44*L44*revleg_mid,0))-(((battery/range_nm)*D44*ROUND(K44*L44*revleg_mid,0)*VLOOKUP(B44,country_opex,3,FALSE))+V44+W44+X44+Y44+Z44)))</f>
         <v/>
       </c>
-      <c r="AV44" s="43">
+      <c r="AW44" s="43">
         <f>IF(((S44*pax_cap*load_full*ROUND(K44*L44*revleg_full,0))-(((battery/range_nm)*D44*ROUND(K44*L44*revleg_full,0)*VLOOKUP(B44,country_opex,3,FALSE))+V44+W44+X44+Y44+Z44))&lt;=0,"",VLOOKUP(B44,country_opex,7,FALSE)/((S44*pax_cap*load_full*ROUND(K44*L44*revleg_full,0))-(((battery/range_nm)*D44*ROUND(K44*L44*revleg_full,0)*VLOOKUP(B44,country_opex,3,FALSE))+V44+W44+X44+Y44+Z44)))</f>
         <v/>
       </c>
-      <c r="AW44" s="44" t="n"/>
       <c r="AX44" s="44" t="n"/>
+      <c r="AY44" s="44" t="n"/>
     </row>
     <row r="45">
       <c r="A45" s="29" t="inlineStr">
@@ -9880,11 +10087,11 @@
       </c>
       <c r="C45" s="30" t="inlineStr">
         <is>
-          <t>Ras Al Khaimah → Fujairah</t>
+          <t>Dubai Harbour Marina → Wynn Al Marjan Island arrival lagoon</t>
         </is>
       </c>
       <c r="D45" s="31" t="n">
-        <v>54.7</v>
+        <v>49.8</v>
       </c>
       <c r="E45" s="26" t="n">
         <v>35</v>
@@ -10019,7 +10226,7 @@
         <v/>
       </c>
       <c r="AL45" s="34">
-        <f>IF(OR(AG45="",R45=0),"",MIN(IF(AS45="",9.9E+99,AS45),FLOOR(AK45/R45,1)))</f>
+        <f>IF(OR(AG45="",R45=0),"",MIN(IF(AT45="",9.9E+99,AT45),FLOOR(AK45/R45,1)))</f>
         <v/>
       </c>
       <c r="AM45" s="38">
@@ -10027,7 +10234,7 @@
         <v/>
       </c>
       <c r="AN45" s="36">
-        <f>IF(OR(AG45="",R45=0),"",MIN(IF(AS45="",9.9E+99,AS45),AK45/R45))</f>
+        <f>IF(OR(AG45="",R45=0),"",MIN(IF(AT45="",9.9E+99,AT45),AK45/R45))</f>
         <v/>
       </c>
       <c r="AO45" s="38">
@@ -10035,161 +10242,584 @@
         <v/>
       </c>
       <c r="AP45" s="40" t="n"/>
-      <c r="AQ45" s="41" t="n"/>
+      <c r="AQ45" s="32" t="inlineStr">
+        <is>
+          <t>Grounded</t>
+        </is>
+      </c>
       <c r="AR45" s="41" t="n"/>
-      <c r="AS45" s="42" t="n"/>
-      <c r="AT45" s="43">
+      <c r="AS45" s="41" t="n"/>
+      <c r="AT45" s="42" t="n"/>
+      <c r="AU45" s="43">
         <f>IF(((S45*pax_cap*load_thin*ROUND(K45*L45*revleg_thin,0))-(((battery/range_nm)*D45*ROUND(K45*L45*revleg_thin,0)*VLOOKUP(B45,country_opex,3,FALSE))+V45+W45+X45+Y45+Z45))&lt;=0,"",VLOOKUP(B45,country_opex,7,FALSE)/((S45*pax_cap*load_thin*ROUND(K45*L45*revleg_thin,0))-(((battery/range_nm)*D45*ROUND(K45*L45*revleg_thin,0)*VLOOKUP(B45,country_opex,3,FALSE))+V45+W45+X45+Y45+Z45)))</f>
         <v/>
       </c>
-      <c r="AU45" s="43">
+      <c r="AV45" s="43">
         <f>IF(((S45*pax_cap*load_mid*ROUND(K45*L45*revleg_mid,0))-(((battery/range_nm)*D45*ROUND(K45*L45*revleg_mid,0)*VLOOKUP(B45,country_opex,3,FALSE))+V45+W45+X45+Y45+Z45))&lt;=0,"",VLOOKUP(B45,country_opex,7,FALSE)/((S45*pax_cap*load_mid*ROUND(K45*L45*revleg_mid,0))-(((battery/range_nm)*D45*ROUND(K45*L45*revleg_mid,0)*VLOOKUP(B45,country_opex,3,FALSE))+V45+W45+X45+Y45+Z45)))</f>
         <v/>
       </c>
-      <c r="AV45" s="43">
+      <c r="AW45" s="43">
         <f>IF(((S45*pax_cap*load_full*ROUND(K45*L45*revleg_full,0))-(((battery/range_nm)*D45*ROUND(K45*L45*revleg_full,0)*VLOOKUP(B45,country_opex,3,FALSE))+V45+W45+X45+Y45+Z45))&lt;=0,"",VLOOKUP(B45,country_opex,7,FALSE)/((S45*pax_cap*load_full*ROUND(K45*L45*revleg_full,0))-(((battery/range_nm)*D45*ROUND(K45*L45*revleg_full,0)*VLOOKUP(B45,country_opex,3,FALSE))+V45+W45+X45+Y45+Z45)))</f>
         <v/>
       </c>
-      <c r="AW45" s="44" t="n"/>
       <c r="AX45" s="44" t="n"/>
+      <c r="AY45" s="44" t="n"/>
     </row>
     <row r="46">
-      <c r="A46" s="45" t="inlineStr">
+      <c r="A46" s="29" t="inlineStr">
+        <is>
+          <t>Gulf Authority Rakta</t>
+        </is>
+      </c>
+      <c r="B46" s="29" t="inlineStr">
+        <is>
+          <t>United Arab Emirates</t>
+        </is>
+      </c>
+      <c r="C46" s="30" t="inlineStr">
+        <is>
+          <t>Ras Al Khaimah → Dubai Islands Marina</t>
+        </is>
+      </c>
+      <c r="D46" s="31" t="n">
+        <v>50</v>
+      </c>
+      <c r="E46" s="26" t="n">
+        <v>35</v>
+      </c>
+      <c r="F46" s="32" t="inlineStr">
+        <is>
+          <t>T3</t>
+        </is>
+      </c>
+      <c r="G46" s="32" t="inlineStr">
+        <is>
+          <t>med-low</t>
+        </is>
+      </c>
+      <c r="H46" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="I46" s="33">
+        <f>60*D46/cruise_kt</f>
+        <v/>
+      </c>
+      <c r="J46" s="33">
+        <f>I46+turn_min+dwell_min</f>
+        <v/>
+      </c>
+      <c r="K46" s="34">
+        <f>MIN(15,FLOOR(60*service_hr/J46,1))</f>
+        <v/>
+      </c>
+      <c r="L46" s="34">
+        <f>ROUND(365*mech_uptime*H46,0)</f>
+        <v/>
+      </c>
+      <c r="M46" s="35">
+        <f>mech_uptime</f>
+        <v/>
+      </c>
+      <c r="N46" s="35">
+        <f>revleg_sel</f>
+        <v/>
+      </c>
+      <c r="O46" s="34">
+        <f>ROUND(K46*L46*revleg_sel,0)</f>
+        <v/>
+      </c>
+      <c r="P46" s="36">
+        <f>load_sel</f>
+        <v/>
+      </c>
+      <c r="Q46" s="36">
+        <f>pax_cap*P46</f>
+        <v/>
+      </c>
+      <c r="R46" s="34">
+        <f>Q46*O46</f>
+        <v/>
+      </c>
+      <c r="S46" s="37">
+        <f>E46*discount</f>
+        <v/>
+      </c>
+      <c r="T46" s="38">
+        <f>S46*R46</f>
+        <v/>
+      </c>
+      <c r="U46" s="38">
+        <f>(battery/range_nm)*D46*O46*VLOOKUP(B46,country_opex,3,FALSE)</f>
+        <v/>
+      </c>
+      <c r="V46" s="38">
+        <f>VLOOKUP(B46,country_opex,2,FALSE)*crew_factor</f>
+        <v/>
+      </c>
+      <c r="W46" s="38">
+        <f>VLOOKUP(B46,country_opex,5,FALSE)</f>
+        <v/>
+      </c>
+      <c r="X46" s="38">
+        <f>maint</f>
+        <v/>
+      </c>
+      <c r="Y46" s="38">
+        <f>VLOOKUP(B46,country_opex,7,FALSE)*ins_pct</f>
+        <v/>
+      </c>
+      <c r="Z46" s="38">
+        <f>charge_berth</f>
+        <v/>
+      </c>
+      <c r="AA46" s="38">
+        <f>U46+V46+W46+X46+Y46+Z46</f>
+        <v/>
+      </c>
+      <c r="AB46" s="38">
+        <f>VLOOKUP(B46,country_opex,7,FALSE)/dep_years</f>
+        <v/>
+      </c>
+      <c r="AC46" s="38">
+        <f>T46-AA46</f>
+        <v/>
+      </c>
+      <c r="AD46" s="35">
+        <f>IF(T46=0,"",AC46/T46)</f>
+        <v/>
+      </c>
+      <c r="AE46" s="36">
+        <f>IF(AC46&lt;=0,"",VLOOKUP(B46,country_opex,7,FALSE)/AC46)</f>
+        <v/>
+      </c>
+      <c r="AF46" s="33">
+        <f>((D46*O46/diesel_nmpg)*diesel_co2pg-(battery/range_nm)*D46*O46*VLOOKUP(B46,country_opex,4,FALSE))/1000</f>
+        <v/>
+      </c>
+      <c r="AG46" s="31" t="n">
+        <v>5217</v>
+      </c>
+      <c r="AH46" s="32" t="inlineStr">
+        <is>
+          <t>T3</t>
+        </is>
+      </c>
+      <c r="AI46" s="32" t="inlineStr">
+        <is>
+          <t>med-low</t>
+        </is>
+      </c>
+      <c r="AJ46" s="39" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AK46" s="34">
+        <f>IF(AG46="","",AG46*AJ46)</f>
+        <v/>
+      </c>
+      <c r="AL46" s="34">
+        <f>IF(OR(AG46="",R46=0),"",MIN(IF(AT46="",9.9E+99,AT46),FLOOR(AK46/R46,1)))</f>
+        <v/>
+      </c>
+      <c r="AM46" s="38">
+        <f>IF(AL46="","",AL46*T46)</f>
+        <v/>
+      </c>
+      <c r="AN46" s="36">
+        <f>IF(OR(AG46="",R46=0),"",MIN(IF(AT46="",9.9E+99,AT46),AK46/R46))</f>
+        <v/>
+      </c>
+      <c r="AO46" s="38">
+        <f>IF(AN46="","",AN46*T46)</f>
+        <v/>
+      </c>
+      <c r="AP46" s="40" t="n"/>
+      <c r="AQ46" s="32" t="inlineStr">
+        <is>
+          <t>Grounded</t>
+        </is>
+      </c>
+      <c r="AR46" s="41" t="n"/>
+      <c r="AS46" s="41" t="n"/>
+      <c r="AT46" s="42" t="n"/>
+      <c r="AU46" s="43">
+        <f>IF(((S46*pax_cap*load_thin*ROUND(K46*L46*revleg_thin,0))-(((battery/range_nm)*D46*ROUND(K46*L46*revleg_thin,0)*VLOOKUP(B46,country_opex,3,FALSE))+V46+W46+X46+Y46+Z46))&lt;=0,"",VLOOKUP(B46,country_opex,7,FALSE)/((S46*pax_cap*load_thin*ROUND(K46*L46*revleg_thin,0))-(((battery/range_nm)*D46*ROUND(K46*L46*revleg_thin,0)*VLOOKUP(B46,country_opex,3,FALSE))+V46+W46+X46+Y46+Z46)))</f>
+        <v/>
+      </c>
+      <c r="AV46" s="43">
+        <f>IF(((S46*pax_cap*load_mid*ROUND(K46*L46*revleg_mid,0))-(((battery/range_nm)*D46*ROUND(K46*L46*revleg_mid,0)*VLOOKUP(B46,country_opex,3,FALSE))+V46+W46+X46+Y46+Z46))&lt;=0,"",VLOOKUP(B46,country_opex,7,FALSE)/((S46*pax_cap*load_mid*ROUND(K46*L46*revleg_mid,0))-(((battery/range_nm)*D46*ROUND(K46*L46*revleg_mid,0)*VLOOKUP(B46,country_opex,3,FALSE))+V46+W46+X46+Y46+Z46)))</f>
+        <v/>
+      </c>
+      <c r="AW46" s="43">
+        <f>IF(((S46*pax_cap*load_full*ROUND(K46*L46*revleg_full,0))-(((battery/range_nm)*D46*ROUND(K46*L46*revleg_full,0)*VLOOKUP(B46,country_opex,3,FALSE))+V46+W46+X46+Y46+Z46))&lt;=0,"",VLOOKUP(B46,country_opex,7,FALSE)/((S46*pax_cap*load_full*ROUND(K46*L46*revleg_full,0))-(((battery/range_nm)*D46*ROUND(K46*L46*revleg_full,0)*VLOOKUP(B46,country_opex,3,FALSE))+V46+W46+X46+Y46+Z46)))</f>
+        <v/>
+      </c>
+      <c r="AX46" s="44" t="n"/>
+      <c r="AY46" s="44" t="n"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="29" t="inlineStr">
+        <is>
+          <t>Gulf Authority Rakta</t>
+        </is>
+      </c>
+      <c r="B47" s="29" t="inlineStr">
+        <is>
+          <t>United Arab Emirates</t>
+        </is>
+      </c>
+      <c r="C47" s="30" t="inlineStr">
+        <is>
+          <t>Ras Al Khaimah → Fujairah</t>
+        </is>
+      </c>
+      <c r="D47" s="31" t="n">
+        <v>54.7</v>
+      </c>
+      <c r="E47" s="26" t="n">
+        <v>35</v>
+      </c>
+      <c r="F47" s="32" t="inlineStr">
+        <is>
+          <t>T3</t>
+        </is>
+      </c>
+      <c r="G47" s="32" t="inlineStr">
+        <is>
+          <t>med-low</t>
+        </is>
+      </c>
+      <c r="H47" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="I47" s="33">
+        <f>60*D47/cruise_kt</f>
+        <v/>
+      </c>
+      <c r="J47" s="33">
+        <f>I47+turn_min+dwell_min</f>
+        <v/>
+      </c>
+      <c r="K47" s="34">
+        <f>MIN(15,FLOOR(60*service_hr/J47,1))</f>
+        <v/>
+      </c>
+      <c r="L47" s="34">
+        <f>ROUND(365*mech_uptime*H47,0)</f>
+        <v/>
+      </c>
+      <c r="M47" s="35">
+        <f>mech_uptime</f>
+        <v/>
+      </c>
+      <c r="N47" s="35">
+        <f>revleg_sel</f>
+        <v/>
+      </c>
+      <c r="O47" s="34">
+        <f>ROUND(K47*L47*revleg_sel,0)</f>
+        <v/>
+      </c>
+      <c r="P47" s="36">
+        <f>load_sel</f>
+        <v/>
+      </c>
+      <c r="Q47" s="36">
+        <f>pax_cap*P47</f>
+        <v/>
+      </c>
+      <c r="R47" s="34">
+        <f>Q47*O47</f>
+        <v/>
+      </c>
+      <c r="S47" s="37">
+        <f>E47*discount</f>
+        <v/>
+      </c>
+      <c r="T47" s="38">
+        <f>S47*R47</f>
+        <v/>
+      </c>
+      <c r="U47" s="38">
+        <f>(battery/range_nm)*D47*O47*VLOOKUP(B47,country_opex,3,FALSE)</f>
+        <v/>
+      </c>
+      <c r="V47" s="38">
+        <f>VLOOKUP(B47,country_opex,2,FALSE)*crew_factor</f>
+        <v/>
+      </c>
+      <c r="W47" s="38">
+        <f>VLOOKUP(B47,country_opex,5,FALSE)</f>
+        <v/>
+      </c>
+      <c r="X47" s="38">
+        <f>maint</f>
+        <v/>
+      </c>
+      <c r="Y47" s="38">
+        <f>VLOOKUP(B47,country_opex,7,FALSE)*ins_pct</f>
+        <v/>
+      </c>
+      <c r="Z47" s="38">
+        <f>charge_berth</f>
+        <v/>
+      </c>
+      <c r="AA47" s="38">
+        <f>U47+V47+W47+X47+Y47+Z47</f>
+        <v/>
+      </c>
+      <c r="AB47" s="38">
+        <f>VLOOKUP(B47,country_opex,7,FALSE)/dep_years</f>
+        <v/>
+      </c>
+      <c r="AC47" s="38">
+        <f>T47-AA47</f>
+        <v/>
+      </c>
+      <c r="AD47" s="35">
+        <f>IF(T47=0,"",AC47/T47)</f>
+        <v/>
+      </c>
+      <c r="AE47" s="36">
+        <f>IF(AC47&lt;=0,"",VLOOKUP(B47,country_opex,7,FALSE)/AC47)</f>
+        <v/>
+      </c>
+      <c r="AF47" s="33">
+        <f>((D47*O47/diesel_nmpg)*diesel_co2pg-(battery/range_nm)*D47*O47*VLOOKUP(B47,country_opex,4,FALSE))/1000</f>
+        <v/>
+      </c>
+      <c r="AG47" s="31" t="n">
+        <v>5217</v>
+      </c>
+      <c r="AH47" s="32" t="inlineStr">
+        <is>
+          <t>T3</t>
+        </is>
+      </c>
+      <c r="AI47" s="32" t="inlineStr">
+        <is>
+          <t>med-low</t>
+        </is>
+      </c>
+      <c r="AJ47" s="39" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AK47" s="34">
+        <f>IF(AG47="","",AG47*AJ47)</f>
+        <v/>
+      </c>
+      <c r="AL47" s="34">
+        <f>IF(OR(AG47="",R47=0),"",MIN(IF(AT47="",9.9E+99,AT47),FLOOR(AK47/R47,1)))</f>
+        <v/>
+      </c>
+      <c r="AM47" s="38">
+        <f>IF(AL47="","",AL47*T47)</f>
+        <v/>
+      </c>
+      <c r="AN47" s="36">
+        <f>IF(OR(AG47="",R47=0),"",MIN(IF(AT47="",9.9E+99,AT47),AK47/R47))</f>
+        <v/>
+      </c>
+      <c r="AO47" s="38">
+        <f>IF(AN47="","",AN47*T47)</f>
+        <v/>
+      </c>
+      <c r="AP47" s="40" t="n"/>
+      <c r="AQ47" s="32" t="inlineStr">
+        <is>
+          <t>Grounded</t>
+        </is>
+      </c>
+      <c r="AR47" s="41" t="n"/>
+      <c r="AS47" s="41" t="n"/>
+      <c r="AT47" s="42" t="n"/>
+      <c r="AU47" s="43">
+        <f>IF(((S47*pax_cap*load_thin*ROUND(K47*L47*revleg_thin,0))-(((battery/range_nm)*D47*ROUND(K47*L47*revleg_thin,0)*VLOOKUP(B47,country_opex,3,FALSE))+V47+W47+X47+Y47+Z47))&lt;=0,"",VLOOKUP(B47,country_opex,7,FALSE)/((S47*pax_cap*load_thin*ROUND(K47*L47*revleg_thin,0))-(((battery/range_nm)*D47*ROUND(K47*L47*revleg_thin,0)*VLOOKUP(B47,country_opex,3,FALSE))+V47+W47+X47+Y47+Z47)))</f>
+        <v/>
+      </c>
+      <c r="AV47" s="43">
+        <f>IF(((S47*pax_cap*load_mid*ROUND(K47*L47*revleg_mid,0))-(((battery/range_nm)*D47*ROUND(K47*L47*revleg_mid,0)*VLOOKUP(B47,country_opex,3,FALSE))+V47+W47+X47+Y47+Z47))&lt;=0,"",VLOOKUP(B47,country_opex,7,FALSE)/((S47*pax_cap*load_mid*ROUND(K47*L47*revleg_mid,0))-(((battery/range_nm)*D47*ROUND(K47*L47*revleg_mid,0)*VLOOKUP(B47,country_opex,3,FALSE))+V47+W47+X47+Y47+Z47)))</f>
+        <v/>
+      </c>
+      <c r="AW47" s="43">
+        <f>IF(((S47*pax_cap*load_full*ROUND(K47*L47*revleg_full,0))-(((battery/range_nm)*D47*ROUND(K47*L47*revleg_full,0)*VLOOKUP(B47,country_opex,3,FALSE))+V47+W47+X47+Y47+Z47))&lt;=0,"",VLOOKUP(B47,country_opex,7,FALSE)/((S47*pax_cap*load_full*ROUND(K47*L47*revleg_full,0))-(((battery/range_nm)*D47*ROUND(K47*L47*revleg_full,0)*VLOOKUP(B47,country_opex,3,FALSE))+V47+W47+X47+Y47+Z47)))</f>
+        <v/>
+      </c>
+      <c r="AX47" s="44" t="n"/>
+      <c r="AY47" s="44" t="n"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="45" t="inlineStr">
         <is>
           <t>TOTAL / median</t>
         </is>
       </c>
-      <c r="T46" s="46">
-        <f>SUM(T4:T45)</f>
-        <v/>
-      </c>
-      <c r="AC46" s="46">
-        <f>SUM(AC4:AC45)</f>
-        <v/>
-      </c>
-      <c r="AD46" s="47">
-        <f>IF(T46=0,"",AC46/T46)</f>
-        <v/>
-      </c>
-      <c r="AL46" s="48">
-        <f>SUM(AL4:AL45)</f>
-        <v/>
-      </c>
-      <c r="AM46" s="46">
-        <f>SUM(AM4:AM45)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="8" t="inlineStr">
+      <c r="T48" s="46">
+        <f>SUM(T4:T47)</f>
+        <v/>
+      </c>
+      <c r="AC48" s="46">
+        <f>SUM(AC4:AC47)</f>
+        <v/>
+      </c>
+      <c r="AD48" s="47">
+        <f>IF(T48=0,"",AC48/T48)</f>
+        <v/>
+      </c>
+      <c r="AL48" s="48">
+        <f>SUM(AL4:AL47)</f>
+        <v/>
+      </c>
+      <c r="AM48" s="46">
+        <f>SUM(AM4:AM47)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="8" t="inlineStr">
         <is>
           <t>Market fleet build-up — grounded floor (network-sum of raw vessel fractions per market, rounded once; subset slices excluded; legacy per-corridor-floor totals above kept for reference)</t>
         </is>
       </c>
     </row>
-    <row r="49">
-      <c r="A49" s="24" t="inlineStr">
+    <row r="51">
+      <c r="A51" s="24" t="inlineStr">
         <is>
           <t>Market</t>
         </is>
       </c>
-      <c r="B49" s="24" t="inlineStr">
+      <c r="B51" s="24" t="inlineStr">
         <is>
           <t>Fleet basis</t>
         </is>
       </c>
-      <c r="C49" s="24" t="inlineStr">
+      <c r="C51" s="24" t="inlineStr">
         <is>
           <t>Raw vessels (sum)</t>
         </is>
       </c>
-      <c r="D49" s="24" t="inlineStr">
+      <c r="D51" s="24" t="inlineStr">
         <is>
           <t>Fleet (rounded once)</t>
         </is>
       </c>
-      <c r="E49" s="24" t="inlineStr">
+      <c r="E51" s="24" t="inlineStr">
         <is>
           <t>Market rev/yr (raw sum)</t>
         </is>
       </c>
     </row>
-    <row r="50">
-      <c r="A50" s="25" t="inlineStr">
+    <row r="52">
+      <c r="A52" s="25" t="inlineStr">
         <is>
           <t>Gulf Authority Rakta</t>
         </is>
       </c>
-      <c r="B50" s="13" t="inlineStr">
+      <c r="B52" s="13" t="inlineStr">
         <is>
           <t>network_sum / ceil</t>
         </is>
       </c>
-      <c r="C50" s="23">
-        <f>SUMIFS(AN4:AN45,A4:A45,"Gulf Authority Rakta",AP4:AP45,"=",AQ4:AQ45,"=",AR4:AR45,"=")</f>
-        <v/>
-      </c>
-      <c r="D50" s="49">
-        <f>IF(C50=0,0,CEILING(C50,1))</f>
-        <v/>
-      </c>
-      <c r="E50" s="50">
-        <f>SUMIFS(AO4:AO45,A4:A45,"Gulf Authority Rakta",AP4:AP45,"=",AQ4:AQ45,"=",AR4:AR45,"=")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="45" t="inlineStr">
+      <c r="C52" s="23">
+        <f>SUMIFS(AN4:AN47,A4:A47,"Gulf Authority Rakta",AP4:AP47,"=",AQ4:AQ47,"Grounded")</f>
+        <v/>
+      </c>
+      <c r="D52" s="49">
+        <f>IF(C52=0,0,CEILING(C52,1))</f>
+        <v/>
+      </c>
+      <c r="E52" s="50">
+        <f>SUMIFS(AO4:AO47,A4:A47,"Gulf Authority Rakta",AP4:AP47,"=",AQ4:AQ47,"Grounded")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="45" t="inlineStr">
         <is>
           <t>GROUNDED FLOOR (PUBLISHED)</t>
         </is>
       </c>
-      <c r="D51" s="48">
-        <f>SUM(D50:D50)</f>
-        <v/>
-      </c>
-      <c r="E51" s="46">
-        <f>SUM(E50:E50)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="51" t="inlineStr">
+      <c r="D53" s="48">
+        <f>SUM(D52:D52)</f>
+        <v/>
+      </c>
+      <c r="E53" s="46">
+        <f>SUM(E52:E52)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="20" t="inlineStr">
+        <is>
+          <t>ESTIMATED DEMAND (country-median cascade; held OUT of grounded floor)</t>
+        </is>
+      </c>
+      <c r="D54" s="51">
+        <f>SUMIF(AQ4:AQ47,"Estimated",AL4:AL47)</f>
+        <v/>
+      </c>
+      <c r="E54" s="52">
+        <f>SUMIF(AQ4:AQ47,"Estimated",AM4:AM47)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="53" t="inlineStr">
         <is>
           <t>Held for Quanta-LR (&gt;70nm, roadmap H2 2026+):</t>
         </is>
       </c>
-      <c r="C53" s="52" t="inlineStr">
+      <c r="C55" s="54" t="inlineStr">
+        <is>
+          <t>Abu Dhabi → Manama (264.1nm)</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="C56" s="54" t="inlineStr">
+        <is>
+          <t>Manama → Doha (98.8nm)</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="C57" s="54" t="inlineStr">
+        <is>
+          <t>Manama → Dubai (290.6nm)</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="C58" s="54" t="inlineStr">
         <is>
           <t>Ras Al Khaimah → Abu Dhabi (112.0nm)</t>
         </is>
       </c>
     </row>
-    <row r="54">
-      <c r="C54" s="52" t="inlineStr">
+    <row r="59">
+      <c r="C59" s="54" t="inlineStr">
+        <is>
+          <t>Ras Al Khaimah → Doha (240.7nm)</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="C60" s="54" t="inlineStr">
+        <is>
+          <t>Ras Al Khaimah → Manama (289.7nm)</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="C61" s="54" t="inlineStr">
         <is>
           <t>Ras Al Khaimah → Muscat (263.5nm)</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="C55" s="52" t="inlineStr">
-        <is>
-          <t>Ras Al Khaimah → Doha (240.7nm)</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="C56" s="52" t="inlineStr">
-        <is>
-          <t>Ras Al Khaimah → Manama (289.7nm)</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
+    <mergeCell ref="A50:L50"/>
     <mergeCell ref="A1:L1"/>
-    <mergeCell ref="A48:L48"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -10412,7 +11042,7 @@
       </c>
       <c r="E15" s="14" t="inlineStr">
         <is>
-          <t>Live sum of grounded corridor market-rev (10% capture, today's demand, sourced corridors).</t>
+          <t>Live sum of grounded-floor corridor market-rev only (Floor bucket = Grounded; cascade-estimated rows held out). Matches growth.py _headline_anchor and deck TAM.</t>
         </is>
       </c>
     </row>
@@ -10601,12 +11231,12 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="53" t="inlineStr">
+      <c r="A26" s="55" t="inlineStr">
         <is>
           <t>Note</t>
         </is>
       </c>
-      <c r="B26" s="54" t="inlineStr">
+      <c r="B26" s="56" t="inlineStr">
         <is>
           <t>All rungs are one multiplication chain off M_today, which is live off the corridor floor. Change any input (a fare, a multiplier, the scenario) and the whole ladder moves. Bands (low/MID/high) are never single points; greenfield census is per-partner.</t>
         </is>
